--- a/Reference_docs/Ormeco Sensor List_Rev04- commenets by IE.xlsx
+++ b/Reference_docs/Ormeco Sensor List_Rev04- commenets by IE.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DAIKAI VR\Desktop\Ormin_Project_V5\Reference_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF1B2281-37BB-4B2E-99FB-49C69192E084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31039E42-5174-4D84-AF5A-A6426A6E0FF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rev04" sheetId="1" r:id="rId1"/>
     <sheet name="Modbus Digital" sheetId="2" r:id="rId2"/>
+    <sheet name="Modbus Analog" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -185,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4747" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4765" uniqueCount="632">
   <si>
     <t>No.</t>
   </si>
@@ -2663,6 +2664,57 @@
   </si>
   <si>
     <t>Address</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name </t>
+  </si>
+  <si>
+    <t>Flow 1</t>
+  </si>
+  <si>
+    <t>Flow 2</t>
+  </si>
+  <si>
+    <t>Flow 3</t>
+  </si>
+  <si>
+    <t>Flow 4</t>
+  </si>
+  <si>
+    <t>Flow 5</t>
+  </si>
+  <si>
+    <t>Flow 6</t>
+  </si>
+  <si>
+    <t>Flow 7</t>
+  </si>
+  <si>
+    <t>Flow 8</t>
+  </si>
+  <si>
+    <t>Flow 9</t>
+  </si>
+  <si>
+    <t>Flow 10</t>
+  </si>
+  <si>
+    <t>Flow 11</t>
+  </si>
+  <si>
+    <t>Flow 12</t>
+  </si>
+  <si>
+    <t>Flow 13</t>
+  </si>
+  <si>
+    <t>Flow 14</t>
+  </si>
+  <si>
+    <t>Flow 15</t>
+  </si>
+  <si>
+    <t>Flow 16</t>
   </si>
 </sst>
 </file>
@@ -39132,4 +39184,151 @@
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEBAB262-57D3-42DC-96D3-D86004D06A38}">
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>615</v>
+      </c>
+      <c r="B1" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>616</v>
+      </c>
+      <c r="B2">
+        <v>40001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>617</v>
+      </c>
+      <c r="B3">
+        <v>40001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>618</v>
+      </c>
+      <c r="B4">
+        <v>40001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>619</v>
+      </c>
+      <c r="B5">
+        <v>40001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>620</v>
+      </c>
+      <c r="B6">
+        <v>40001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>621</v>
+      </c>
+      <c r="B7">
+        <v>40001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>622</v>
+      </c>
+      <c r="B8">
+        <v>40001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>623</v>
+      </c>
+      <c r="B9">
+        <v>40001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>624</v>
+      </c>
+      <c r="B10">
+        <v>40001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>625</v>
+      </c>
+      <c r="B11">
+        <v>40001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>626</v>
+      </c>
+      <c r="B12">
+        <v>40001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>627</v>
+      </c>
+      <c r="B13">
+        <v>40001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>628</v>
+      </c>
+      <c r="B14">
+        <v>40001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>629</v>
+      </c>
+      <c r="B15">
+        <v>40001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>630</v>
+      </c>
+      <c r="B16">
+        <v>40001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>631</v>
+      </c>
+      <c r="B17">
+        <v>40001</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Reference_docs/Ormeco Sensor List_Rev04- commenets by IE.xlsx
+++ b/Reference_docs/Ormeco Sensor List_Rev04- commenets by IE.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Quyen PC\Desktop\My Repo\Ormin_Project_V5\Reference_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4227A5F-B191-47A9-9153-2AA9D3678C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3C25682-3819-4909-8FE2-9DE32E9F8EA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rev04" sheetId="1" r:id="rId1"/>
-    <sheet name="Modbus Digital" sheetId="2" r:id="rId2"/>
-    <sheet name="Modbus Analog" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId2"/>
+    <sheet name="Modbus Digital" sheetId="2" r:id="rId3"/>
+    <sheet name="Modbus Analog" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -186,7 +187,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4765" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4926" uniqueCount="694">
   <si>
     <t>No.</t>
   </si>
@@ -2715,6 +2716,192 @@
   </si>
   <si>
     <t>Column1</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Channel name</t>
+  </si>
+  <si>
+    <t>PMS</t>
+  </si>
+  <si>
+    <t>GENERATOR BEARING  (ANTI-FLY-WHEEL SIDE)</t>
+  </si>
+  <si>
+    <t>Lable</t>
+  </si>
+  <si>
+    <t>Intake Air Pressure</t>
+  </si>
+  <si>
+    <t>Air Receiver Pressure</t>
+  </si>
+  <si>
+    <t>AIR SYSTEM</t>
+  </si>
+  <si>
+    <t>Stator Winding Temp U</t>
+  </si>
+  <si>
+    <t>Stator Winding Temp V</t>
+  </si>
+  <si>
+    <t>Stator Winding Temp W</t>
+  </si>
+  <si>
+    <t>DE Bearing Temp</t>
+  </si>
+  <si>
+    <t>NDE Bearing Temp</t>
+  </si>
+  <si>
+    <t>FUEL OIL FLOW SYSTEM</t>
+  </si>
+  <si>
+    <t>DO Transfer Flow</t>
+  </si>
+  <si>
+    <t>HO Transfer Flow</t>
+  </si>
+  <si>
+    <t>DO Engine Inlet Flow</t>
+  </si>
+  <si>
+    <t>HO Engine Inlet Flow</t>
+  </si>
+  <si>
+    <t>DO Engine Return Flow</t>
+  </si>
+  <si>
+    <t>HO Engine Return Flow</t>
+  </si>
+  <si>
+    <t>ENGINE PARAMETERS</t>
+  </si>
+  <si>
+    <t>Engine Running Hours</t>
+  </si>
+  <si>
+    <t>Engine Power</t>
+  </si>
+  <si>
+    <t>Engine Speed</t>
+  </si>
+  <si>
+    <t>T/C Outlet Temp</t>
+  </si>
+  <si>
+    <t>Cyl 1 Exhaust Temp</t>
+  </si>
+  <si>
+    <t>Cyl 2 Exhaust Temp</t>
+  </si>
+  <si>
+    <t>Cyl 3 Exhaust Temp</t>
+  </si>
+  <si>
+    <t>Cyl 4 Exhaust Temp</t>
+  </si>
+  <si>
+    <t>Cyl 5 Exhaust Temp</t>
+  </si>
+  <si>
+    <t>Cyl 6 Exhaust Temp</t>
+  </si>
+  <si>
+    <t>T/C Inlet Temp</t>
+  </si>
+  <si>
+    <t>Generator Voltage</t>
+  </si>
+  <si>
+    <t>Generator Frequency</t>
+  </si>
+  <si>
+    <t>Generator Current</t>
+  </si>
+  <si>
+    <t>Generator Power Factor</t>
+  </si>
+  <si>
+    <t>FUEL TEMPERATURE</t>
+  </si>
+  <si>
+    <t>FUEL OIL SYSTEM</t>
+  </si>
+  <si>
+    <t>Fuel Oil Pressure</t>
+  </si>
+  <si>
+    <t>LUB OIL SYSTEM</t>
+  </si>
+  <si>
+    <t>Engine LO Pressure</t>
+  </si>
+  <si>
+    <t>Turbo LO Pressure</t>
+  </si>
+  <si>
+    <t>LO Cooler Inlet Temp</t>
+  </si>
+  <si>
+    <t>LO Cooler Outlet Temp</t>
+  </si>
+  <si>
+    <t>DO Engine Inlet Temp</t>
+  </si>
+  <si>
+    <t>HO Engine Inlet Temp</t>
+  </si>
+  <si>
+    <t>DO Engine Return Temp</t>
+  </si>
+  <si>
+    <t>HO Engine Return Temp</t>
+  </si>
+  <si>
+    <t>Oil Mist Level</t>
+  </si>
+  <si>
+    <t>OMD Analog Signal</t>
+  </si>
+  <si>
+    <t>OIL MIST DETECTION</t>
+  </si>
+  <si>
+    <t>COOLING WATER SYSTEM</t>
+  </si>
+  <si>
+    <t>Jacket Water Pressure</t>
+  </si>
+  <si>
+    <t>Cooler Water Pressure</t>
+  </si>
+  <si>
+    <t>Jacket Water Inlet Temp</t>
+  </si>
+  <si>
+    <t>Jacket Water Outlet Temp</t>
+  </si>
+  <si>
+    <t>Cooler Water Inlet Temp</t>
+  </si>
+  <si>
+    <t>Cooler Water Outlet Temp</t>
+  </si>
+  <si>
+    <t>CW Before LO Cooler Temp</t>
+  </si>
+  <si>
+    <t>ALTERNATOR TEMPERATURE</t>
+  </si>
+  <si>
+    <t>EXHAUST GAS TEMP</t>
   </si>
 </sst>
 </file>
@@ -2777,7 +2964,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2796,8 +2983,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="28">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -3138,11 +3331,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF757070"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF757070"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF757070"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF757070"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF757070"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF757070"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="157">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3457,25 +3680,21 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3509,57 +3728,36 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="9">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3768,6 +3966,52 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3782,7 +4026,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{68E061EB-B5F0-44C5-B2D5-A92C5D4115C8}" name="Table1" displayName="Table1" ref="A1:F1189" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" tableBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{68E061EB-B5F0-44C5-B2D5-A92C5D4115C8}" name="Table1" displayName="Table1" ref="A1:F1189" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7" tableBorderDxfId="6">
   <autoFilter ref="A1:F1189" xr:uid="{68E061EB-B5F0-44C5-B2D5-A92C5D4115C8}">
     <filterColumn colId="2">
       <filters>
@@ -3796,14 +4040,29 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{2C899472-D557-48E2-8865-CC2280D66928}" name="No." dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{C7636155-AFB5-448D-B5CD-583B717D1DC7}" name="Device " dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{1AC23AD8-99E3-490A-84A3-7F7275A97222}" name="Column1" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{EE3DA178-9443-47E0-A48B-08AB9DF900EA}" name="Name" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{7B57A30E-846F-47AB-AA98-153838862D67}" name="Description" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{3D8ED10F-C9D3-45ED-A78F-67321872599D}" name="I/O Type" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{2C899472-D557-48E2-8865-CC2280D66928}" name="No." dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{C7636155-AFB5-448D-B5CD-583B717D1DC7}" name="Device " dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{1AC23AD8-99E3-490A-84A3-7F7275A97222}" name="Column1" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{EE3DA178-9443-47E0-A48B-08AB9DF900EA}" name="Name" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{7B57A30E-846F-47AB-AA98-153838862D67}" name="Description" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{3D8ED10F-C9D3-45ED-A78F-67321872599D}" name="I/O Type" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A6989B32-4ED1-4B5C-8116-07963E5A6047}" name="Table2" displayName="Table2" ref="B1:D47" totalsRowShown="0">
+  <autoFilter ref="B1:D47" xr:uid="{A6989B32-4ED1-4B5C-8116-07963E5A6047}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D47">
+    <sortCondition ref="C1:C47"/>
+  </sortState>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{33214016-635D-4635-BFA6-165B320C9D46}" name="Channel name"/>
+    <tableColumn id="2" xr3:uid="{4DE78A70-5298-4187-8142-1E320C9E3489}" name="Group"/>
+    <tableColumn id="3" xr3:uid="{7EB1FB42-51D1-456A-8CB6-7A110FEC989C}" name="Lable"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -4029,22 +4288,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="42.75" customHeight="1">
-      <c r="A1" s="143" t="s">
+      <c r="A1" s="141" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="144" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="144" t="s">
+      <c r="B1" s="142" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="142" t="s">
         <v>631</v>
       </c>
-      <c r="D1" s="144" t="s">
+      <c r="D1" s="142" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="144" t="s">
+      <c r="E1" s="142" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="145" t="s">
+      <c r="F1" s="143" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -4065,10 +4324,10 @@
       <c r="L1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="128" t="s">
+      <c r="M1" s="148" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="129"/>
+      <c r="N1" s="149"/>
     </row>
     <row r="2" spans="1:16" ht="35.4" hidden="1" customHeight="1">
       <c r="A2" s="87">
@@ -4109,7 +4368,7 @@
       <c r="P2" s="12"/>
     </row>
     <row r="3" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A3" s="138"/>
+      <c r="A3" s="136"/>
       <c r="B3" s="5">
         <v>12</v>
       </c>
@@ -4145,7 +4404,7 @@
       <c r="P3" s="12"/>
     </row>
     <row r="4" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A4" s="138"/>
+      <c r="A4" s="136"/>
       <c r="B4" s="5">
         <v>12</v>
       </c>
@@ -4181,7 +4440,7 @@
       <c r="P4" s="12"/>
     </row>
     <row r="5" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A5" s="130"/>
+      <c r="A5" s="128"/>
       <c r="B5" s="5">
         <v>12</v>
       </c>
@@ -4271,7 +4530,7 @@
       <c r="P7" s="12"/>
     </row>
     <row r="8" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A8" s="138"/>
+      <c r="A8" s="136"/>
       <c r="B8" s="5" t="s">
         <v>24</v>
       </c>
@@ -4305,7 +4564,7 @@
       <c r="P8" s="12"/>
     </row>
     <row r="9" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A9" s="138"/>
+      <c r="A9" s="136"/>
       <c r="B9" s="5" t="s">
         <v>24</v>
       </c>
@@ -4339,7 +4598,7 @@
       <c r="P9" s="12"/>
     </row>
     <row r="10" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A10" s="130"/>
+      <c r="A10" s="128"/>
       <c r="B10" s="5" t="s">
         <v>24</v>
       </c>
@@ -4429,7 +4688,7 @@
       <c r="P12" s="12"/>
     </row>
     <row r="13" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A13" s="138"/>
+      <c r="A13" s="136"/>
       <c r="B13" s="5" t="s">
         <v>27</v>
       </c>
@@ -4465,7 +4724,7 @@
       <c r="P13" s="12"/>
     </row>
     <row r="14" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A14" s="138"/>
+      <c r="A14" s="136"/>
       <c r="B14" s="5" t="s">
         <v>27</v>
       </c>
@@ -4501,7 +4760,7 @@
       <c r="P14" s="12"/>
     </row>
     <row r="15" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A15" s="130"/>
+      <c r="A15" s="128"/>
       <c r="B15" s="5" t="s">
         <v>27</v>
       </c>
@@ -4591,7 +4850,7 @@
       <c r="P17" s="12"/>
     </row>
     <row r="18" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A18" s="138"/>
+      <c r="A18" s="136"/>
       <c r="B18" s="5" t="s">
         <v>31</v>
       </c>
@@ -4625,7 +4884,7 @@
       <c r="P18" s="12"/>
     </row>
     <row r="19" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A19" s="138"/>
+      <c r="A19" s="136"/>
       <c r="B19" s="5" t="s">
         <v>31</v>
       </c>
@@ -4659,7 +4918,7 @@
       <c r="P19" s="12"/>
     </row>
     <row r="20" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A20" s="130"/>
+      <c r="A20" s="128"/>
       <c r="B20" s="5" t="s">
         <v>31</v>
       </c>
@@ -4749,7 +5008,7 @@
       <c r="P22" s="12"/>
     </row>
     <row r="23" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A23" s="138"/>
+      <c r="A23" s="136"/>
       <c r="B23" s="5" t="s">
         <v>34</v>
       </c>
@@ -4785,7 +5044,7 @@
       <c r="P23" s="12"/>
     </row>
     <row r="24" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A24" s="138"/>
+      <c r="A24" s="136"/>
       <c r="B24" s="5" t="s">
         <v>34</v>
       </c>
@@ -4821,7 +5080,7 @@
       <c r="P24" s="12"/>
     </row>
     <row r="25" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A25" s="130"/>
+      <c r="A25" s="128"/>
       <c r="B25" s="5" t="s">
         <v>34</v>
       </c>
@@ -4913,7 +5172,7 @@
       <c r="P27" s="12"/>
     </row>
     <row r="28" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A28" s="138"/>
+      <c r="A28" s="136"/>
       <c r="B28" s="5" t="s">
         <v>37</v>
       </c>
@@ -4949,7 +5208,7 @@
       <c r="P28" s="12"/>
     </row>
     <row r="29" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A29" s="138"/>
+      <c r="A29" s="136"/>
       <c r="B29" s="5" t="s">
         <v>37</v>
       </c>
@@ -4985,7 +5244,7 @@
       <c r="P29" s="12"/>
     </row>
     <row r="30" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A30" s="130"/>
+      <c r="A30" s="128"/>
       <c r="B30" s="5" t="s">
         <v>37</v>
       </c>
@@ -5077,7 +5336,7 @@
       <c r="P32" s="12"/>
     </row>
     <row r="33" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A33" s="138"/>
+      <c r="A33" s="136"/>
       <c r="B33" s="5" t="s">
         <v>40</v>
       </c>
@@ -5113,7 +5372,7 @@
       <c r="P33" s="12"/>
     </row>
     <row r="34" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A34" s="138"/>
+      <c r="A34" s="136"/>
       <c r="B34" s="5" t="s">
         <v>40</v>
       </c>
@@ -5149,7 +5408,7 @@
       <c r="P34" s="12"/>
     </row>
     <row r="35" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A35" s="130"/>
+      <c r="A35" s="128"/>
       <c r="B35" s="5" t="s">
         <v>40</v>
       </c>
@@ -5241,7 +5500,7 @@
       <c r="P37" s="12"/>
     </row>
     <row r="38" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A38" s="138"/>
+      <c r="A38" s="136"/>
       <c r="B38" s="5" t="s">
         <v>43</v>
       </c>
@@ -5277,7 +5536,7 @@
       <c r="P38" s="12"/>
     </row>
     <row r="39" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A39" s="138"/>
+      <c r="A39" s="136"/>
       <c r="B39" s="5" t="s">
         <v>43</v>
       </c>
@@ -5313,7 +5572,7 @@
       <c r="P39" s="12"/>
     </row>
     <row r="40" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A40" s="130"/>
+      <c r="A40" s="128"/>
       <c r="B40" s="5" t="s">
         <v>43</v>
       </c>
@@ -5399,7 +5658,7 @@
       <c r="P42" s="12"/>
     </row>
     <row r="43" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A43" s="138"/>
+      <c r="A43" s="136"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5" t="s">
         <v>18</v>
@@ -5429,7 +5688,7 @@
       <c r="P43" s="12"/>
     </row>
     <row r="44" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A44" s="138"/>
+      <c r="A44" s="136"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5" t="s">
         <v>20</v>
@@ -5459,7 +5718,7 @@
       <c r="P44" s="12"/>
     </row>
     <row r="45" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A45" s="130"/>
+      <c r="A45" s="128"/>
       <c r="B45" s="5"/>
       <c r="C45" s="5" t="s">
         <v>22</v>
@@ -5539,7 +5798,7 @@
       <c r="P47" s="12"/>
     </row>
     <row r="48" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A48" s="138"/>
+      <c r="A48" s="136"/>
       <c r="B48" s="5"/>
       <c r="C48" s="5" t="s">
         <v>18</v>
@@ -5569,7 +5828,7 @@
       <c r="P48" s="12"/>
     </row>
     <row r="49" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A49" s="138"/>
+      <c r="A49" s="136"/>
       <c r="B49" s="5"/>
       <c r="C49" s="5" t="s">
         <v>20</v>
@@ -5599,7 +5858,7 @@
       <c r="P49" s="12"/>
     </row>
     <row r="50" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A50" s="130"/>
+      <c r="A50" s="128"/>
       <c r="B50" s="5"/>
       <c r="C50" s="5" t="s">
         <v>22</v>
@@ -5683,7 +5942,7 @@
       <c r="P52" s="12"/>
     </row>
     <row r="53" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A53" s="138"/>
+      <c r="A53" s="136"/>
       <c r="B53" s="5" t="s">
         <v>48</v>
       </c>
@@ -5717,7 +5976,7 @@
       <c r="P53" s="12"/>
     </row>
     <row r="54" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A54" s="138"/>
+      <c r="A54" s="136"/>
       <c r="B54" s="5" t="s">
         <v>48</v>
       </c>
@@ -5751,7 +6010,7 @@
       <c r="P54" s="12"/>
     </row>
     <row r="55" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A55" s="130"/>
+      <c r="A55" s="128"/>
       <c r="B55" s="5" t="s">
         <v>48</v>
       </c>
@@ -5841,7 +6100,7 @@
       <c r="P57" s="12"/>
     </row>
     <row r="58" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A58" s="138"/>
+      <c r="A58" s="136"/>
       <c r="B58" s="5" t="s">
         <v>51</v>
       </c>
@@ -5877,7 +6136,7 @@
       <c r="P58" s="12"/>
     </row>
     <row r="59" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A59" s="138"/>
+      <c r="A59" s="136"/>
       <c r="B59" s="5" t="s">
         <v>51</v>
       </c>
@@ -5913,7 +6172,7 @@
       <c r="P59" s="12"/>
     </row>
     <row r="60" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A60" s="130"/>
+      <c r="A60" s="128"/>
       <c r="B60" s="5" t="s">
         <v>51</v>
       </c>
@@ -5997,7 +6256,7 @@
       <c r="N62" s="11"/>
     </row>
     <row r="63" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A63" s="138"/>
+      <c r="A63" s="136"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5" t="s">
         <v>18</v>
@@ -6025,7 +6284,7 @@
       <c r="N63" s="11"/>
     </row>
     <row r="64" spans="1:16" ht="18.75" hidden="1" customHeight="1">
-      <c r="A64" s="138"/>
+      <c r="A64" s="136"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5" t="s">
         <v>20</v>
@@ -6053,7 +6312,7 @@
       <c r="N64" s="11"/>
     </row>
     <row r="65" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A65" s="130"/>
+      <c r="A65" s="128"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5" t="s">
         <v>22</v>
@@ -6127,7 +6386,7 @@
       <c r="N67" s="11"/>
     </row>
     <row r="68" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A68" s="138"/>
+      <c r="A68" s="136"/>
       <c r="B68" s="5"/>
       <c r="C68" s="5" t="s">
         <v>18</v>
@@ -6155,7 +6414,7 @@
       <c r="N68" s="11"/>
     </row>
     <row r="69" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A69" s="138"/>
+      <c r="A69" s="136"/>
       <c r="B69" s="5"/>
       <c r="C69" s="5" t="s">
         <v>20</v>
@@ -6183,7 +6442,7 @@
       <c r="N69" s="11"/>
     </row>
     <row r="70" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A70" s="130"/>
+      <c r="A70" s="128"/>
       <c r="B70" s="5"/>
       <c r="C70" s="5" t="s">
         <v>22</v>
@@ -6257,7 +6516,7 @@
       <c r="N72" s="11"/>
     </row>
     <row r="73" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A73" s="138"/>
+      <c r="A73" s="136"/>
       <c r="B73" s="5"/>
       <c r="C73" s="5" t="s">
         <v>18</v>
@@ -6285,7 +6544,7 @@
       <c r="N73" s="11"/>
     </row>
     <row r="74" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A74" s="138"/>
+      <c r="A74" s="136"/>
       <c r="B74" s="5"/>
       <c r="C74" s="5" t="s">
         <v>20</v>
@@ -6313,7 +6572,7 @@
       <c r="N74" s="11"/>
     </row>
     <row r="75" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A75" s="130"/>
+      <c r="A75" s="128"/>
       <c r="B75" s="5"/>
       <c r="C75" s="5" t="s">
         <v>22</v>
@@ -6390,7 +6649,7 @@
       <c r="Q77" s="12"/>
     </row>
     <row r="78" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A78" s="138"/>
+      <c r="A78" s="136"/>
       <c r="B78" s="5"/>
       <c r="C78" s="5" t="s">
         <v>18</v>
@@ -6421,7 +6680,7 @@
       <c r="Q78" s="12"/>
     </row>
     <row r="79" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A79" s="138"/>
+      <c r="A79" s="136"/>
       <c r="B79" s="5"/>
       <c r="C79" s="5" t="s">
         <v>20</v>
@@ -6452,7 +6711,7 @@
       <c r="Q79" s="12"/>
     </row>
     <row r="80" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A80" s="130"/>
+      <c r="A80" s="128"/>
       <c r="B80" s="5"/>
       <c r="C80" s="5" t="s">
         <v>22</v>
@@ -6535,7 +6794,7 @@
       <c r="Q82" s="12"/>
     </row>
     <row r="83" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A83" s="138"/>
+      <c r="A83" s="136"/>
       <c r="B83" s="5"/>
       <c r="C83" s="5" t="s">
         <v>18</v>
@@ -6566,7 +6825,7 @@
       <c r="Q83" s="12"/>
     </row>
     <row r="84" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A84" s="138"/>
+      <c r="A84" s="136"/>
       <c r="B84" s="5"/>
       <c r="C84" s="5" t="s">
         <v>20</v>
@@ -6597,7 +6856,7 @@
       <c r="Q84" s="12"/>
     </row>
     <row r="85" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A85" s="130"/>
+      <c r="A85" s="128"/>
       <c r="B85" s="5"/>
       <c r="C85" s="5" t="s">
         <v>22</v>
@@ -6684,7 +6943,7 @@
       <c r="Q87" s="12"/>
     </row>
     <row r="88" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A88" s="138"/>
+      <c r="A88" s="136"/>
       <c r="B88" s="5" t="s">
         <v>60</v>
       </c>
@@ -6719,7 +6978,7 @@
       <c r="Q88" s="12"/>
     </row>
     <row r="89" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A89" s="138"/>
+      <c r="A89" s="136"/>
       <c r="B89" s="5" t="s">
         <v>60</v>
       </c>
@@ -6754,7 +7013,7 @@
       <c r="Q89" s="12"/>
     </row>
     <row r="90" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A90" s="130"/>
+      <c r="A90" s="128"/>
       <c r="B90" s="5" t="s">
         <v>60</v>
       </c>
@@ -6845,7 +7104,7 @@
       <c r="Q92" s="12"/>
     </row>
     <row r="93" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A93" s="138"/>
+      <c r="A93" s="136"/>
       <c r="B93" s="5" t="s">
         <v>63</v>
       </c>
@@ -6880,7 +7139,7 @@
       <c r="Q93" s="12"/>
     </row>
     <row r="94" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A94" s="138"/>
+      <c r="A94" s="136"/>
       <c r="B94" s="5" t="s">
         <v>63</v>
       </c>
@@ -6915,7 +7174,7 @@
       <c r="Q94" s="12"/>
     </row>
     <row r="95" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A95" s="130"/>
+      <c r="A95" s="128"/>
       <c r="B95" s="5" t="s">
         <v>63</v>
       </c>
@@ -7008,7 +7267,7 @@
       <c r="Q97" s="12"/>
     </row>
     <row r="98" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A98" s="138"/>
+      <c r="A98" s="136"/>
       <c r="B98" s="5" t="s">
         <v>66</v>
       </c>
@@ -7045,7 +7304,7 @@
       <c r="Q98" s="12"/>
     </row>
     <row r="99" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A99" s="138"/>
+      <c r="A99" s="136"/>
       <c r="B99" s="5" t="s">
         <v>66</v>
       </c>
@@ -7082,7 +7341,7 @@
       <c r="Q99" s="12"/>
     </row>
     <row r="100" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A100" s="130"/>
+      <c r="A100" s="128"/>
       <c r="B100" s="5" t="s">
         <v>66</v>
       </c>
@@ -7177,7 +7436,7 @@
       <c r="Q102" s="12"/>
     </row>
     <row r="103" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A103" s="138"/>
+      <c r="A103" s="136"/>
       <c r="B103" s="5" t="s">
         <v>70</v>
       </c>
@@ -7214,7 +7473,7 @@
       <c r="Q103" s="12"/>
     </row>
     <row r="104" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A104" s="138"/>
+      <c r="A104" s="136"/>
       <c r="B104" s="5" t="s">
         <v>70</v>
       </c>
@@ -7251,7 +7510,7 @@
       <c r="Q104" s="12"/>
     </row>
     <row r="105" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A105" s="130"/>
+      <c r="A105" s="128"/>
       <c r="B105" s="5" t="s">
         <v>70</v>
       </c>
@@ -7515,7 +7774,7 @@
       <c r="Q112" s="12"/>
     </row>
     <row r="113" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A113" s="138"/>
+      <c r="A113" s="136"/>
       <c r="B113" s="5" t="s">
         <v>77</v>
       </c>
@@ -7552,7 +7811,7 @@
       <c r="Q113" s="12"/>
     </row>
     <row r="114" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A114" s="138"/>
+      <c r="A114" s="136"/>
       <c r="B114" s="5" t="s">
         <v>77</v>
       </c>
@@ -7589,7 +7848,7 @@
       <c r="Q114" s="12"/>
     </row>
     <row r="115" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A115" s="130"/>
+      <c r="A115" s="128"/>
       <c r="B115" s="5" t="s">
         <v>77</v>
       </c>
@@ -7684,7 +7943,7 @@
       <c r="Q117" s="12"/>
     </row>
     <row r="118" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A118" s="138"/>
+      <c r="A118" s="136"/>
       <c r="B118" s="5" t="s">
         <v>81</v>
       </c>
@@ -7721,7 +7980,7 @@
       <c r="Q118" s="12"/>
     </row>
     <row r="119" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A119" s="138"/>
+      <c r="A119" s="136"/>
       <c r="B119" s="5" t="s">
         <v>81</v>
       </c>
@@ -7758,7 +8017,7 @@
       <c r="Q119" s="12"/>
     </row>
     <row r="120" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A120" s="130"/>
+      <c r="A120" s="128"/>
       <c r="B120" s="5" t="s">
         <v>81</v>
       </c>
@@ -7851,7 +8110,7 @@
       <c r="Q122" s="12"/>
     </row>
     <row r="123" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A123" s="138"/>
+      <c r="A123" s="136"/>
       <c r="B123" s="5" t="s">
         <v>85</v>
       </c>
@@ -7886,7 +8145,7 @@
       <c r="Q123" s="12"/>
     </row>
     <row r="124" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A124" s="138"/>
+      <c r="A124" s="136"/>
       <c r="B124" s="5" t="s">
         <v>85</v>
       </c>
@@ -7921,7 +8180,7 @@
       <c r="Q124" s="12"/>
     </row>
     <row r="125" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A125" s="130"/>
+      <c r="A125" s="128"/>
       <c r="B125" s="5" t="s">
         <v>85</v>
       </c>
@@ -8012,7 +8271,7 @@
       <c r="Q127" s="12"/>
     </row>
     <row r="128" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A128" s="138"/>
+      <c r="A128" s="136"/>
       <c r="B128" s="5" t="s">
         <v>88</v>
       </c>
@@ -8047,7 +8306,7 @@
       <c r="Q128" s="12"/>
     </row>
     <row r="129" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A129" s="138"/>
+      <c r="A129" s="136"/>
       <c r="B129" s="5" t="s">
         <v>88</v>
       </c>
@@ -8082,7 +8341,7 @@
       <c r="Q129" s="12"/>
     </row>
     <row r="130" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A130" s="130"/>
+      <c r="A130" s="128"/>
       <c r="B130" s="5" t="s">
         <v>88</v>
       </c>
@@ -8175,7 +8434,7 @@
       <c r="Q132" s="12"/>
     </row>
     <row r="133" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A133" s="138"/>
+      <c r="A133" s="136"/>
       <c r="B133" s="5" t="s">
         <v>91</v>
       </c>
@@ -8212,7 +8471,7 @@
       <c r="Q133" s="12"/>
     </row>
     <row r="134" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A134" s="138"/>
+      <c r="A134" s="136"/>
       <c r="B134" s="5" t="s">
         <v>91</v>
       </c>
@@ -8249,7 +8508,7 @@
       <c r="Q134" s="12"/>
     </row>
     <row r="135" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A135" s="130"/>
+      <c r="A135" s="128"/>
       <c r="B135" s="5" t="s">
         <v>91</v>
       </c>
@@ -8344,7 +8603,7 @@
       <c r="Q137" s="12"/>
     </row>
     <row r="138" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A138" s="138"/>
+      <c r="A138" s="136"/>
       <c r="B138" s="5" t="s">
         <v>95</v>
       </c>
@@ -8381,7 +8640,7 @@
       <c r="Q138" s="12"/>
     </row>
     <row r="139" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A139" s="138"/>
+      <c r="A139" s="136"/>
       <c r="B139" s="5" t="s">
         <v>95</v>
       </c>
@@ -8418,7 +8677,7 @@
       <c r="Q139" s="12"/>
     </row>
     <row r="140" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A140" s="130"/>
+      <c r="A140" s="128"/>
       <c r="B140" s="5" t="s">
         <v>95</v>
       </c>
@@ -8511,7 +8770,7 @@
       <c r="Q142" s="12"/>
     </row>
     <row r="143" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A143" s="138"/>
+      <c r="A143" s="136"/>
       <c r="B143" s="5" t="s">
         <v>99</v>
       </c>
@@ -8546,7 +8805,7 @@
       <c r="Q143" s="12"/>
     </row>
     <row r="144" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A144" s="138"/>
+      <c r="A144" s="136"/>
       <c r="B144" s="5" t="s">
         <v>99</v>
       </c>
@@ -8581,7 +8840,7 @@
       <c r="Q144" s="12"/>
     </row>
     <row r="145" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A145" s="130"/>
+      <c r="A145" s="128"/>
       <c r="B145" s="5" t="s">
         <v>99</v>
       </c>
@@ -8672,7 +8931,7 @@
       <c r="Q147" s="12"/>
     </row>
     <row r="148" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A148" s="138"/>
+      <c r="A148" s="136"/>
       <c r="B148" s="5" t="s">
         <v>102</v>
       </c>
@@ -8707,7 +8966,7 @@
       <c r="Q148" s="12"/>
     </row>
     <row r="149" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A149" s="138"/>
+      <c r="A149" s="136"/>
       <c r="B149" s="5" t="s">
         <v>102</v>
       </c>
@@ -8742,7 +9001,7 @@
       <c r="Q149" s="12"/>
     </row>
     <row r="150" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A150" s="130"/>
+      <c r="A150" s="128"/>
       <c r="B150" s="5" t="s">
         <v>102</v>
       </c>
@@ -8835,7 +9094,7 @@
       <c r="Q152" s="12"/>
     </row>
     <row r="153" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A153" s="138"/>
+      <c r="A153" s="136"/>
       <c r="B153" s="5" t="s">
         <v>105</v>
       </c>
@@ -8872,7 +9131,7 @@
       <c r="Q153" s="12"/>
     </row>
     <row r="154" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A154" s="138"/>
+      <c r="A154" s="136"/>
       <c r="B154" s="5" t="s">
         <v>105</v>
       </c>
@@ -8909,7 +9168,7 @@
       <c r="Q154" s="12"/>
     </row>
     <row r="155" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A155" s="130"/>
+      <c r="A155" s="128"/>
       <c r="B155" s="5" t="s">
         <v>105</v>
       </c>
@@ -8983,7 +9242,9 @@
       <c r="F157" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="G157" s="3"/>
+      <c r="G157" s="3" t="s">
+        <v>632</v>
+      </c>
       <c r="H157" s="3"/>
       <c r="I157" s="3"/>
       <c r="J157" s="5">
@@ -9004,7 +9265,7 @@
       <c r="Q157" s="12"/>
     </row>
     <row r="158" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A158" s="138"/>
+      <c r="A158" s="136"/>
       <c r="B158" s="5" t="s">
         <v>108</v>
       </c>
@@ -9041,7 +9302,7 @@
       <c r="Q158" s="12"/>
     </row>
     <row r="159" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A159" s="138"/>
+      <c r="A159" s="136"/>
       <c r="B159" s="5" t="s">
         <v>108</v>
       </c>
@@ -9078,7 +9339,7 @@
       <c r="Q159" s="12"/>
     </row>
     <row r="160" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A160" s="130"/>
+      <c r="A160" s="128"/>
       <c r="B160" s="5" t="s">
         <v>108</v>
       </c>
@@ -9173,7 +9434,7 @@
       <c r="Q162" s="12"/>
     </row>
     <row r="163" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A163" s="138"/>
+      <c r="A163" s="136"/>
       <c r="B163" s="5" t="s">
         <v>113</v>
       </c>
@@ -9210,7 +9471,7 @@
       <c r="Q163" s="12"/>
     </row>
     <row r="164" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A164" s="138"/>
+      <c r="A164" s="136"/>
       <c r="B164" s="5" t="s">
         <v>113</v>
       </c>
@@ -9247,7 +9508,7 @@
       <c r="Q164" s="12"/>
     </row>
     <row r="165" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A165" s="130"/>
+      <c r="A165" s="128"/>
       <c r="B165" s="5" t="s">
         <v>113</v>
       </c>
@@ -9335,7 +9596,7 @@
       <c r="N167" s="11"/>
     </row>
     <row r="168" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A168" s="138"/>
+      <c r="A168" s="136"/>
       <c r="B168" s="5" t="s">
         <v>116</v>
       </c>
@@ -9365,7 +9626,7 @@
       <c r="N168" s="11"/>
     </row>
     <row r="169" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A169" s="130"/>
+      <c r="A169" s="128"/>
       <c r="B169" s="5" t="s">
         <v>116</v>
       </c>
@@ -9443,7 +9704,7 @@
       <c r="N171" s="11"/>
     </row>
     <row r="172" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A172" s="138"/>
+      <c r="A172" s="136"/>
       <c r="B172" s="5" t="s">
         <v>120</v>
       </c>
@@ -9473,7 +9734,7 @@
       <c r="N172" s="11"/>
     </row>
     <row r="173" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A173" s="130"/>
+      <c r="A173" s="128"/>
       <c r="B173" s="5" t="s">
         <v>120</v>
       </c>
@@ -9553,7 +9814,7 @@
       <c r="N175" s="11"/>
     </row>
     <row r="176" spans="1:17" ht="18.75" hidden="1" customHeight="1">
-      <c r="A176" s="138"/>
+      <c r="A176" s="136"/>
       <c r="B176" s="5" t="s">
         <v>122</v>
       </c>
@@ -9585,7 +9846,7 @@
       <c r="N176" s="11"/>
     </row>
     <row r="177" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A177" s="138"/>
+      <c r="A177" s="136"/>
       <c r="B177" s="5" t="s">
         <v>122</v>
       </c>
@@ -9617,7 +9878,7 @@
       <c r="N177" s="11"/>
     </row>
     <row r="178" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A178" s="130"/>
+      <c r="A178" s="128"/>
       <c r="B178" s="5" t="s">
         <v>122</v>
       </c>
@@ -9699,7 +9960,7 @@
       <c r="N180" s="11"/>
     </row>
     <row r="181" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A181" s="138"/>
+      <c r="A181" s="136"/>
       <c r="B181" s="5" t="s">
         <v>125</v>
       </c>
@@ -9731,7 +9992,7 @@
       <c r="N181" s="11"/>
     </row>
     <row r="182" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A182" s="138"/>
+      <c r="A182" s="136"/>
       <c r="B182" s="5" t="s">
         <v>125</v>
       </c>
@@ -9763,7 +10024,7 @@
       <c r="N182" s="11"/>
     </row>
     <row r="183" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A183" s="130"/>
+      <c r="A183" s="128"/>
       <c r="B183" s="5" t="s">
         <v>125</v>
       </c>
@@ -9847,7 +10108,7 @@
       </c>
     </row>
     <row r="186" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A186" s="138"/>
+      <c r="A186" s="136"/>
       <c r="B186" s="5" t="s">
         <v>127</v>
       </c>
@@ -9881,7 +10142,7 @@
       </c>
     </row>
     <row r="187" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A187" s="138"/>
+      <c r="A187" s="136"/>
       <c r="B187" s="5" t="s">
         <v>127</v>
       </c>
@@ -9915,7 +10176,7 @@
       </c>
     </row>
     <row r="188" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A188" s="130"/>
+      <c r="A188" s="128"/>
       <c r="B188" s="5" t="s">
         <v>127</v>
       </c>
@@ -10001,7 +10262,7 @@
       </c>
     </row>
     <row r="191" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A191" s="138"/>
+      <c r="A191" s="136"/>
       <c r="B191" s="5" t="s">
         <v>130</v>
       </c>
@@ -10035,7 +10296,7 @@
       </c>
     </row>
     <row r="192" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A192" s="138"/>
+      <c r="A192" s="136"/>
       <c r="B192" s="5" t="s">
         <v>130</v>
       </c>
@@ -10069,7 +10330,7 @@
       </c>
     </row>
     <row r="193" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A193" s="130"/>
+      <c r="A193" s="128"/>
       <c r="B193" s="5" t="s">
         <v>130</v>
       </c>
@@ -10155,7 +10416,7 @@
       </c>
     </row>
     <row r="196" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A196" s="138"/>
+      <c r="A196" s="136"/>
       <c r="B196" s="5" t="s">
         <v>131</v>
       </c>
@@ -10189,7 +10450,7 @@
       </c>
     </row>
     <row r="197" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A197" s="138"/>
+      <c r="A197" s="136"/>
       <c r="B197" s="5" t="s">
         <v>131</v>
       </c>
@@ -10223,7 +10484,7 @@
       </c>
     </row>
     <row r="198" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A198" s="130"/>
+      <c r="A198" s="128"/>
       <c r="B198" s="5" t="s">
         <v>131</v>
       </c>
@@ -10309,7 +10570,7 @@
       </c>
     </row>
     <row r="201" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A201" s="138"/>
+      <c r="A201" s="136"/>
       <c r="B201" s="5" t="s">
         <v>134</v>
       </c>
@@ -10343,7 +10604,7 @@
       </c>
     </row>
     <row r="202" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A202" s="138"/>
+      <c r="A202" s="136"/>
       <c r="B202" s="5" t="s">
         <v>134</v>
       </c>
@@ -10377,7 +10638,7 @@
       </c>
     </row>
     <row r="203" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A203" s="130"/>
+      <c r="A203" s="128"/>
       <c r="B203" s="5" t="s">
         <v>134</v>
       </c>
@@ -10463,7 +10724,7 @@
       </c>
     </row>
     <row r="206" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A206" s="138"/>
+      <c r="A206" s="136"/>
       <c r="B206" s="19" t="s">
         <v>136</v>
       </c>
@@ -10497,7 +10758,7 @@
       </c>
     </row>
     <row r="207" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A207" s="138"/>
+      <c r="A207" s="136"/>
       <c r="B207" s="19" t="s">
         <v>136</v>
       </c>
@@ -10531,7 +10792,7 @@
       </c>
     </row>
     <row r="208" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A208" s="130"/>
+      <c r="A208" s="128"/>
       <c r="B208" s="19" t="s">
         <v>136</v>
       </c>
@@ -10617,7 +10878,7 @@
       </c>
     </row>
     <row r="211" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A211" s="138"/>
+      <c r="A211" s="136"/>
       <c r="B211" s="19" t="s">
         <v>139</v>
       </c>
@@ -10651,7 +10912,7 @@
       </c>
     </row>
     <row r="212" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A212" s="138"/>
+      <c r="A212" s="136"/>
       <c r="B212" s="19" t="s">
         <v>139</v>
       </c>
@@ -10685,7 +10946,7 @@
       </c>
     </row>
     <row r="213" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A213" s="130"/>
+      <c r="A213" s="128"/>
       <c r="B213" s="19" t="s">
         <v>139</v>
       </c>
@@ -10771,7 +11032,7 @@
       </c>
     </row>
     <row r="216" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A216" s="138"/>
+      <c r="A216" s="136"/>
       <c r="B216" s="19" t="s">
         <v>141</v>
       </c>
@@ -10805,7 +11066,7 @@
       </c>
     </row>
     <row r="217" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A217" s="138"/>
+      <c r="A217" s="136"/>
       <c r="B217" s="19" t="s">
         <v>141</v>
       </c>
@@ -10839,7 +11100,7 @@
       </c>
     </row>
     <row r="218" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A218" s="130"/>
+      <c r="A218" s="128"/>
       <c r="B218" s="19" t="s">
         <v>141</v>
       </c>
@@ -10925,7 +11186,7 @@
       </c>
     </row>
     <row r="221" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A221" s="138"/>
+      <c r="A221" s="136"/>
       <c r="B221" s="19" t="s">
         <v>143</v>
       </c>
@@ -10959,7 +11220,7 @@
       </c>
     </row>
     <row r="222" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A222" s="138"/>
+      <c r="A222" s="136"/>
       <c r="B222" s="19" t="s">
         <v>143</v>
       </c>
@@ -10993,7 +11254,7 @@
       </c>
     </row>
     <row r="223" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A223" s="130"/>
+      <c r="A223" s="128"/>
       <c r="B223" s="19" t="s">
         <v>143</v>
       </c>
@@ -11079,7 +11340,7 @@
       </c>
     </row>
     <row r="226" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A226" s="138"/>
+      <c r="A226" s="136"/>
       <c r="B226" s="19" t="s">
         <v>145</v>
       </c>
@@ -11113,7 +11374,7 @@
       </c>
     </row>
     <row r="227" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A227" s="138"/>
+      <c r="A227" s="136"/>
       <c r="B227" s="19" t="s">
         <v>145</v>
       </c>
@@ -11147,7 +11408,7 @@
       </c>
     </row>
     <row r="228" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A228" s="130"/>
+      <c r="A228" s="128"/>
       <c r="B228" s="19" t="s">
         <v>145</v>
       </c>
@@ -11233,7 +11494,7 @@
       </c>
     </row>
     <row r="231" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A231" s="138"/>
+      <c r="A231" s="136"/>
       <c r="B231" s="5" t="s">
         <v>147</v>
       </c>
@@ -11267,7 +11528,7 @@
       </c>
     </row>
     <row r="232" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A232" s="138"/>
+      <c r="A232" s="136"/>
       <c r="B232" s="5" t="s">
         <v>147</v>
       </c>
@@ -11301,7 +11562,7 @@
       </c>
     </row>
     <row r="233" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A233" s="130"/>
+      <c r="A233" s="128"/>
       <c r="B233" s="5" t="s">
         <v>147</v>
       </c>
@@ -11385,7 +11646,7 @@
       <c r="N235" s="11"/>
     </row>
     <row r="236" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A236" s="138"/>
+      <c r="A236" s="136"/>
       <c r="B236" s="19" t="s">
         <v>150</v>
       </c>
@@ -11417,7 +11678,7 @@
       <c r="N236" s="25"/>
     </row>
     <row r="237" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A237" s="138"/>
+      <c r="A237" s="136"/>
       <c r="B237" s="19" t="s">
         <v>150</v>
       </c>
@@ -11449,7 +11710,7 @@
       <c r="N237" s="25"/>
     </row>
     <row r="238" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A238" s="130"/>
+      <c r="A238" s="128"/>
       <c r="B238" s="19" t="s">
         <v>150</v>
       </c>
@@ -11531,7 +11792,7 @@
       <c r="N240" s="11"/>
     </row>
     <row r="241" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A241" s="138"/>
+      <c r="A241" s="136"/>
       <c r="B241" s="19" t="s">
         <v>153</v>
       </c>
@@ -11563,7 +11824,7 @@
       <c r="N241" s="25"/>
     </row>
     <row r="242" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A242" s="138"/>
+      <c r="A242" s="136"/>
       <c r="B242" s="19" t="s">
         <v>153</v>
       </c>
@@ -11595,7 +11856,7 @@
       <c r="N242" s="25"/>
     </row>
     <row r="243" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A243" s="130"/>
+      <c r="A243" s="128"/>
       <c r="B243" s="19" t="s">
         <v>153</v>
       </c>
@@ -11677,7 +11938,7 @@
       <c r="N245" s="11"/>
     </row>
     <row r="246" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A246" s="138"/>
+      <c r="A246" s="136"/>
       <c r="B246" s="19" t="s">
         <v>154</v>
       </c>
@@ -11709,7 +11970,7 @@
       <c r="N246" s="25"/>
     </row>
     <row r="247" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A247" s="138"/>
+      <c r="A247" s="136"/>
       <c r="B247" s="19" t="s">
         <v>154</v>
       </c>
@@ -11741,7 +12002,7 @@
       <c r="N247" s="25"/>
     </row>
     <row r="248" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A248" s="130"/>
+      <c r="A248" s="128"/>
       <c r="B248" s="19" t="s">
         <v>154</v>
       </c>
@@ -11819,7 +12080,7 @@
       <c r="N250" s="11"/>
     </row>
     <row r="251" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A251" s="138"/>
+      <c r="A251" s="136"/>
       <c r="B251" s="5"/>
       <c r="C251" s="5" t="s">
         <v>18</v>
@@ -11847,7 +12108,7 @@
       <c r="N251" s="11"/>
     </row>
     <row r="252" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A252" s="138"/>
+      <c r="A252" s="136"/>
       <c r="B252" s="5"/>
       <c r="C252" s="5" t="s">
         <v>20</v>
@@ -11875,7 +12136,7 @@
       <c r="N252" s="11"/>
     </row>
     <row r="253" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A253" s="130"/>
+      <c r="A253" s="128"/>
       <c r="B253" s="5"/>
       <c r="C253" s="5" t="s">
         <v>22</v>
@@ -11949,7 +12210,7 @@
       <c r="N255" s="11"/>
     </row>
     <row r="256" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A256" s="138"/>
+      <c r="A256" s="136"/>
       <c r="B256" s="5"/>
       <c r="C256" s="5" t="s">
         <v>18</v>
@@ -11977,7 +12238,7 @@
       <c r="N256" s="11"/>
     </row>
     <row r="257" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A257" s="138"/>
+      <c r="A257" s="136"/>
       <c r="B257" s="5"/>
       <c r="C257" s="5" t="s">
         <v>20</v>
@@ -12005,7 +12266,7 @@
       <c r="N257" s="11"/>
     </row>
     <row r="258" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A258" s="130"/>
+      <c r="A258" s="128"/>
       <c r="B258" s="5"/>
       <c r="C258" s="5" t="s">
         <v>22</v>
@@ -12079,7 +12340,7 @@
       <c r="N260" s="11"/>
     </row>
     <row r="261" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A261" s="138"/>
+      <c r="A261" s="136"/>
       <c r="B261" s="5"/>
       <c r="C261" s="5" t="s">
         <v>18</v>
@@ -12107,7 +12368,7 @@
       <c r="N261" s="11"/>
     </row>
     <row r="262" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A262" s="138"/>
+      <c r="A262" s="136"/>
       <c r="B262" s="5"/>
       <c r="C262" s="5" t="s">
         <v>20</v>
@@ -12135,7 +12396,7 @@
       <c r="N262" s="11"/>
     </row>
     <row r="263" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A263" s="130"/>
+      <c r="A263" s="128"/>
       <c r="B263" s="5"/>
       <c r="C263" s="5" t="s">
         <v>22</v>
@@ -12209,7 +12470,7 @@
       <c r="N265" s="11"/>
     </row>
     <row r="266" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A266" s="138"/>
+      <c r="A266" s="136"/>
       <c r="B266" s="5"/>
       <c r="C266" s="5" t="s">
         <v>18</v>
@@ -12237,7 +12498,7 @@
       <c r="N266" s="11"/>
     </row>
     <row r="267" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A267" s="138"/>
+      <c r="A267" s="136"/>
       <c r="B267" s="5"/>
       <c r="C267" s="5" t="s">
         <v>20</v>
@@ -12265,7 +12526,7 @@
       <c r="N267" s="11"/>
     </row>
     <row r="268" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A268" s="130"/>
+      <c r="A268" s="128"/>
       <c r="B268" s="5"/>
       <c r="C268" s="5" t="s">
         <v>22</v>
@@ -12339,7 +12600,7 @@
       <c r="N270" s="11"/>
     </row>
     <row r="271" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A271" s="138"/>
+      <c r="A271" s="136"/>
       <c r="B271" s="5"/>
       <c r="C271" s="5" t="s">
         <v>18</v>
@@ -12367,7 +12628,7 @@
       <c r="N271" s="11"/>
     </row>
     <row r="272" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A272" s="138"/>
+      <c r="A272" s="136"/>
       <c r="B272" s="5"/>
       <c r="C272" s="5" t="s">
         <v>20</v>
@@ -12395,7 +12656,7 @@
       <c r="N272" s="11"/>
     </row>
     <row r="273" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A273" s="130"/>
+      <c r="A273" s="128"/>
       <c r="B273" s="5"/>
       <c r="C273" s="5" t="s">
         <v>22</v>
@@ -12473,7 +12734,7 @@
       </c>
     </row>
     <row r="276" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A276" s="138"/>
+      <c r="A276" s="136"/>
       <c r="B276" s="5" t="s">
         <v>161</v>
       </c>
@@ -12505,7 +12766,7 @@
       </c>
     </row>
     <row r="277" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A277" s="138"/>
+      <c r="A277" s="136"/>
       <c r="B277" s="5" t="s">
         <v>161</v>
       </c>
@@ -12537,7 +12798,7 @@
       </c>
     </row>
     <row r="278" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A278" s="130"/>
+      <c r="A278" s="128"/>
       <c r="B278" s="26" t="s">
         <v>161</v>
       </c>
@@ -12651,7 +12912,7 @@
       <c r="N282" s="11"/>
     </row>
     <row r="283" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A283" s="138"/>
+      <c r="A283" s="136"/>
       <c r="B283" s="6" t="s">
         <v>164</v>
       </c>
@@ -12683,7 +12944,7 @@
       <c r="N283" s="11"/>
     </row>
     <row r="284" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A284" s="138"/>
+      <c r="A284" s="136"/>
       <c r="B284" s="6" t="s">
         <v>164</v>
       </c>
@@ -12715,7 +12976,7 @@
       <c r="N284" s="11"/>
     </row>
     <row r="285" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A285" s="130"/>
+      <c r="A285" s="128"/>
       <c r="B285" s="6" t="s">
         <v>164</v>
       </c>
@@ -12797,7 +13058,7 @@
       <c r="N287" s="34"/>
     </row>
     <row r="288" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A288" s="138"/>
+      <c r="A288" s="136"/>
       <c r="B288" s="17" t="s">
         <v>167</v>
       </c>
@@ -12829,7 +13090,7 @@
       <c r="N288" s="34"/>
     </row>
     <row r="289" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A289" s="138"/>
+      <c r="A289" s="136"/>
       <c r="B289" s="17" t="s">
         <v>167</v>
       </c>
@@ -12861,7 +13122,7 @@
       <c r="N289" s="34"/>
     </row>
     <row r="290" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A290" s="130"/>
+      <c r="A290" s="128"/>
       <c r="B290" s="17" t="s">
         <v>167</v>
       </c>
@@ -12943,7 +13204,7 @@
       <c r="N292" s="11"/>
     </row>
     <row r="293" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A293" s="138"/>
+      <c r="A293" s="136"/>
       <c r="B293" s="17" t="s">
         <v>170</v>
       </c>
@@ -12975,7 +13236,7 @@
       <c r="N293" s="11"/>
     </row>
     <row r="294" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A294" s="138"/>
+      <c r="A294" s="136"/>
       <c r="B294" s="17" t="s">
         <v>170</v>
       </c>
@@ -13007,7 +13268,7 @@
       <c r="N294" s="11"/>
     </row>
     <row r="295" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A295" s="130"/>
+      <c r="A295" s="128"/>
       <c r="B295" s="17" t="s">
         <v>170</v>
       </c>
@@ -13089,7 +13350,7 @@
       <c r="N297" s="11"/>
     </row>
     <row r="298" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A298" s="138"/>
+      <c r="A298" s="136"/>
       <c r="B298" s="35">
         <v>13</v>
       </c>
@@ -13121,7 +13382,7 @@
       <c r="N298" s="11"/>
     </row>
     <row r="299" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A299" s="138"/>
+      <c r="A299" s="136"/>
       <c r="B299" s="35">
         <v>13</v>
       </c>
@@ -13153,7 +13414,7 @@
       <c r="N299" s="11"/>
     </row>
     <row r="300" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A300" s="130"/>
+      <c r="A300" s="128"/>
       <c r="B300" s="35">
         <v>13</v>
       </c>
@@ -13381,7 +13642,7 @@
       <c r="N307" s="11"/>
     </row>
     <row r="308" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A308" s="138"/>
+      <c r="A308" s="136"/>
       <c r="B308" s="41" t="s">
         <v>179</v>
       </c>
@@ -13413,7 +13674,7 @@
       <c r="N308" s="11"/>
     </row>
     <row r="309" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A309" s="138"/>
+      <c r="A309" s="136"/>
       <c r="B309" s="41" t="s">
         <v>179</v>
       </c>
@@ -13445,7 +13706,7 @@
       <c r="N309" s="11"/>
     </row>
     <row r="310" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A310" s="130"/>
+      <c r="A310" s="128"/>
       <c r="B310" s="41" t="s">
         <v>179</v>
       </c>
@@ -13527,7 +13788,7 @@
       <c r="N312" s="11"/>
     </row>
     <row r="313" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A313" s="138"/>
+      <c r="A313" s="136"/>
       <c r="B313" s="47" t="s">
         <v>182</v>
       </c>
@@ -13559,7 +13820,7 @@
       <c r="N313" s="11"/>
     </row>
     <row r="314" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A314" s="138"/>
+      <c r="A314" s="136"/>
       <c r="B314" s="47" t="s">
         <v>182</v>
       </c>
@@ -13591,7 +13852,7 @@
       <c r="N314" s="11"/>
     </row>
     <row r="315" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A315" s="130"/>
+      <c r="A315" s="128"/>
       <c r="B315" s="47" t="s">
         <v>182</v>
       </c>
@@ -13673,7 +13934,7 @@
       <c r="N317" s="11"/>
     </row>
     <row r="318" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A318" s="138"/>
+      <c r="A318" s="136"/>
       <c r="B318" s="47" t="s">
         <v>185</v>
       </c>
@@ -13705,7 +13966,7 @@
       <c r="N318" s="11"/>
     </row>
     <row r="319" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A319" s="138"/>
+      <c r="A319" s="136"/>
       <c r="B319" s="47" t="s">
         <v>185</v>
       </c>
@@ -13737,7 +13998,7 @@
       <c r="N319" s="11"/>
     </row>
     <row r="320" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A320" s="130"/>
+      <c r="A320" s="128"/>
       <c r="B320" s="47" t="s">
         <v>185</v>
       </c>
@@ -13819,7 +14080,7 @@
       <c r="N322" s="11"/>
     </row>
     <row r="323" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A323" s="138"/>
+      <c r="A323" s="136"/>
       <c r="B323" s="47" t="s">
         <v>187</v>
       </c>
@@ -13851,7 +14112,7 @@
       <c r="N323" s="11"/>
     </row>
     <row r="324" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A324" s="138"/>
+      <c r="A324" s="136"/>
       <c r="B324" s="47" t="s">
         <v>187</v>
       </c>
@@ -13883,7 +14144,7 @@
       <c r="N324" s="11"/>
     </row>
     <row r="325" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A325" s="130"/>
+      <c r="A325" s="128"/>
       <c r="B325" s="47" t="s">
         <v>187</v>
       </c>
@@ -13940,7 +14201,7 @@
       <c r="C327" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D327" s="148" t="s">
+      <c r="D327" s="146" t="s">
         <v>190</v>
       </c>
       <c r="E327" s="48" t="s">
@@ -13949,7 +14210,9 @@
       <c r="F327" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="G327" s="49"/>
+      <c r="G327" s="49" t="s">
+        <v>632</v>
+      </c>
       <c r="H327" s="50"/>
       <c r="I327" s="50"/>
       <c r="J327" s="5">
@@ -13965,7 +14228,7 @@
       <c r="N327" s="11"/>
     </row>
     <row r="328" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A328" s="138"/>
+      <c r="A328" s="136"/>
       <c r="B328" s="47" t="s">
         <v>189</v>
       </c>
@@ -13997,7 +14260,7 @@
       <c r="N328" s="11"/>
     </row>
     <row r="329" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A329" s="138"/>
+      <c r="A329" s="136"/>
       <c r="B329" s="47" t="s">
         <v>189</v>
       </c>
@@ -14029,7 +14292,7 @@
       <c r="N329" s="11"/>
     </row>
     <row r="330" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A330" s="130"/>
+      <c r="A330" s="128"/>
       <c r="B330" s="47" t="s">
         <v>189</v>
       </c>
@@ -14111,7 +14374,7 @@
       <c r="N332" s="11"/>
     </row>
     <row r="333" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A333" s="138"/>
+      <c r="A333" s="136"/>
       <c r="B333" s="47" t="s">
         <v>192</v>
       </c>
@@ -14143,7 +14406,7 @@
       <c r="N333" s="11"/>
     </row>
     <row r="334" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A334" s="138"/>
+      <c r="A334" s="136"/>
       <c r="B334" s="47" t="s">
         <v>192</v>
       </c>
@@ -14175,7 +14438,7 @@
       <c r="N334" s="11"/>
     </row>
     <row r="335" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A335" s="130"/>
+      <c r="A335" s="128"/>
       <c r="B335" s="47" t="s">
         <v>192</v>
       </c>
@@ -14257,7 +14520,7 @@
       <c r="N337" s="11"/>
     </row>
     <row r="338" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A338" s="138"/>
+      <c r="A338" s="136"/>
       <c r="B338" s="47" t="s">
         <v>195</v>
       </c>
@@ -14289,7 +14552,7 @@
       <c r="N338" s="11"/>
     </row>
     <row r="339" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A339" s="138"/>
+      <c r="A339" s="136"/>
       <c r="B339" s="47" t="s">
         <v>195</v>
       </c>
@@ -14321,7 +14584,7 @@
       <c r="N339" s="11"/>
     </row>
     <row r="340" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A340" s="130"/>
+      <c r="A340" s="128"/>
       <c r="B340" s="47" t="s">
         <v>195</v>
       </c>
@@ -14378,7 +14641,7 @@
       <c r="C342" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D342" s="148" t="s">
+      <c r="D342" s="146" t="s">
         <v>198</v>
       </c>
       <c r="E342" s="48" t="s">
@@ -14387,7 +14650,9 @@
       <c r="F342" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="G342" s="49"/>
+      <c r="G342" s="49" t="s">
+        <v>632</v>
+      </c>
       <c r="H342" s="50"/>
       <c r="I342" s="50"/>
       <c r="J342" s="5">
@@ -14403,7 +14668,7 @@
       <c r="N342" s="11"/>
     </row>
     <row r="343" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A343" s="138"/>
+      <c r="A343" s="136"/>
       <c r="B343" s="47" t="s">
         <v>197</v>
       </c>
@@ -14435,7 +14700,7 @@
       <c r="N343" s="11"/>
     </row>
     <row r="344" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A344" s="138"/>
+      <c r="A344" s="136"/>
       <c r="B344" s="47" t="s">
         <v>197</v>
       </c>
@@ -14467,7 +14732,7 @@
       <c r="N344" s="11"/>
     </row>
     <row r="345" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A345" s="130"/>
+      <c r="A345" s="128"/>
       <c r="B345" s="47" t="s">
         <v>197</v>
       </c>
@@ -14524,7 +14789,7 @@
       <c r="C347" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D347" s="148" t="s">
+      <c r="D347" s="146" t="s">
         <v>198</v>
       </c>
       <c r="E347" s="48" t="s">
@@ -14533,7 +14798,9 @@
       <c r="F347" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="G347" s="49"/>
+      <c r="G347" s="49" t="s">
+        <v>632</v>
+      </c>
       <c r="H347" s="50"/>
       <c r="I347" s="50"/>
       <c r="J347" s="5">
@@ -14549,7 +14816,7 @@
       <c r="N347" s="11"/>
     </row>
     <row r="348" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A348" s="138"/>
+      <c r="A348" s="136"/>
       <c r="B348" s="47" t="s">
         <v>200</v>
       </c>
@@ -14581,7 +14848,7 @@
       <c r="N348" s="11"/>
     </row>
     <row r="349" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A349" s="138"/>
+      <c r="A349" s="136"/>
       <c r="B349" s="47" t="s">
         <v>200</v>
       </c>
@@ -14613,7 +14880,7 @@
       <c r="N349" s="11"/>
     </row>
     <row r="350" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A350" s="130"/>
+      <c r="A350" s="128"/>
       <c r="B350" s="47" t="s">
         <v>200</v>
       </c>
@@ -14670,7 +14937,7 @@
       <c r="C352" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D352" s="148" t="s">
+      <c r="D352" s="146" t="s">
         <v>198</v>
       </c>
       <c r="E352" s="48" t="s">
@@ -14679,7 +14946,9 @@
       <c r="F352" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="G352" s="49"/>
+      <c r="G352" s="49" t="s">
+        <v>632</v>
+      </c>
       <c r="H352" s="50"/>
       <c r="I352" s="50"/>
       <c r="J352" s="5">
@@ -14695,7 +14964,7 @@
       <c r="N352" s="11"/>
     </row>
     <row r="353" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A353" s="138"/>
+      <c r="A353" s="136"/>
       <c r="B353" s="47" t="s">
         <v>201</v>
       </c>
@@ -14727,7 +14996,7 @@
       <c r="N353" s="11"/>
     </row>
     <row r="354" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A354" s="138"/>
+      <c r="A354" s="136"/>
       <c r="B354" s="47" t="s">
         <v>201</v>
       </c>
@@ -14759,7 +15028,7 @@
       <c r="N354" s="11"/>
     </row>
     <row r="355" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A355" s="130"/>
+      <c r="A355" s="128"/>
       <c r="B355" s="47" t="s">
         <v>201</v>
       </c>
@@ -14807,7 +15076,7 @@
       <c r="N356" s="11"/>
     </row>
     <row r="357" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A357" s="137">
+      <c r="A357" s="135">
         <v>77</v>
       </c>
       <c r="B357" s="52" t="s">
@@ -14853,7 +15122,7 @@
       <c r="Z357" s="56"/>
     </row>
     <row r="358" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A358" s="138"/>
+      <c r="A358" s="136"/>
       <c r="B358" s="52" t="s">
         <v>202</v>
       </c>
@@ -14897,7 +15166,7 @@
       <c r="Z358" s="56"/>
     </row>
     <row r="359" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A359" s="138"/>
+      <c r="A359" s="136"/>
       <c r="B359" s="52" t="s">
         <v>202</v>
       </c>
@@ -14941,7 +15210,7 @@
       <c r="Z359" s="56"/>
     </row>
     <row r="360" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A360" s="130"/>
+      <c r="A360" s="128"/>
       <c r="B360" s="52" t="s">
         <v>202</v>
       </c>
@@ -15013,7 +15282,7 @@
       <c r="Z361" s="56"/>
     </row>
     <row r="362" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A362" s="137">
+      <c r="A362" s="135">
         <v>78</v>
       </c>
       <c r="B362" s="52" t="s">
@@ -15059,7 +15328,7 @@
       <c r="Z362" s="56"/>
     </row>
     <row r="363" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A363" s="138"/>
+      <c r="A363" s="136"/>
       <c r="B363" s="52" t="s">
         <v>204</v>
       </c>
@@ -15103,7 +15372,7 @@
       <c r="Z363" s="56"/>
     </row>
     <row r="364" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A364" s="138"/>
+      <c r="A364" s="136"/>
       <c r="B364" s="52" t="s">
         <v>204</v>
       </c>
@@ -15147,7 +15416,7 @@
       <c r="Z364" s="56"/>
     </row>
     <row r="365" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A365" s="130"/>
+      <c r="A365" s="128"/>
       <c r="B365" s="52" t="s">
         <v>204</v>
       </c>
@@ -15219,7 +15488,7 @@
       <c r="Z366" s="56"/>
     </row>
     <row r="367" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A367" s="137">
+      <c r="A367" s="135">
         <v>79</v>
       </c>
       <c r="B367" s="52" t="s">
@@ -15265,7 +15534,7 @@
       <c r="Z367" s="56"/>
     </row>
     <row r="368" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A368" s="138"/>
+      <c r="A368" s="136"/>
       <c r="B368" s="52" t="s">
         <v>205</v>
       </c>
@@ -15309,7 +15578,7 @@
       <c r="Z368" s="56"/>
     </row>
     <row r="369" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A369" s="138"/>
+      <c r="A369" s="136"/>
       <c r="B369" s="52" t="s">
         <v>205</v>
       </c>
@@ -15353,7 +15622,7 @@
       <c r="Z369" s="56"/>
     </row>
     <row r="370" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A370" s="130"/>
+      <c r="A370" s="128"/>
       <c r="B370" s="52" t="s">
         <v>205</v>
       </c>
@@ -15422,7 +15691,7 @@
       <c r="C372" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D372" s="148" t="s">
+      <c r="D372" s="146" t="s">
         <v>207</v>
       </c>
       <c r="E372" s="48" t="s">
@@ -15431,7 +15700,9 @@
       <c r="F372" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="G372" s="49"/>
+      <c r="G372" s="49" t="s">
+        <v>632</v>
+      </c>
       <c r="H372" s="50"/>
       <c r="I372" s="50"/>
       <c r="J372" s="5">
@@ -15447,7 +15718,7 @@
       <c r="N372" s="11"/>
     </row>
     <row r="373" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A373" s="138"/>
+      <c r="A373" s="136"/>
       <c r="B373" s="47" t="s">
         <v>206</v>
       </c>
@@ -15479,7 +15750,7 @@
       <c r="N373" s="11"/>
     </row>
     <row r="374" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A374" s="138"/>
+      <c r="A374" s="136"/>
       <c r="B374" s="47" t="s">
         <v>206</v>
       </c>
@@ -15511,7 +15782,7 @@
       <c r="N374" s="11"/>
     </row>
     <row r="375" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A375" s="130"/>
+      <c r="A375" s="128"/>
       <c r="B375" s="47" t="s">
         <v>206</v>
       </c>
@@ -15568,7 +15839,7 @@
       <c r="C377" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D377" s="148" t="s">
+      <c r="D377" s="146" t="s">
         <v>210</v>
       </c>
       <c r="E377" s="48" t="s">
@@ -15577,7 +15848,9 @@
       <c r="F377" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="G377" s="49"/>
+      <c r="G377" s="49" t="s">
+        <v>632</v>
+      </c>
       <c r="H377" s="50"/>
       <c r="I377" s="50"/>
       <c r="J377" s="5">
@@ -15593,7 +15866,7 @@
       <c r="N377" s="11"/>
     </row>
     <row r="378" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A378" s="138"/>
+      <c r="A378" s="136"/>
       <c r="B378" s="47" t="s">
         <v>209</v>
       </c>
@@ -15625,7 +15898,7 @@
       <c r="N378" s="11"/>
     </row>
     <row r="379" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A379" s="138"/>
+      <c r="A379" s="136"/>
       <c r="B379" s="47" t="s">
         <v>209</v>
       </c>
@@ -15657,7 +15930,7 @@
       <c r="N379" s="11"/>
     </row>
     <row r="380" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A380" s="130"/>
+      <c r="A380" s="128"/>
       <c r="B380" s="47" t="s">
         <v>209</v>
       </c>
@@ -15723,7 +15996,9 @@
       <c r="F382" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="G382" s="43"/>
+      <c r="G382" s="43" t="s">
+        <v>632</v>
+      </c>
       <c r="H382" s="44"/>
       <c r="I382" s="44"/>
       <c r="J382" s="5">
@@ -15739,7 +16014,7 @@
       <c r="N382" s="11"/>
     </row>
     <row r="383" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A383" s="138"/>
+      <c r="A383" s="136"/>
       <c r="B383" s="41" t="s">
         <v>211</v>
       </c>
@@ -15771,7 +16046,7 @@
       <c r="N383" s="11"/>
     </row>
     <row r="384" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A384" s="138"/>
+      <c r="A384" s="136"/>
       <c r="B384" s="41" t="s">
         <v>211</v>
       </c>
@@ -15803,7 +16078,7 @@
       <c r="N384" s="11"/>
     </row>
     <row r="385" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A385" s="130"/>
+      <c r="A385" s="128"/>
       <c r="B385" s="41" t="s">
         <v>211</v>
       </c>
@@ -15869,7 +16144,9 @@
       <c r="F387" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="G387" s="49"/>
+      <c r="G387" s="49" t="s">
+        <v>632</v>
+      </c>
       <c r="H387" s="50"/>
       <c r="I387" s="50"/>
       <c r="J387" s="5">
@@ -15885,7 +16162,7 @@
       <c r="N387" s="11"/>
     </row>
     <row r="388" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A388" s="138"/>
+      <c r="A388" s="136"/>
       <c r="B388" s="47" t="s">
         <v>213</v>
       </c>
@@ -15917,7 +16194,7 @@
       <c r="N388" s="11"/>
     </row>
     <row r="389" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A389" s="138"/>
+      <c r="A389" s="136"/>
       <c r="B389" s="47" t="s">
         <v>213</v>
       </c>
@@ -15949,7 +16226,7 @@
       <c r="N389" s="11"/>
     </row>
     <row r="390" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A390" s="130"/>
+      <c r="A390" s="128"/>
       <c r="B390" s="47" t="s">
         <v>213</v>
       </c>
@@ -16015,7 +16292,9 @@
       <c r="F392" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="G392" s="49"/>
+      <c r="G392" s="49" t="s">
+        <v>632</v>
+      </c>
       <c r="H392" s="50"/>
       <c r="I392" s="50"/>
       <c r="J392" s="5">
@@ -16031,7 +16310,7 @@
       <c r="N392" s="11"/>
     </row>
     <row r="393" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A393" s="138"/>
+      <c r="A393" s="136"/>
       <c r="B393" s="47" t="s">
         <v>215</v>
       </c>
@@ -16063,7 +16342,7 @@
       <c r="N393" s="11"/>
     </row>
     <row r="394" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A394" s="138"/>
+      <c r="A394" s="136"/>
       <c r="B394" s="47" t="s">
         <v>215</v>
       </c>
@@ -16095,7 +16374,7 @@
       <c r="N394" s="11"/>
     </row>
     <row r="395" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A395" s="130"/>
+      <c r="A395" s="128"/>
       <c r="B395" s="47" t="s">
         <v>215</v>
       </c>
@@ -16161,7 +16440,9 @@
       <c r="F397" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="G397" s="49"/>
+      <c r="G397" s="49" t="s">
+        <v>632</v>
+      </c>
       <c r="H397" s="50"/>
       <c r="I397" s="50"/>
       <c r="J397" s="5">
@@ -16177,7 +16458,7 @@
       <c r="N397" s="11"/>
     </row>
     <row r="398" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A398" s="138"/>
+      <c r="A398" s="136"/>
       <c r="B398" s="47" t="s">
         <v>217</v>
       </c>
@@ -16209,7 +16490,7 @@
       <c r="N398" s="11"/>
     </row>
     <row r="399" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A399" s="138"/>
+      <c r="A399" s="136"/>
       <c r="B399" s="47" t="s">
         <v>217</v>
       </c>
@@ -16241,7 +16522,7 @@
       <c r="N399" s="11"/>
     </row>
     <row r="400" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A400" s="130"/>
+      <c r="A400" s="128"/>
       <c r="B400" s="47" t="s">
         <v>217</v>
       </c>
@@ -16307,7 +16588,9 @@
       <c r="F402" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="G402" s="49"/>
+      <c r="G402" s="49" t="s">
+        <v>632</v>
+      </c>
       <c r="H402" s="50"/>
       <c r="I402" s="50"/>
       <c r="J402" s="5">
@@ -16323,7 +16606,7 @@
       <c r="N402" s="11"/>
     </row>
     <row r="403" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A403" s="138"/>
+      <c r="A403" s="136"/>
       <c r="B403" s="47" t="s">
         <v>219</v>
       </c>
@@ -16355,7 +16638,7 @@
       <c r="N403" s="11"/>
     </row>
     <row r="404" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A404" s="138"/>
+      <c r="A404" s="136"/>
       <c r="B404" s="47" t="s">
         <v>219</v>
       </c>
@@ -16387,7 +16670,7 @@
       <c r="N404" s="11"/>
     </row>
     <row r="405" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A405" s="130"/>
+      <c r="A405" s="128"/>
       <c r="B405" s="47" t="s">
         <v>219</v>
       </c>
@@ -16453,7 +16736,9 @@
       <c r="F407" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="G407" s="49"/>
+      <c r="G407" s="49" t="s">
+        <v>632</v>
+      </c>
       <c r="H407" s="50"/>
       <c r="I407" s="50"/>
       <c r="J407" s="5">
@@ -16469,7 +16754,7 @@
       <c r="N407" s="11"/>
     </row>
     <row r="408" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A408" s="138"/>
+      <c r="A408" s="136"/>
       <c r="B408" s="47" t="s">
         <v>221</v>
       </c>
@@ -16501,7 +16786,7 @@
       <c r="N408" s="11"/>
     </row>
     <row r="409" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A409" s="138"/>
+      <c r="A409" s="136"/>
       <c r="B409" s="47" t="s">
         <v>221</v>
       </c>
@@ -16533,7 +16818,7 @@
       <c r="N409" s="11"/>
     </row>
     <row r="410" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A410" s="130"/>
+      <c r="A410" s="128"/>
       <c r="B410" s="47" t="s">
         <v>221</v>
       </c>
@@ -16599,7 +16884,9 @@
       <c r="F412" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="G412" s="49"/>
+      <c r="G412" s="49" t="s">
+        <v>632</v>
+      </c>
       <c r="H412" s="50"/>
       <c r="I412" s="50"/>
       <c r="J412" s="5">
@@ -16615,7 +16902,7 @@
       <c r="N412" s="11"/>
     </row>
     <row r="413" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A413" s="138"/>
+      <c r="A413" s="136"/>
       <c r="B413" s="47" t="s">
         <v>223</v>
       </c>
@@ -16647,7 +16934,7 @@
       <c r="N413" s="11"/>
     </row>
     <row r="414" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A414" s="138"/>
+      <c r="A414" s="136"/>
       <c r="B414" s="47" t="s">
         <v>223</v>
       </c>
@@ -16679,7 +16966,7 @@
       <c r="N414" s="11"/>
     </row>
     <row r="415" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A415" s="130"/>
+      <c r="A415" s="128"/>
       <c r="B415" s="47" t="s">
         <v>223</v>
       </c>
@@ -16736,7 +17023,7 @@
       <c r="C417" s="122" t="s">
         <v>12</v>
       </c>
-      <c r="D417" s="148" t="s">
+      <c r="D417" s="146" t="s">
         <v>226</v>
       </c>
       <c r="E417" s="124" t="s">
@@ -16746,7 +17033,9 @@
         <v>111</v>
       </c>
       <c r="G417" s="49"/>
-      <c r="H417" s="50"/>
+      <c r="H417" s="50" t="s">
+        <v>632</v>
+      </c>
       <c r="I417" s="50"/>
       <c r="J417" s="5">
         <v>0.5</v>
@@ -16761,7 +17050,7 @@
       <c r="N417" s="11"/>
     </row>
     <row r="418" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A418" s="138"/>
+      <c r="A418" s="136"/>
       <c r="B418" s="47" t="s">
         <v>225</v>
       </c>
@@ -16793,7 +17082,7 @@
       <c r="N418" s="11"/>
     </row>
     <row r="419" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A419" s="138"/>
+      <c r="A419" s="136"/>
       <c r="B419" s="47" t="s">
         <v>225</v>
       </c>
@@ -16825,7 +17114,7 @@
       <c r="N419" s="11"/>
     </row>
     <row r="420" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A420" s="130"/>
+      <c r="A420" s="128"/>
       <c r="B420" s="47" t="s">
         <v>225</v>
       </c>
@@ -16882,7 +17171,7 @@
       <c r="C422" s="122" t="s">
         <v>12</v>
       </c>
-      <c r="D422" s="148" t="s">
+      <c r="D422" s="146" t="s">
         <v>229</v>
       </c>
       <c r="E422" s="124" t="s">
@@ -16892,7 +17181,9 @@
         <v>111</v>
       </c>
       <c r="G422" s="49"/>
-      <c r="H422" s="50"/>
+      <c r="H422" s="50" t="s">
+        <v>632</v>
+      </c>
       <c r="I422" s="50"/>
       <c r="J422" s="5">
         <v>0.5</v>
@@ -16907,7 +17198,7 @@
       <c r="N422" s="11"/>
     </row>
     <row r="423" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A423" s="138"/>
+      <c r="A423" s="136"/>
       <c r="B423" s="47" t="s">
         <v>228</v>
       </c>
@@ -16939,7 +17230,7 @@
       <c r="N423" s="11"/>
     </row>
     <row r="424" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A424" s="138"/>
+      <c r="A424" s="136"/>
       <c r="B424" s="47" t="s">
         <v>228</v>
       </c>
@@ -16971,7 +17262,7 @@
       <c r="N424" s="11"/>
     </row>
     <row r="425" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A425" s="130"/>
+      <c r="A425" s="128"/>
       <c r="B425" s="47" t="s">
         <v>228</v>
       </c>
@@ -17028,7 +17319,7 @@
       <c r="C427" s="122" t="s">
         <v>12</v>
       </c>
-      <c r="D427" s="148" t="s">
+      <c r="D427" s="146" t="s">
         <v>232</v>
       </c>
       <c r="E427" s="124" t="s">
@@ -17038,7 +17329,9 @@
         <v>111</v>
       </c>
       <c r="G427" s="49"/>
-      <c r="H427" s="50"/>
+      <c r="H427" s="50" t="s">
+        <v>632</v>
+      </c>
       <c r="I427" s="50"/>
       <c r="J427" s="5">
         <v>0.5</v>
@@ -17053,7 +17346,7 @@
       <c r="N427" s="11"/>
     </row>
     <row r="428" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A428" s="138"/>
+      <c r="A428" s="136"/>
       <c r="B428" s="47" t="s">
         <v>231</v>
       </c>
@@ -17085,7 +17378,7 @@
       <c r="N428" s="11"/>
     </row>
     <row r="429" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A429" s="138"/>
+      <c r="A429" s="136"/>
       <c r="B429" s="47" t="s">
         <v>231</v>
       </c>
@@ -17117,7 +17410,7 @@
       <c r="N429" s="11"/>
     </row>
     <row r="430" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A430" s="130"/>
+      <c r="A430" s="128"/>
       <c r="B430" s="47" t="s">
         <v>231</v>
       </c>
@@ -17174,7 +17467,7 @@
       <c r="C432" s="122" t="s">
         <v>12</v>
       </c>
-      <c r="D432" s="148" t="s">
+      <c r="D432" s="146" t="s">
         <v>234</v>
       </c>
       <c r="E432" s="124" t="s">
@@ -17184,7 +17477,9 @@
         <v>111</v>
       </c>
       <c r="G432" s="49"/>
-      <c r="H432" s="50"/>
+      <c r="H432" s="50" t="s">
+        <v>632</v>
+      </c>
       <c r="I432" s="50"/>
       <c r="J432" s="5">
         <v>0.5</v>
@@ -17199,7 +17494,7 @@
       <c r="N432" s="11"/>
     </row>
     <row r="433" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A433" s="138"/>
+      <c r="A433" s="136"/>
       <c r="B433" s="47" t="s">
         <v>233</v>
       </c>
@@ -17231,7 +17526,7 @@
       <c r="N433" s="11"/>
     </row>
     <row r="434" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A434" s="138"/>
+      <c r="A434" s="136"/>
       <c r="B434" s="47" t="s">
         <v>233</v>
       </c>
@@ -17263,7 +17558,7 @@
       <c r="N434" s="11"/>
     </row>
     <row r="435" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A435" s="130"/>
+      <c r="A435" s="128"/>
       <c r="B435" s="47" t="s">
         <v>233</v>
       </c>
@@ -17320,7 +17615,7 @@
       <c r="C437" s="122" t="s">
         <v>12</v>
       </c>
-      <c r="D437" s="148" t="s">
+      <c r="D437" s="146" t="s">
         <v>236</v>
       </c>
       <c r="E437" s="124" t="s">
@@ -17330,7 +17625,9 @@
         <v>111</v>
       </c>
       <c r="G437" s="49"/>
-      <c r="H437" s="50"/>
+      <c r="H437" s="50" t="s">
+        <v>632</v>
+      </c>
       <c r="I437" s="50"/>
       <c r="J437" s="5">
         <v>0.5</v>
@@ -17345,7 +17642,7 @@
       <c r="N437" s="11"/>
     </row>
     <row r="438" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A438" s="138"/>
+      <c r="A438" s="136"/>
       <c r="B438" s="47" t="s">
         <v>235</v>
       </c>
@@ -17377,7 +17674,7 @@
       <c r="N438" s="11"/>
     </row>
     <row r="439" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A439" s="138"/>
+      <c r="A439" s="136"/>
       <c r="B439" s="47" t="s">
         <v>235</v>
       </c>
@@ -17409,7 +17706,7 @@
       <c r="N439" s="11"/>
     </row>
     <row r="440" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A440" s="130"/>
+      <c r="A440" s="128"/>
       <c r="B440" s="47" t="s">
         <v>235</v>
       </c>
@@ -17466,7 +17763,7 @@
       <c r="C442" s="122" t="s">
         <v>12</v>
       </c>
-      <c r="D442" s="148" t="s">
+      <c r="D442" s="146" t="s">
         <v>238</v>
       </c>
       <c r="E442" s="124" t="s">
@@ -17476,7 +17773,9 @@
         <v>111</v>
       </c>
       <c r="G442" s="49"/>
-      <c r="H442" s="50"/>
+      <c r="H442" s="50" t="s">
+        <v>632</v>
+      </c>
       <c r="I442" s="50"/>
       <c r="J442" s="5">
         <v>0.5</v>
@@ -17491,7 +17790,7 @@
       <c r="N442" s="11"/>
     </row>
     <row r="443" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A443" s="138"/>
+      <c r="A443" s="136"/>
       <c r="B443" s="47" t="s">
         <v>237</v>
       </c>
@@ -17523,7 +17822,7 @@
       <c r="N443" s="11"/>
     </row>
     <row r="444" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A444" s="138"/>
+      <c r="A444" s="136"/>
       <c r="B444" s="47" t="s">
         <v>237</v>
       </c>
@@ -17555,7 +17854,7 @@
       <c r="N444" s="11"/>
     </row>
     <row r="445" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A445" s="130"/>
+      <c r="A445" s="128"/>
       <c r="B445" s="47" t="s">
         <v>237</v>
       </c>
@@ -17637,7 +17936,7 @@
       <c r="N447" s="11"/>
     </row>
     <row r="448" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A448" s="138"/>
+      <c r="A448" s="136"/>
       <c r="B448" s="47" t="s">
         <v>239</v>
       </c>
@@ -17669,7 +17968,7 @@
       <c r="N448" s="11"/>
     </row>
     <row r="449" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A449" s="138"/>
+      <c r="A449" s="136"/>
       <c r="B449" s="47" t="s">
         <v>239</v>
       </c>
@@ -17701,7 +18000,7 @@
       <c r="N449" s="11"/>
     </row>
     <row r="450" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A450" s="130"/>
+      <c r="A450" s="128"/>
       <c r="B450" s="47" t="s">
         <v>239</v>
       </c>
@@ -17783,7 +18082,7 @@
       <c r="N452" s="11"/>
     </row>
     <row r="453" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A453" s="138"/>
+      <c r="A453" s="136"/>
       <c r="B453" s="47" t="s">
         <v>242</v>
       </c>
@@ -17815,7 +18114,7 @@
       <c r="N453" s="11"/>
     </row>
     <row r="454" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A454" s="138"/>
+      <c r="A454" s="136"/>
       <c r="B454" s="47" t="s">
         <v>242</v>
       </c>
@@ -17847,7 +18146,7 @@
       <c r="N454" s="11"/>
     </row>
     <row r="455" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A455" s="130"/>
+      <c r="A455" s="128"/>
       <c r="B455" s="47" t="s">
         <v>242</v>
       </c>
@@ -17929,7 +18228,7 @@
       <c r="N457" s="11"/>
     </row>
     <row r="458" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A458" s="138"/>
+      <c r="A458" s="136"/>
       <c r="B458" s="47" t="s">
         <v>245</v>
       </c>
@@ -17961,7 +18260,7 @@
       <c r="N458" s="11"/>
     </row>
     <row r="459" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A459" s="138"/>
+      <c r="A459" s="136"/>
       <c r="B459" s="47" t="s">
         <v>245</v>
       </c>
@@ -17993,7 +18292,7 @@
       <c r="N459" s="11"/>
     </row>
     <row r="460" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A460" s="130"/>
+      <c r="A460" s="128"/>
       <c r="B460" s="47" t="s">
         <v>245</v>
       </c>
@@ -18075,7 +18374,7 @@
       <c r="N462" s="11"/>
     </row>
     <row r="463" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A463" s="138"/>
+      <c r="A463" s="136"/>
       <c r="B463" s="47" t="s">
         <v>247</v>
       </c>
@@ -18107,7 +18406,7 @@
       <c r="N463" s="11"/>
     </row>
     <row r="464" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A464" s="138"/>
+      <c r="A464" s="136"/>
       <c r="B464" s="47" t="s">
         <v>247</v>
       </c>
@@ -18139,7 +18438,7 @@
       <c r="N464" s="11"/>
     </row>
     <row r="465" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A465" s="130"/>
+      <c r="A465" s="128"/>
       <c r="B465" s="47" t="s">
         <v>247</v>
       </c>
@@ -18221,7 +18520,7 @@
       <c r="N467" s="11"/>
     </row>
     <row r="468" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A468" s="138"/>
+      <c r="A468" s="136"/>
       <c r="B468" s="47" t="s">
         <v>249</v>
       </c>
@@ -18253,7 +18552,7 @@
       <c r="N468" s="11"/>
     </row>
     <row r="469" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A469" s="138"/>
+      <c r="A469" s="136"/>
       <c r="B469" s="47" t="s">
         <v>249</v>
       </c>
@@ -18285,7 +18584,7 @@
       <c r="N469" s="11"/>
     </row>
     <row r="470" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A470" s="130"/>
+      <c r="A470" s="128"/>
       <c r="B470" s="47" t="s">
         <v>249</v>
       </c>
@@ -18367,7 +18666,7 @@
       <c r="N472" s="11"/>
     </row>
     <row r="473" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A473" s="138"/>
+      <c r="A473" s="136"/>
       <c r="B473" s="61" t="s">
         <v>251</v>
       </c>
@@ -18399,7 +18698,7 @@
       <c r="N473" s="11"/>
     </row>
     <row r="474" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A474" s="138"/>
+      <c r="A474" s="136"/>
       <c r="B474" s="61" t="s">
         <v>251</v>
       </c>
@@ -18431,7 +18730,7 @@
       <c r="N474" s="11"/>
     </row>
     <row r="475" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A475" s="130"/>
+      <c r="A475" s="128"/>
       <c r="B475" s="61" t="s">
         <v>251</v>
       </c>
@@ -18515,7 +18814,7 @@
       </c>
     </row>
     <row r="478" spans="1:14" ht="14.25" hidden="1" customHeight="1">
-      <c r="A478" s="138"/>
+      <c r="A478" s="136"/>
       <c r="B478" s="47" t="s">
         <v>254</v>
       </c>
@@ -18549,7 +18848,7 @@
       </c>
     </row>
     <row r="479" spans="1:14" ht="14.25" hidden="1" customHeight="1">
-      <c r="A479" s="138"/>
+      <c r="A479" s="136"/>
       <c r="B479" s="47" t="s">
         <v>254</v>
       </c>
@@ -18583,7 +18882,7 @@
       </c>
     </row>
     <row r="480" spans="1:14" ht="14.25" hidden="1" customHeight="1">
-      <c r="A480" s="130"/>
+      <c r="A480" s="128"/>
       <c r="B480" s="47" t="s">
         <v>254</v>
       </c>
@@ -18667,7 +18966,7 @@
       <c r="N482" s="11"/>
     </row>
     <row r="483" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A483" s="138"/>
+      <c r="A483" s="136"/>
       <c r="B483" s="47" t="s">
         <v>258</v>
       </c>
@@ -18699,7 +18998,7 @@
       <c r="N483" s="11"/>
     </row>
     <row r="484" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A484" s="138"/>
+      <c r="A484" s="136"/>
       <c r="B484" s="47" t="s">
         <v>258</v>
       </c>
@@ -18731,7 +19030,7 @@
       <c r="N484" s="11"/>
     </row>
     <row r="485" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A485" s="130"/>
+      <c r="A485" s="128"/>
       <c r="B485" s="47" t="s">
         <v>258</v>
       </c>
@@ -18813,7 +19112,7 @@
       <c r="N487" s="11"/>
     </row>
     <row r="488" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A488" s="138"/>
+      <c r="A488" s="136"/>
       <c r="B488" s="47" t="s">
         <v>261</v>
       </c>
@@ -18845,7 +19144,7 @@
       <c r="N488" s="11"/>
     </row>
     <row r="489" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A489" s="138"/>
+      <c r="A489" s="136"/>
       <c r="B489" s="47" t="s">
         <v>261</v>
       </c>
@@ -18877,7 +19176,7 @@
       <c r="N489" s="11"/>
     </row>
     <row r="490" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A490" s="130"/>
+      <c r="A490" s="128"/>
       <c r="B490" s="47" t="s">
         <v>261</v>
       </c>
@@ -18959,7 +19258,7 @@
       <c r="N492" s="11"/>
     </row>
     <row r="493" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A493" s="138"/>
+      <c r="A493" s="136"/>
       <c r="B493" s="47" t="s">
         <v>263</v>
       </c>
@@ -18991,7 +19290,7 @@
       <c r="N493" s="11"/>
     </row>
     <row r="494" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A494" s="138"/>
+      <c r="A494" s="136"/>
       <c r="B494" s="47" t="s">
         <v>263</v>
       </c>
@@ -19023,7 +19322,7 @@
       <c r="N494" s="11"/>
     </row>
     <row r="495" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A495" s="130"/>
+      <c r="A495" s="128"/>
       <c r="B495" s="47" t="s">
         <v>263</v>
       </c>
@@ -19105,7 +19404,7 @@
       <c r="N497" s="11"/>
     </row>
     <row r="498" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A498" s="138"/>
+      <c r="A498" s="136"/>
       <c r="B498" s="47" t="s">
         <v>265</v>
       </c>
@@ -19137,7 +19436,7 @@
       <c r="N498" s="11"/>
     </row>
     <row r="499" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A499" s="138"/>
+      <c r="A499" s="136"/>
       <c r="B499" s="47" t="s">
         <v>265</v>
       </c>
@@ -19169,7 +19468,7 @@
       <c r="N499" s="11"/>
     </row>
     <row r="500" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A500" s="130"/>
+      <c r="A500" s="128"/>
       <c r="B500" s="47" t="s">
         <v>265</v>
       </c>
@@ -19251,7 +19550,7 @@
       <c r="N502" s="11"/>
     </row>
     <row r="503" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A503" s="138"/>
+      <c r="A503" s="136"/>
       <c r="B503" s="47" t="s">
         <v>267</v>
       </c>
@@ -19283,7 +19582,7 @@
       <c r="N503" s="11"/>
     </row>
     <row r="504" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A504" s="138"/>
+      <c r="A504" s="136"/>
       <c r="B504" s="47" t="s">
         <v>267</v>
       </c>
@@ -19315,7 +19614,7 @@
       <c r="N504" s="11"/>
     </row>
     <row r="505" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A505" s="130"/>
+      <c r="A505" s="128"/>
       <c r="B505" s="47" t="s">
         <v>267</v>
       </c>
@@ -19397,7 +19696,7 @@
       <c r="N507" s="11"/>
     </row>
     <row r="508" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A508" s="138"/>
+      <c r="A508" s="136"/>
       <c r="B508" s="47" t="s">
         <v>269</v>
       </c>
@@ -19429,7 +19728,7 @@
       <c r="N508" s="11"/>
     </row>
     <row r="509" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A509" s="138"/>
+      <c r="A509" s="136"/>
       <c r="B509" s="47" t="s">
         <v>269</v>
       </c>
@@ -19461,7 +19760,7 @@
       <c r="N509" s="11"/>
     </row>
     <row r="510" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A510" s="130"/>
+      <c r="A510" s="128"/>
       <c r="B510" s="47" t="s">
         <v>269</v>
       </c>
@@ -19543,7 +19842,7 @@
       <c r="N512" s="11"/>
     </row>
     <row r="513" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A513" s="138"/>
+      <c r="A513" s="136"/>
       <c r="B513" s="67" t="s">
         <v>271</v>
       </c>
@@ -19575,7 +19874,7 @@
       <c r="N513" s="11"/>
     </row>
     <row r="514" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A514" s="138"/>
+      <c r="A514" s="136"/>
       <c r="B514" s="67" t="s">
         <v>271</v>
       </c>
@@ -19607,7 +19906,7 @@
       <c r="N514" s="11"/>
     </row>
     <row r="515" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A515" s="130"/>
+      <c r="A515" s="128"/>
       <c r="B515" s="74" t="s">
         <v>271</v>
       </c>
@@ -19655,7 +19954,7 @@
       <c r="N516" s="11"/>
     </row>
     <row r="517" spans="1:14" ht="14.25" hidden="1" customHeight="1">
-      <c r="A517" s="131">
+      <c r="A517" s="129">
         <v>109</v>
       </c>
       <c r="B517" s="81" t="s">
@@ -19691,7 +19990,7 @@
       <c r="N517" s="11"/>
     </row>
     <row r="518" spans="1:14" ht="14.25" hidden="1" customHeight="1">
-      <c r="A518" s="132"/>
+      <c r="A518" s="130"/>
       <c r="B518" s="82" t="s">
         <v>273</v>
       </c>
@@ -19725,7 +20024,7 @@
       <c r="N518" s="25"/>
     </row>
     <row r="519" spans="1:14" ht="14.25" hidden="1" customHeight="1">
-      <c r="A519" s="132"/>
+      <c r="A519" s="130"/>
       <c r="B519" s="82" t="s">
         <v>273</v>
       </c>
@@ -19759,7 +20058,7 @@
       <c r="N519" s="25"/>
     </row>
     <row r="520" spans="1:14" ht="14.25" hidden="1" customHeight="1">
-      <c r="A520" s="133"/>
+      <c r="A520" s="131"/>
       <c r="B520" s="82" t="s">
         <v>273</v>
       </c>
@@ -19855,7 +20154,7 @@
       <c r="N523" s="11"/>
     </row>
     <row r="524" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A524" s="131">
+      <c r="A524" s="129">
         <v>111</v>
       </c>
       <c r="B524" s="17" t="s">
@@ -19889,7 +20188,7 @@
       <c r="N524" s="11"/>
     </row>
     <row r="525" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A525" s="132"/>
+      <c r="A525" s="130"/>
       <c r="B525" s="17" t="s">
         <v>280</v>
       </c>
@@ -19921,7 +20220,7 @@
       <c r="N525" s="11"/>
     </row>
     <row r="526" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A526" s="132"/>
+      <c r="A526" s="130"/>
       <c r="B526" s="17" t="s">
         <v>280</v>
       </c>
@@ -19953,7 +20252,7 @@
       <c r="N526" s="11"/>
     </row>
     <row r="527" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A527" s="133"/>
+      <c r="A527" s="131"/>
       <c r="B527" s="88" t="s">
         <v>280</v>
       </c>
@@ -20001,7 +20300,7 @@
       <c r="N528" s="11"/>
     </row>
     <row r="529" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A529" s="131">
+      <c r="A529" s="129">
         <v>112</v>
       </c>
       <c r="B529" s="11" t="s">
@@ -20035,7 +20334,7 @@
       <c r="N529" s="11"/>
     </row>
     <row r="530" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A530" s="132"/>
+      <c r="A530" s="130"/>
       <c r="B530" s="25" t="s">
         <v>283</v>
       </c>
@@ -20067,7 +20366,7 @@
       <c r="N530" s="25"/>
     </row>
     <row r="531" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A531" s="132"/>
+      <c r="A531" s="130"/>
       <c r="B531" s="25" t="s">
         <v>283</v>
       </c>
@@ -20099,7 +20398,7 @@
       <c r="N531" s="25"/>
     </row>
     <row r="532" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A532" s="133"/>
+      <c r="A532" s="131"/>
       <c r="B532" s="25" t="s">
         <v>283</v>
       </c>
@@ -20519,7 +20818,7 @@
       <c r="N549" s="11"/>
     </row>
     <row r="550" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A550" s="131">
+      <c r="A550" s="129">
         <v>121</v>
       </c>
       <c r="B550" s="11" t="s">
@@ -20553,7 +20852,7 @@
       <c r="N550" s="11"/>
     </row>
     <row r="551" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A551" s="132"/>
+      <c r="A551" s="130"/>
       <c r="B551" s="11" t="s">
         <v>311</v>
       </c>
@@ -20585,7 +20884,7 @@
       <c r="N551" s="11"/>
     </row>
     <row r="552" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A552" s="132"/>
+      <c r="A552" s="130"/>
       <c r="B552" s="11" t="s">
         <v>311</v>
       </c>
@@ -20617,7 +20916,7 @@
       <c r="N552" s="11"/>
     </row>
     <row r="553" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A553" s="132"/>
+      <c r="A553" s="130"/>
       <c r="B553" s="11" t="s">
         <v>311</v>
       </c>
@@ -20649,7 +20948,7 @@
       <c r="N553" s="11"/>
     </row>
     <row r="554" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A554" s="132"/>
+      <c r="A554" s="130"/>
       <c r="B554" s="11" t="s">
         <v>311</v>
       </c>
@@ -20681,7 +20980,7 @@
       <c r="N554" s="11"/>
     </row>
     <row r="555" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A555" s="132"/>
+      <c r="A555" s="130"/>
       <c r="B555" s="11" t="s">
         <v>311</v>
       </c>
@@ -20713,7 +21012,7 @@
       <c r="N555" s="11"/>
     </row>
     <row r="556" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A556" s="132"/>
+      <c r="A556" s="130"/>
       <c r="B556" s="11" t="s">
         <v>311</v>
       </c>
@@ -20745,7 +21044,7 @@
       <c r="N556" s="11"/>
     </row>
     <row r="557" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A557" s="133"/>
+      <c r="A557" s="131"/>
       <c r="B557" s="11" t="s">
         <v>311</v>
       </c>
@@ -20793,7 +21092,7 @@
       <c r="N558" s="11"/>
     </row>
     <row r="559" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A559" s="131">
+      <c r="A559" s="129">
         <v>122</v>
       </c>
       <c r="B559" s="11" t="s">
@@ -20827,7 +21126,7 @@
       <c r="N559" s="11"/>
     </row>
     <row r="560" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A560" s="132"/>
+      <c r="A560" s="130"/>
       <c r="B560" s="11" t="s">
         <v>314</v>
       </c>
@@ -20859,7 +21158,7 @@
       <c r="N560" s="11"/>
     </row>
     <row r="561" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A561" s="132"/>
+      <c r="A561" s="130"/>
       <c r="B561" s="11" t="s">
         <v>314</v>
       </c>
@@ -20891,7 +21190,7 @@
       <c r="N561" s="11"/>
     </row>
     <row r="562" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A562" s="132"/>
+      <c r="A562" s="130"/>
       <c r="B562" s="11" t="s">
         <v>314</v>
       </c>
@@ -20923,7 +21222,7 @@
       <c r="N562" s="11"/>
     </row>
     <row r="563" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A563" s="132"/>
+      <c r="A563" s="130"/>
       <c r="B563" s="11" t="s">
         <v>314</v>
       </c>
@@ -20955,7 +21254,7 @@
       <c r="N563" s="11"/>
     </row>
     <row r="564" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A564" s="132"/>
+      <c r="A564" s="130"/>
       <c r="B564" s="11" t="s">
         <v>314</v>
       </c>
@@ -20987,7 +21286,7 @@
       <c r="N564" s="11"/>
     </row>
     <row r="565" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A565" s="132"/>
+      <c r="A565" s="130"/>
       <c r="B565" s="11" t="s">
         <v>314</v>
       </c>
@@ -21019,7 +21318,7 @@
       <c r="N565" s="11"/>
     </row>
     <row r="566" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A566" s="133"/>
+      <c r="A566" s="131"/>
       <c r="B566" s="11" t="s">
         <v>314</v>
       </c>
@@ -21161,7 +21460,7 @@
       <c r="N571" s="11"/>
     </row>
     <row r="572" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A572" s="131">
+      <c r="A572" s="129">
         <v>125</v>
       </c>
       <c r="B572" s="92" t="s">
@@ -21195,7 +21494,7 @@
       <c r="N572" s="11"/>
     </row>
     <row r="573" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A573" s="132"/>
+      <c r="A573" s="130"/>
       <c r="B573" s="92" t="s">
         <v>322</v>
       </c>
@@ -21227,7 +21526,7 @@
       <c r="N573" s="11"/>
     </row>
     <row r="574" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A574" s="132"/>
+      <c r="A574" s="130"/>
       <c r="B574" s="92" t="s">
         <v>322</v>
       </c>
@@ -21259,7 +21558,7 @@
       <c r="N574" s="11"/>
     </row>
     <row r="575" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A575" s="133"/>
+      <c r="A575" s="131"/>
       <c r="B575" s="92" t="s">
         <v>322</v>
       </c>
@@ -21307,7 +21606,7 @@
       <c r="N576" s="11"/>
     </row>
     <row r="577" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A577" s="131">
+      <c r="A577" s="129">
         <v>126</v>
       </c>
       <c r="B577" s="94" t="s">
@@ -21341,7 +21640,7 @@
       <c r="N577" s="11"/>
     </row>
     <row r="578" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A578" s="132"/>
+      <c r="A578" s="130"/>
       <c r="B578" s="94" t="s">
         <v>324</v>
       </c>
@@ -21373,7 +21672,7 @@
       <c r="N578" s="11"/>
     </row>
     <row r="579" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A579" s="132"/>
+      <c r="A579" s="130"/>
       <c r="B579" s="94" t="s">
         <v>324</v>
       </c>
@@ -21405,7 +21704,7 @@
       <c r="N579" s="11"/>
     </row>
     <row r="580" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A580" s="133"/>
+      <c r="A580" s="131"/>
       <c r="B580" s="94" t="s">
         <v>324</v>
       </c>
@@ -21453,7 +21752,7 @@
       <c r="N581" s="11"/>
     </row>
     <row r="582" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A582" s="131">
+      <c r="A582" s="129">
         <v>127</v>
       </c>
       <c r="B582" s="94" t="s">
@@ -21487,7 +21786,7 @@
       <c r="N582" s="11"/>
     </row>
     <row r="583" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A583" s="132"/>
+      <c r="A583" s="130"/>
       <c r="B583" s="94" t="s">
         <v>326</v>
       </c>
@@ -21519,7 +21818,7 @@
       <c r="N583" s="11"/>
     </row>
     <row r="584" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A584" s="132"/>
+      <c r="A584" s="130"/>
       <c r="B584" s="94" t="s">
         <v>326</v>
       </c>
@@ -21551,7 +21850,7 @@
       <c r="N584" s="11"/>
     </row>
     <row r="585" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A585" s="133"/>
+      <c r="A585" s="131"/>
       <c r="B585" s="94" t="s">
         <v>326</v>
       </c>
@@ -21599,7 +21898,7 @@
       <c r="N586" s="11"/>
     </row>
     <row r="587" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A587" s="131">
+      <c r="A587" s="129">
         <v>128</v>
       </c>
       <c r="B587" s="94" t="s">
@@ -21633,7 +21932,7 @@
       <c r="N587" s="11"/>
     </row>
     <row r="588" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A588" s="132"/>
+      <c r="A588" s="130"/>
       <c r="B588" s="94" t="s">
         <v>328</v>
       </c>
@@ -21665,7 +21964,7 @@
       <c r="N588" s="11"/>
     </row>
     <row r="589" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A589" s="132"/>
+      <c r="A589" s="130"/>
       <c r="B589" s="94" t="s">
         <v>328</v>
       </c>
@@ -21697,7 +21996,7 @@
       <c r="N589" s="11"/>
     </row>
     <row r="590" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A590" s="133"/>
+      <c r="A590" s="131"/>
       <c r="B590" s="94" t="s">
         <v>328</v>
       </c>
@@ -21789,7 +22088,7 @@
       <c r="N593" s="11"/>
     </row>
     <row r="594" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A594" s="131">
+      <c r="A594" s="129">
         <v>130</v>
       </c>
       <c r="B594" s="17" t="s">
@@ -21823,7 +22122,7 @@
       <c r="N594" s="11"/>
     </row>
     <row r="595" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A595" s="132"/>
+      <c r="A595" s="130"/>
       <c r="B595" s="17" t="s">
         <v>332</v>
       </c>
@@ -21855,7 +22154,7 @@
       <c r="N595" s="11"/>
     </row>
     <row r="596" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A596" s="132"/>
+      <c r="A596" s="130"/>
       <c r="B596" s="17" t="s">
         <v>332</v>
       </c>
@@ -21887,7 +22186,7 @@
       <c r="N596" s="11"/>
     </row>
     <row r="597" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A597" s="133"/>
+      <c r="A597" s="131"/>
       <c r="B597" s="17" t="s">
         <v>332</v>
       </c>
@@ -21935,7 +22234,7 @@
       <c r="N598" s="11"/>
     </row>
     <row r="599" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A599" s="131">
+      <c r="A599" s="129">
         <v>131</v>
       </c>
       <c r="B599" s="17" t="s">
@@ -21969,7 +22268,7 @@
       <c r="N599" s="11"/>
     </row>
     <row r="600" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A600" s="132"/>
+      <c r="A600" s="130"/>
       <c r="B600" s="17" t="s">
         <v>335</v>
       </c>
@@ -22001,7 +22300,7 @@
       <c r="N600" s="11"/>
     </row>
     <row r="601" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A601" s="132"/>
+      <c r="A601" s="130"/>
       <c r="B601" s="17" t="s">
         <v>335</v>
       </c>
@@ -22033,7 +22332,7 @@
       <c r="N601" s="11"/>
     </row>
     <row r="602" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A602" s="133"/>
+      <c r="A602" s="131"/>
       <c r="B602" s="17" t="s">
         <v>335</v>
       </c>
@@ -22081,7 +22380,7 @@
       <c r="N603" s="11"/>
     </row>
     <row r="604" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A604" s="131">
+      <c r="A604" s="129">
         <v>132</v>
       </c>
       <c r="B604" s="17" t="s">
@@ -22115,7 +22414,7 @@
       <c r="N604" s="11"/>
     </row>
     <row r="605" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A605" s="132"/>
+      <c r="A605" s="130"/>
       <c r="B605" s="17" t="s">
         <v>337</v>
       </c>
@@ -22147,7 +22446,7 @@
       <c r="N605" s="60"/>
     </row>
     <row r="606" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A606" s="132"/>
+      <c r="A606" s="130"/>
       <c r="B606" s="17" t="s">
         <v>337</v>
       </c>
@@ -22179,7 +22478,7 @@
       <c r="N606" s="60"/>
     </row>
     <row r="607" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A607" s="133"/>
+      <c r="A607" s="131"/>
       <c r="B607" s="17" t="s">
         <v>337</v>
       </c>
@@ -22227,7 +22526,7 @@
       <c r="N608" s="60"/>
     </row>
     <row r="609" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A609" s="131">
+      <c r="A609" s="129">
         <v>133</v>
       </c>
       <c r="B609" s="17" t="s">
@@ -22261,7 +22560,7 @@
       <c r="N609" s="60"/>
     </row>
     <row r="610" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A610" s="132"/>
+      <c r="A610" s="130"/>
       <c r="B610" s="17" t="s">
         <v>339</v>
       </c>
@@ -22293,7 +22592,7 @@
       <c r="N610" s="60"/>
     </row>
     <row r="611" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A611" s="132"/>
+      <c r="A611" s="130"/>
       <c r="B611" s="17" t="s">
         <v>339</v>
       </c>
@@ -22325,7 +22624,7 @@
       <c r="N611" s="60"/>
     </row>
     <row r="612" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A612" s="133"/>
+      <c r="A612" s="131"/>
       <c r="B612" s="17" t="s">
         <v>339</v>
       </c>
@@ -22465,7 +22764,7 @@
       <c r="N617" s="11"/>
     </row>
     <row r="618" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A618" s="131">
+      <c r="A618" s="129">
         <v>136</v>
       </c>
       <c r="B618" s="17" t="s">
@@ -22497,7 +22796,7 @@
       <c r="N618" s="11"/>
     </row>
     <row r="619" spans="1:14" ht="14.25" hidden="1" customHeight="1">
-      <c r="A619" s="132"/>
+      <c r="A619" s="130"/>
       <c r="B619" s="17" t="s">
         <v>345</v>
       </c>
@@ -22527,7 +22826,7 @@
       <c r="N619" s="11"/>
     </row>
     <row r="620" spans="1:14" ht="14.25" hidden="1" customHeight="1">
-      <c r="A620" s="132"/>
+      <c r="A620" s="130"/>
       <c r="B620" s="17" t="s">
         <v>345</v>
       </c>
@@ -22557,7 +22856,7 @@
       <c r="N620" s="11"/>
     </row>
     <row r="621" spans="1:14" ht="14.25" hidden="1" customHeight="1">
-      <c r="A621" s="133"/>
+      <c r="A621" s="131"/>
       <c r="B621" s="17" t="s">
         <v>345</v>
       </c>
@@ -22654,7 +22953,7 @@
       <c r="C625" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D625" s="148" t="s">
+      <c r="D625" s="146" t="s">
         <v>349</v>
       </c>
       <c r="E625" s="48" t="s">
@@ -22679,7 +22978,7 @@
       <c r="N625" s="11"/>
     </row>
     <row r="626" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A626" s="135"/>
+      <c r="A626" s="133"/>
       <c r="B626" s="47"/>
       <c r="C626" s="5" t="s">
         <v>18</v>
@@ -22709,7 +23008,7 @@
       <c r="N626" s="11"/>
     </row>
     <row r="627" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A627" s="135"/>
+      <c r="A627" s="133"/>
       <c r="B627" s="47"/>
       <c r="C627" s="5" t="s">
         <v>20</v>
@@ -22739,7 +23038,7 @@
       <c r="N627" s="11"/>
     </row>
     <row r="628" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A628" s="136"/>
+      <c r="A628" s="134"/>
       <c r="B628" s="47"/>
       <c r="C628" s="5" t="s">
         <v>22</v>
@@ -22785,14 +23084,14 @@
       <c r="N629" s="11"/>
     </row>
     <row r="630" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A630" s="140">
+      <c r="A630" s="138">
         <v>141</v>
       </c>
       <c r="B630" s="47"/>
       <c r="C630" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D630" s="148" t="s">
+      <c r="D630" s="146" t="s">
         <v>351</v>
       </c>
       <c r="E630" s="101" t="s">
@@ -22817,7 +23116,7 @@
       <c r="N630" s="11"/>
     </row>
     <row r="631" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A631" s="135"/>
+      <c r="A631" s="133"/>
       <c r="B631" s="47"/>
       <c r="C631" s="5" t="s">
         <v>18</v>
@@ -22847,7 +23146,7 @@
       <c r="N631" s="11"/>
     </row>
     <row r="632" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A632" s="135"/>
+      <c r="A632" s="133"/>
       <c r="B632" s="47"/>
       <c r="C632" s="5" t="s">
         <v>20</v>
@@ -22877,7 +23176,7 @@
       <c r="N632" s="11"/>
     </row>
     <row r="633" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A633" s="136"/>
+      <c r="A633" s="134"/>
       <c r="B633" s="47"/>
       <c r="C633" s="5" t="s">
         <v>22</v>
@@ -22923,14 +23222,14 @@
       <c r="N634" s="11"/>
     </row>
     <row r="635" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A635" s="141" t="s">
+      <c r="A635" s="139" t="s">
         <v>353</v>
       </c>
       <c r="B635" s="102"/>
       <c r="C635" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="D635" s="149" t="s">
+      <c r="D635" s="147" t="s">
         <v>354</v>
       </c>
       <c r="E635" s="103"/>
@@ -22965,7 +23264,7 @@
       <c r="Z635" s="107"/>
     </row>
     <row r="636" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A636" s="135"/>
+      <c r="A636" s="133"/>
       <c r="B636" s="102"/>
       <c r="C636" s="26" t="s">
         <v>18</v>
@@ -23005,7 +23304,7 @@
       <c r="Z636" s="107"/>
     </row>
     <row r="637" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A637" s="135"/>
+      <c r="A637" s="133"/>
       <c r="B637" s="102"/>
       <c r="C637" s="26" t="s">
         <v>20</v>
@@ -23045,7 +23344,7 @@
       <c r="Z637" s="107"/>
     </row>
     <row r="638" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A638" s="136"/>
+      <c r="A638" s="134"/>
       <c r="B638" s="102"/>
       <c r="C638" s="26" t="s">
         <v>22</v>
@@ -23133,7 +23432,7 @@
       <c r="N640" s="11"/>
     </row>
     <row r="641" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A641" s="135"/>
+      <c r="A641" s="133"/>
       <c r="B641" s="47"/>
       <c r="C641" s="47"/>
       <c r="D641" s="47"/>
@@ -23159,7 +23458,7 @@
       <c r="N641" s="11"/>
     </row>
     <row r="642" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A642" s="135"/>
+      <c r="A642" s="133"/>
       <c r="B642" s="47"/>
       <c r="C642" s="47"/>
       <c r="D642" s="47"/>
@@ -23185,7 +23484,7 @@
       <c r="N642" s="11"/>
     </row>
     <row r="643" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A643" s="135"/>
+      <c r="A643" s="133"/>
       <c r="B643" s="47" t="s">
         <v>360</v>
       </c>
@@ -23215,7 +23514,7 @@
       <c r="N643" s="11"/>
     </row>
     <row r="644" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A644" s="135"/>
+      <c r="A644" s="133"/>
       <c r="B644" s="47"/>
       <c r="C644" s="47"/>
       <c r="D644" s="47"/>
@@ -23241,7 +23540,7 @@
       <c r="N644" s="11"/>
     </row>
     <row r="645" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A645" s="135"/>
+      <c r="A645" s="133"/>
       <c r="B645" s="47"/>
       <c r="C645" s="47"/>
       <c r="D645" s="47"/>
@@ -23267,7 +23566,7 @@
       <c r="N645" s="11"/>
     </row>
     <row r="646" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A646" s="135"/>
+      <c r="A646" s="133"/>
       <c r="B646" s="47" t="s">
         <v>361</v>
       </c>
@@ -23297,7 +23596,7 @@
       <c r="N646" s="11"/>
     </row>
     <row r="647" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A647" s="135"/>
+      <c r="A647" s="133"/>
       <c r="B647" s="47"/>
       <c r="C647" s="47"/>
       <c r="D647" s="47"/>
@@ -23323,7 +23622,7 @@
       <c r="N647" s="11"/>
     </row>
     <row r="648" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A648" s="135"/>
+      <c r="A648" s="133"/>
       <c r="B648" s="47"/>
       <c r="C648" s="47"/>
       <c r="D648" s="47"/>
@@ -23349,7 +23648,7 @@
       <c r="N648" s="11"/>
     </row>
     <row r="649" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A649" s="135"/>
+      <c r="A649" s="133"/>
       <c r="B649" s="47" t="s">
         <v>362</v>
       </c>
@@ -23379,7 +23678,7 @@
       <c r="N649" s="11"/>
     </row>
     <row r="650" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A650" s="135"/>
+      <c r="A650" s="133"/>
       <c r="B650" s="47"/>
       <c r="C650" s="47"/>
       <c r="D650" s="47"/>
@@ -23405,7 +23704,7 @@
       <c r="N650" s="11"/>
     </row>
     <row r="651" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A651" s="136"/>
+      <c r="A651" s="134"/>
       <c r="B651" s="47"/>
       <c r="C651" s="47"/>
       <c r="D651" s="47"/>
@@ -23454,7 +23753,7 @@
       <c r="C653" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D653" s="148" t="s">
+      <c r="D653" s="146" t="s">
         <v>363</v>
       </c>
       <c r="E653" s="101" t="s">
@@ -23479,7 +23778,7 @@
       <c r="N653" s="11"/>
     </row>
     <row r="654" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A654" s="135"/>
+      <c r="A654" s="133"/>
       <c r="B654" s="47"/>
       <c r="C654" s="5" t="s">
         <v>18</v>
@@ -23509,7 +23808,7 @@
       <c r="N654" s="11"/>
     </row>
     <row r="655" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A655" s="135"/>
+      <c r="A655" s="133"/>
       <c r="B655" s="47"/>
       <c r="C655" s="5" t="s">
         <v>20</v>
@@ -23539,7 +23838,7 @@
       <c r="N655" s="11"/>
     </row>
     <row r="656" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A656" s="136"/>
+      <c r="A656" s="134"/>
       <c r="B656" s="47"/>
       <c r="C656" s="5" t="s">
         <v>22</v>
@@ -23617,7 +23916,7 @@
       <c r="N658" s="11"/>
     </row>
     <row r="659" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A659" s="135"/>
+      <c r="A659" s="133"/>
       <c r="B659" s="47"/>
       <c r="C659" s="5" t="s">
         <v>18</v>
@@ -23647,7 +23946,7 @@
       <c r="N659" s="11"/>
     </row>
     <row r="660" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A660" s="135"/>
+      <c r="A660" s="133"/>
       <c r="B660" s="47"/>
       <c r="C660" s="5" t="s">
         <v>20</v>
@@ -23677,7 +23976,7 @@
       <c r="N660" s="11"/>
     </row>
     <row r="661" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A661" s="136"/>
+      <c r="A661" s="134"/>
       <c r="B661" s="47"/>
       <c r="C661" s="5" t="s">
         <v>22</v>
@@ -23723,7 +24022,7 @@
       <c r="N662" s="11"/>
     </row>
     <row r="663" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A663" s="134">
+      <c r="A663" s="132">
         <v>145</v>
       </c>
       <c r="B663" s="52"/>
@@ -23767,7 +24066,7 @@
       <c r="Z663" s="56"/>
     </row>
     <row r="664" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A664" s="135"/>
+      <c r="A664" s="133"/>
       <c r="B664" s="52"/>
       <c r="C664" s="19" t="s">
         <v>18</v>
@@ -23809,7 +24108,7 @@
       <c r="Z664" s="56"/>
     </row>
     <row r="665" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A665" s="135"/>
+      <c r="A665" s="133"/>
       <c r="B665" s="52"/>
       <c r="C665" s="19" t="s">
         <v>20</v>
@@ -23851,7 +24150,7 @@
       <c r="Z665" s="56"/>
     </row>
     <row r="666" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A666" s="136"/>
+      <c r="A666" s="134"/>
       <c r="B666" s="52"/>
       <c r="C666" s="19" t="s">
         <v>22</v>
@@ -23941,7 +24240,7 @@
       <c r="N668" s="11"/>
     </row>
     <row r="669" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A669" s="135"/>
+      <c r="A669" s="133"/>
       <c r="B669" s="61"/>
       <c r="C669" s="5" t="s">
         <v>18</v>
@@ -23971,7 +24270,7 @@
       <c r="N669" s="11"/>
     </row>
     <row r="670" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A670" s="135"/>
+      <c r="A670" s="133"/>
       <c r="B670" s="61"/>
       <c r="C670" s="5" t="s">
         <v>20</v>
@@ -24001,7 +24300,7 @@
       <c r="N670" s="11"/>
     </row>
     <row r="671" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A671" s="136"/>
+      <c r="A671" s="134"/>
       <c r="B671" s="61"/>
       <c r="C671" s="5" t="s">
         <v>22</v>
@@ -24079,7 +24378,7 @@
       <c r="N673" s="11"/>
     </row>
     <row r="674" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A674" s="135"/>
+      <c r="A674" s="133"/>
       <c r="B674" s="64"/>
       <c r="C674" s="5" t="s">
         <v>18</v>
@@ -24109,7 +24408,7 @@
       <c r="N674" s="11"/>
     </row>
     <row r="675" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A675" s="135"/>
+      <c r="A675" s="133"/>
       <c r="B675" s="64"/>
       <c r="C675" s="5" t="s">
         <v>20</v>
@@ -24139,7 +24438,7 @@
       <c r="N675" s="11"/>
     </row>
     <row r="676" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A676" s="136"/>
+      <c r="A676" s="134"/>
       <c r="B676" s="64"/>
       <c r="C676" s="5" t="s">
         <v>22</v>
@@ -24185,7 +24484,7 @@
       <c r="N677" s="11"/>
     </row>
     <row r="678" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A678" s="134">
+      <c r="A678" s="132">
         <v>148</v>
       </c>
       <c r="B678" s="55"/>
@@ -24229,7 +24528,7 @@
       <c r="Z678" s="56"/>
     </row>
     <row r="679" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A679" s="135"/>
+      <c r="A679" s="133"/>
       <c r="B679" s="55"/>
       <c r="C679" s="19" t="s">
         <v>18</v>
@@ -24271,7 +24570,7 @@
       <c r="Z679" s="56"/>
     </row>
     <row r="680" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A680" s="135"/>
+      <c r="A680" s="133"/>
       <c r="B680" s="55"/>
       <c r="C680" s="19" t="s">
         <v>20</v>
@@ -24313,7 +24612,7 @@
       <c r="Z680" s="56"/>
     </row>
     <row r="681" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A681" s="136"/>
+      <c r="A681" s="134"/>
       <c r="B681" s="55"/>
       <c r="C681" s="19" t="s">
         <v>22</v>
@@ -24403,7 +24702,7 @@
       <c r="N683" s="25"/>
     </row>
     <row r="684" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A684" s="135"/>
+      <c r="A684" s="133"/>
       <c r="B684" s="110"/>
       <c r="C684" s="19" t="s">
         <v>18</v>
@@ -24433,7 +24732,7 @@
       <c r="N684" s="25"/>
     </row>
     <row r="685" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A685" s="135"/>
+      <c r="A685" s="133"/>
       <c r="B685" s="110"/>
       <c r="C685" s="19" t="s">
         <v>20</v>
@@ -24463,7 +24762,7 @@
       <c r="N685" s="25"/>
     </row>
     <row r="686" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A686" s="136"/>
+      <c r="A686" s="134"/>
       <c r="B686" s="110"/>
       <c r="C686" s="19" t="s">
         <v>22</v>
@@ -24509,7 +24808,7 @@
       <c r="N687" s="11"/>
     </row>
     <row r="688" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A688" s="137">
+      <c r="A688" s="135">
         <v>150</v>
       </c>
       <c r="B688" s="25"/>
@@ -24553,7 +24852,7 @@
       <c r="Z688" s="56"/>
     </row>
     <row r="689" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A689" s="138"/>
+      <c r="A689" s="136"/>
       <c r="B689" s="25"/>
       <c r="C689" s="19" t="s">
         <v>18</v>
@@ -24595,7 +24894,7 @@
       <c r="Z689" s="56"/>
     </row>
     <row r="690" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A690" s="138"/>
+      <c r="A690" s="136"/>
       <c r="B690" s="25"/>
       <c r="C690" s="19" t="s">
         <v>20</v>
@@ -24637,7 +24936,7 @@
       <c r="Z690" s="56"/>
     </row>
     <row r="691" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A691" s="130"/>
+      <c r="A691" s="128"/>
       <c r="B691" s="25"/>
       <c r="C691" s="19" t="s">
         <v>22</v>
@@ -24695,7 +24994,7 @@
       <c r="N692" s="11"/>
     </row>
     <row r="693" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A693" s="139">
+      <c r="A693" s="137">
         <v>151</v>
       </c>
       <c r="B693" s="113"/>
@@ -24739,7 +25038,7 @@
       <c r="Z693" s="56"/>
     </row>
     <row r="694" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A694" s="132"/>
+      <c r="A694" s="130"/>
       <c r="B694" s="113"/>
       <c r="C694" s="19" t="s">
         <v>18</v>
@@ -24781,7 +25080,7 @@
       <c r="Z694" s="56"/>
     </row>
     <row r="695" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A695" s="132"/>
+      <c r="A695" s="130"/>
       <c r="B695" s="113"/>
       <c r="C695" s="19" t="s">
         <v>20</v>
@@ -24823,7 +25122,7 @@
       <c r="Z695" s="56"/>
     </row>
     <row r="696" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A696" s="133"/>
+      <c r="A696" s="131"/>
       <c r="B696" s="113"/>
       <c r="C696" s="19" t="s">
         <v>22</v>
@@ -24881,7 +25180,7 @@
       <c r="N697" s="11"/>
     </row>
     <row r="698" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A698" s="131">
+      <c r="A698" s="129">
         <v>152</v>
       </c>
       <c r="B698" s="25"/>
@@ -24911,7 +25210,7 @@
       <c r="N698" s="25"/>
     </row>
     <row r="699" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A699" s="132"/>
+      <c r="A699" s="130"/>
       <c r="B699" s="25"/>
       <c r="C699" s="19" t="s">
         <v>18</v>
@@ -24939,7 +25238,7 @@
       <c r="N699" s="25"/>
     </row>
     <row r="700" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A700" s="132"/>
+      <c r="A700" s="130"/>
       <c r="B700" s="25"/>
       <c r="C700" s="19" t="s">
         <v>20</v>
@@ -24967,7 +25266,7 @@
       <c r="N700" s="25"/>
     </row>
     <row r="701" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A701" s="133"/>
+      <c r="A701" s="131"/>
       <c r="B701" s="25"/>
       <c r="C701" s="19" t="s">
         <v>22</v>
@@ -25011,7 +25310,7 @@
       <c r="N702" s="11"/>
     </row>
     <row r="703" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A703" s="131">
+      <c r="A703" s="129">
         <v>153</v>
       </c>
       <c r="B703" s="25"/>
@@ -25041,7 +25340,7 @@
       <c r="N703" s="25"/>
     </row>
     <row r="704" spans="1:26" ht="18.75" hidden="1" customHeight="1">
-      <c r="A704" s="132"/>
+      <c r="A704" s="130"/>
       <c r="B704" s="25"/>
       <c r="C704" s="19" t="s">
         <v>18</v>
@@ -25069,7 +25368,7 @@
       <c r="N704" s="25"/>
     </row>
     <row r="705" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A705" s="132"/>
+      <c r="A705" s="130"/>
       <c r="B705" s="25"/>
       <c r="C705" s="19" t="s">
         <v>20</v>
@@ -25097,7 +25396,7 @@
       <c r="N705" s="25"/>
     </row>
     <row r="706" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A706" s="133"/>
+      <c r="A706" s="131"/>
       <c r="B706" s="25"/>
       <c r="C706" s="19" t="s">
         <v>22</v>
@@ -25141,7 +25440,7 @@
       <c r="N707" s="11"/>
     </row>
     <row r="708" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A708" s="131">
+      <c r="A708" s="129">
         <v>154</v>
       </c>
       <c r="B708" s="11"/>
@@ -25171,7 +25470,7 @@
       <c r="N708" s="11"/>
     </row>
     <row r="709" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A709" s="132"/>
+      <c r="A709" s="130"/>
       <c r="B709" s="11"/>
       <c r="C709" s="5" t="s">
         <v>18</v>
@@ -25199,7 +25498,7 @@
       <c r="N709" s="11"/>
     </row>
     <row r="710" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A710" s="132"/>
+      <c r="A710" s="130"/>
       <c r="B710" s="11"/>
       <c r="C710" s="5" t="s">
         <v>20</v>
@@ -25227,7 +25526,7 @@
       <c r="N710" s="11"/>
     </row>
     <row r="711" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A711" s="133"/>
+      <c r="A711" s="131"/>
       <c r="B711" s="11"/>
       <c r="C711" s="5" t="s">
         <v>22</v>
@@ -25271,7 +25570,7 @@
       <c r="N712" s="11"/>
     </row>
     <row r="713" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A713" s="131">
+      <c r="A713" s="129">
         <v>155</v>
       </c>
       <c r="B713" s="11" t="s">
@@ -25301,7 +25600,7 @@
       <c r="N713" s="11"/>
     </row>
     <row r="714" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A714" s="132"/>
+      <c r="A714" s="130"/>
       <c r="B714" s="11"/>
       <c r="C714" s="11"/>
       <c r="D714" s="11"/>
@@ -25325,7 +25624,7 @@
       <c r="N714" s="11"/>
     </row>
     <row r="715" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A715" s="132"/>
+      <c r="A715" s="130"/>
       <c r="B715" s="11"/>
       <c r="C715" s="11"/>
       <c r="D715" s="11"/>
@@ -25349,7 +25648,7 @@
       <c r="N715" s="11"/>
     </row>
     <row r="716" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A716" s="132"/>
+      <c r="A716" s="130"/>
       <c r="B716" s="11"/>
       <c r="C716" s="11"/>
       <c r="D716" s="11"/>
@@ -25373,7 +25672,7 @@
       <c r="N716" s="11"/>
     </row>
     <row r="717" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A717" s="132"/>
+      <c r="A717" s="130"/>
       <c r="B717" s="11"/>
       <c r="C717" s="11"/>
       <c r="D717" s="11" t="s">
@@ -25399,7 +25698,7 @@
       <c r="N717" s="11"/>
     </row>
     <row r="718" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A718" s="132"/>
+      <c r="A718" s="130"/>
       <c r="B718" s="11"/>
       <c r="C718" s="11"/>
       <c r="D718" s="11"/>
@@ -25423,7 +25722,7 @@
       <c r="N718" s="11"/>
     </row>
     <row r="719" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A719" s="132"/>
+      <c r="A719" s="130"/>
       <c r="B719" s="11"/>
       <c r="C719" s="11"/>
       <c r="D719" s="11"/>
@@ -25447,7 +25746,7 @@
       <c r="N719" s="11"/>
     </row>
     <row r="720" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A720" s="132"/>
+      <c r="A720" s="130"/>
       <c r="B720" s="11"/>
       <c r="C720" s="11"/>
       <c r="D720" s="11"/>
@@ -25471,7 +25770,7 @@
       <c r="N720" s="11"/>
     </row>
     <row r="721" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A721" s="132"/>
+      <c r="A721" s="130"/>
       <c r="B721" s="11"/>
       <c r="C721" s="11"/>
       <c r="D721" s="11" t="s">
@@ -25497,7 +25796,7 @@
       <c r="N721" s="11"/>
     </row>
     <row r="722" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A722" s="132"/>
+      <c r="A722" s="130"/>
       <c r="B722" s="11"/>
       <c r="C722" s="11"/>
       <c r="D722" s="11"/>
@@ -25521,7 +25820,7 @@
       <c r="N722" s="11"/>
     </row>
     <row r="723" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A723" s="132"/>
+      <c r="A723" s="130"/>
       <c r="B723" s="11"/>
       <c r="C723" s="11"/>
       <c r="D723" s="11"/>
@@ -25545,7 +25844,7 @@
       <c r="N723" s="11"/>
     </row>
     <row r="724" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A724" s="132"/>
+      <c r="A724" s="130"/>
       <c r="B724" s="11"/>
       <c r="C724" s="11"/>
       <c r="D724" s="11"/>
@@ -25569,7 +25868,7 @@
       <c r="N724" s="11"/>
     </row>
     <row r="725" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A725" s="132"/>
+      <c r="A725" s="130"/>
       <c r="B725" s="11"/>
       <c r="C725" s="11"/>
       <c r="D725" s="11" t="s">
@@ -25595,7 +25894,7 @@
       <c r="N725" s="11"/>
     </row>
     <row r="726" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A726" s="132"/>
+      <c r="A726" s="130"/>
       <c r="B726" s="11"/>
       <c r="C726" s="11"/>
       <c r="D726" s="11"/>
@@ -25619,7 +25918,7 @@
       <c r="N726" s="11"/>
     </row>
     <row r="727" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A727" s="132"/>
+      <c r="A727" s="130"/>
       <c r="B727" s="11"/>
       <c r="C727" s="11"/>
       <c r="D727" s="11"/>
@@ -25643,7 +25942,7 @@
       <c r="N727" s="11"/>
     </row>
     <row r="728" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A728" s="133"/>
+      <c r="A728" s="131"/>
       <c r="B728" s="11"/>
       <c r="C728" s="11"/>
       <c r="D728" s="11"/>
@@ -25683,7 +25982,7 @@
       <c r="N729" s="11"/>
     </row>
     <row r="730" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A730" s="131">
+      <c r="A730" s="129">
         <v>156</v>
       </c>
       <c r="B730" s="11" t="s">
@@ -25713,7 +26012,7 @@
       <c r="N730" s="11"/>
     </row>
     <row r="731" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A731" s="132"/>
+      <c r="A731" s="130"/>
       <c r="B731" s="11"/>
       <c r="C731" s="11"/>
       <c r="D731" s="11"/>
@@ -25737,7 +26036,7 @@
       <c r="N731" s="11"/>
     </row>
     <row r="732" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A732" s="132"/>
+      <c r="A732" s="130"/>
       <c r="B732" s="11"/>
       <c r="C732" s="11"/>
       <c r="D732" s="11"/>
@@ -25761,7 +26060,7 @@
       <c r="N732" s="11"/>
     </row>
     <row r="733" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A733" s="132"/>
+      <c r="A733" s="130"/>
       <c r="B733" s="11"/>
       <c r="C733" s="11"/>
       <c r="D733" s="11"/>
@@ -25785,7 +26084,7 @@
       <c r="N733" s="11"/>
     </row>
     <row r="734" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A734" s="132"/>
+      <c r="A734" s="130"/>
       <c r="B734" s="11"/>
       <c r="C734" s="11"/>
       <c r="D734" s="11"/>
@@ -25809,7 +26108,7 @@
       <c r="N734" s="11"/>
     </row>
     <row r="735" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A735" s="132"/>
+      <c r="A735" s="130"/>
       <c r="B735" s="11"/>
       <c r="C735" s="11"/>
       <c r="D735" s="11"/>
@@ -25833,7 +26132,7 @@
       <c r="N735" s="11"/>
     </row>
     <row r="736" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A736" s="132"/>
+      <c r="A736" s="130"/>
       <c r="B736" s="11"/>
       <c r="C736" s="11"/>
       <c r="D736" s="11"/>
@@ -25857,7 +26156,7 @@
       <c r="N736" s="11"/>
     </row>
     <row r="737" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A737" s="132"/>
+      <c r="A737" s="130"/>
       <c r="B737" s="11"/>
       <c r="C737" s="11"/>
       <c r="D737" s="11" t="s">
@@ -25883,7 +26182,7 @@
       <c r="N737" s="11"/>
     </row>
     <row r="738" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A738" s="132"/>
+      <c r="A738" s="130"/>
       <c r="B738" s="11"/>
       <c r="C738" s="11"/>
       <c r="D738" s="11"/>
@@ -25907,7 +26206,7 @@
       <c r="N738" s="11"/>
     </row>
     <row r="739" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A739" s="132"/>
+      <c r="A739" s="130"/>
       <c r="B739" s="11"/>
       <c r="C739" s="11"/>
       <c r="D739" s="11"/>
@@ -25931,7 +26230,7 @@
       <c r="N739" s="11"/>
     </row>
     <row r="740" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A740" s="132"/>
+      <c r="A740" s="130"/>
       <c r="B740" s="11"/>
       <c r="C740" s="11"/>
       <c r="D740" s="11"/>
@@ -25955,7 +26254,7 @@
       <c r="N740" s="11"/>
     </row>
     <row r="741" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A741" s="132"/>
+      <c r="A741" s="130"/>
       <c r="B741" s="11"/>
       <c r="C741" s="11"/>
       <c r="D741" s="11"/>
@@ -25979,7 +26278,7 @@
       <c r="N741" s="11"/>
     </row>
     <row r="742" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A742" s="132"/>
+      <c r="A742" s="130"/>
       <c r="B742" s="11"/>
       <c r="C742" s="11"/>
       <c r="D742" s="11"/>
@@ -26003,7 +26302,7 @@
       <c r="N742" s="11"/>
     </row>
     <row r="743" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A743" s="132"/>
+      <c r="A743" s="130"/>
       <c r="B743" s="11"/>
       <c r="C743" s="11"/>
       <c r="D743" s="11"/>
@@ -26027,7 +26326,7 @@
       <c r="N743" s="11"/>
     </row>
     <row r="744" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A744" s="132"/>
+      <c r="A744" s="130"/>
       <c r="B744" s="11"/>
       <c r="C744" s="11"/>
       <c r="D744" s="11" t="s">
@@ -26053,7 +26352,7 @@
       <c r="N744" s="11"/>
     </row>
     <row r="745" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A745" s="132"/>
+      <c r="A745" s="130"/>
       <c r="B745" s="11"/>
       <c r="C745" s="11"/>
       <c r="D745" s="11"/>
@@ -26077,7 +26376,7 @@
       <c r="N745" s="11"/>
     </row>
     <row r="746" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A746" s="132"/>
+      <c r="A746" s="130"/>
       <c r="B746" s="11"/>
       <c r="C746" s="11"/>
       <c r="D746" s="11"/>
@@ -26101,7 +26400,7 @@
       <c r="N746" s="11"/>
     </row>
     <row r="747" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A747" s="132"/>
+      <c r="A747" s="130"/>
       <c r="B747" s="11"/>
       <c r="C747" s="11"/>
       <c r="D747" s="11"/>
@@ -26125,7 +26424,7 @@
       <c r="N747" s="11"/>
     </row>
     <row r="748" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A748" s="132"/>
+      <c r="A748" s="130"/>
       <c r="B748" s="11"/>
       <c r="C748" s="11"/>
       <c r="D748" s="11"/>
@@ -26149,7 +26448,7 @@
       <c r="N748" s="11"/>
     </row>
     <row r="749" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A749" s="132"/>
+      <c r="A749" s="130"/>
       <c r="B749" s="11"/>
       <c r="C749" s="11"/>
       <c r="D749" s="11"/>
@@ -26173,7 +26472,7 @@
       <c r="N749" s="11"/>
     </row>
     <row r="750" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A750" s="132"/>
+      <c r="A750" s="130"/>
       <c r="B750" s="11"/>
       <c r="C750" s="11"/>
       <c r="D750" s="11"/>
@@ -26197,7 +26496,7 @@
       <c r="N750" s="11"/>
     </row>
     <row r="751" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A751" s="132"/>
+      <c r="A751" s="130"/>
       <c r="B751" s="11"/>
       <c r="C751" s="11"/>
       <c r="D751" s="11" t="s">
@@ -26223,7 +26522,7 @@
       <c r="N751" s="11"/>
     </row>
     <row r="752" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A752" s="132"/>
+      <c r="A752" s="130"/>
       <c r="B752" s="11"/>
       <c r="C752" s="11"/>
       <c r="D752" s="11"/>
@@ -26247,7 +26546,7 @@
       <c r="N752" s="11"/>
     </row>
     <row r="753" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A753" s="132"/>
+      <c r="A753" s="130"/>
       <c r="B753" s="11"/>
       <c r="C753" s="11"/>
       <c r="D753" s="11"/>
@@ -26271,7 +26570,7 @@
       <c r="N753" s="11"/>
     </row>
     <row r="754" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A754" s="132"/>
+      <c r="A754" s="130"/>
       <c r="B754" s="11"/>
       <c r="C754" s="11"/>
       <c r="D754" s="11"/>
@@ -26295,7 +26594,7 @@
       <c r="N754" s="11"/>
     </row>
     <row r="755" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A755" s="132"/>
+      <c r="A755" s="130"/>
       <c r="B755" s="11"/>
       <c r="C755" s="11"/>
       <c r="D755" s="11"/>
@@ -26319,7 +26618,7 @@
       <c r="N755" s="11"/>
     </row>
     <row r="756" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A756" s="132"/>
+      <c r="A756" s="130"/>
       <c r="B756" s="11"/>
       <c r="C756" s="11"/>
       <c r="D756" s="11"/>
@@ -26343,7 +26642,7 @@
       <c r="N756" s="11"/>
     </row>
     <row r="757" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A757" s="133"/>
+      <c r="A757" s="131"/>
       <c r="B757" s="11"/>
       <c r="C757" s="11"/>
       <c r="D757" s="11"/>
@@ -26383,7 +26682,7 @@
       <c r="N758" s="11"/>
     </row>
     <row r="759" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A759" s="131">
+      <c r="A759" s="129">
         <v>157</v>
       </c>
       <c r="B759" s="11" t="s">
@@ -26413,7 +26712,7 @@
       <c r="N759" s="11"/>
     </row>
     <row r="760" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A760" s="132"/>
+      <c r="A760" s="130"/>
       <c r="B760" s="11"/>
       <c r="C760" s="11"/>
       <c r="D760" s="11"/>
@@ -26437,7 +26736,7 @@
       <c r="N760" s="11"/>
     </row>
     <row r="761" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A761" s="132"/>
+      <c r="A761" s="130"/>
       <c r="B761" s="11"/>
       <c r="C761" s="11"/>
       <c r="D761" s="11"/>
@@ -26461,7 +26760,7 @@
       <c r="N761" s="11"/>
     </row>
     <row r="762" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A762" s="132"/>
+      <c r="A762" s="130"/>
       <c r="B762" s="11"/>
       <c r="C762" s="11"/>
       <c r="D762" s="11"/>
@@ -26485,7 +26784,7 @@
       <c r="N762" s="11"/>
     </row>
     <row r="763" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A763" s="132"/>
+      <c r="A763" s="130"/>
       <c r="B763" s="11"/>
       <c r="C763" s="11"/>
       <c r="D763" s="11"/>
@@ -26509,7 +26808,7 @@
       <c r="N763" s="11"/>
     </row>
     <row r="764" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A764" s="132"/>
+      <c r="A764" s="130"/>
       <c r="B764" s="11"/>
       <c r="C764" s="11"/>
       <c r="D764" s="11" t="s">
@@ -26535,7 +26834,7 @@
       <c r="N764" s="11"/>
     </row>
     <row r="765" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A765" s="132"/>
+      <c r="A765" s="130"/>
       <c r="B765" s="11"/>
       <c r="C765" s="11"/>
       <c r="D765" s="11"/>
@@ -26559,7 +26858,7 @@
       <c r="N765" s="11"/>
     </row>
     <row r="766" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A766" s="132"/>
+      <c r="A766" s="130"/>
       <c r="B766" s="11"/>
       <c r="C766" s="11"/>
       <c r="D766" s="11"/>
@@ -26583,7 +26882,7 @@
       <c r="N766" s="11"/>
     </row>
     <row r="767" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A767" s="132"/>
+      <c r="A767" s="130"/>
       <c r="B767" s="11"/>
       <c r="C767" s="11"/>
       <c r="D767" s="11"/>
@@ -26607,7 +26906,7 @@
       <c r="N767" s="11"/>
     </row>
     <row r="768" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A768" s="133"/>
+      <c r="A768" s="131"/>
       <c r="B768" s="11"/>
       <c r="C768" s="11"/>
       <c r="D768" s="11"/>
@@ -26647,7 +26946,7 @@
       <c r="N769" s="11"/>
     </row>
     <row r="770" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A770" s="131">
+      <c r="A770" s="129">
         <v>158</v>
       </c>
       <c r="B770" s="11" t="s">
@@ -26677,7 +26976,7 @@
       <c r="N770" s="11"/>
     </row>
     <row r="771" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A771" s="132"/>
+      <c r="A771" s="130"/>
       <c r="B771" s="11"/>
       <c r="C771" s="11"/>
       <c r="D771" s="11"/>
@@ -26701,7 +27000,7 @@
       <c r="N771" s="11"/>
     </row>
     <row r="772" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A772" s="132"/>
+      <c r="A772" s="130"/>
       <c r="B772" s="11"/>
       <c r="C772" s="11"/>
       <c r="D772" s="11"/>
@@ -26725,7 +27024,7 @@
       <c r="N772" s="11"/>
     </row>
     <row r="773" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A773" s="132"/>
+      <c r="A773" s="130"/>
       <c r="B773" s="11"/>
       <c r="C773" s="11"/>
       <c r="D773" s="11"/>
@@ -26749,7 +27048,7 @@
       <c r="N773" s="11"/>
     </row>
     <row r="774" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A774" s="132"/>
+      <c r="A774" s="130"/>
       <c r="B774" s="11"/>
       <c r="C774" s="11"/>
       <c r="D774" s="11"/>
@@ -26773,7 +27072,7 @@
       <c r="N774" s="11"/>
     </row>
     <row r="775" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A775" s="132"/>
+      <c r="A775" s="130"/>
       <c r="B775" s="11"/>
       <c r="C775" s="11"/>
       <c r="D775" s="11" t="s">
@@ -26799,7 +27098,7 @@
       <c r="N775" s="11"/>
     </row>
     <row r="776" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A776" s="132"/>
+      <c r="A776" s="130"/>
       <c r="B776" s="11"/>
       <c r="C776" s="11"/>
       <c r="D776" s="11"/>
@@ -26823,7 +27122,7 @@
       <c r="N776" s="11"/>
     </row>
     <row r="777" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A777" s="132"/>
+      <c r="A777" s="130"/>
       <c r="B777" s="11"/>
       <c r="C777" s="11"/>
       <c r="D777" s="11"/>
@@ -26847,7 +27146,7 @@
       <c r="N777" s="11"/>
     </row>
     <row r="778" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A778" s="132"/>
+      <c r="A778" s="130"/>
       <c r="B778" s="11"/>
       <c r="C778" s="11"/>
       <c r="D778" s="11"/>
@@ -26871,7 +27170,7 @@
       <c r="N778" s="11"/>
     </row>
     <row r="779" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A779" s="132"/>
+      <c r="A779" s="130"/>
       <c r="B779" s="11"/>
       <c r="C779" s="11"/>
       <c r="D779" s="11"/>
@@ -26895,7 +27194,7 @@
       <c r="N779" s="11"/>
     </row>
     <row r="780" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A780" s="132"/>
+      <c r="A780" s="130"/>
       <c r="B780" s="11"/>
       <c r="C780" s="11"/>
       <c r="D780" s="11" t="s">
@@ -26921,7 +27220,7 @@
       <c r="N780" s="11"/>
     </row>
     <row r="781" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A781" s="132"/>
+      <c r="A781" s="130"/>
       <c r="B781" s="11"/>
       <c r="C781" s="11"/>
       <c r="D781" s="11"/>
@@ -26945,7 +27244,7 @@
       <c r="N781" s="11"/>
     </row>
     <row r="782" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A782" s="132"/>
+      <c r="A782" s="130"/>
       <c r="B782" s="11"/>
       <c r="C782" s="11"/>
       <c r="D782" s="11"/>
@@ -26969,7 +27268,7 @@
       <c r="N782" s="11"/>
     </row>
     <row r="783" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A783" s="132"/>
+      <c r="A783" s="130"/>
       <c r="B783" s="11"/>
       <c r="C783" s="11"/>
       <c r="D783" s="11"/>
@@ -26993,7 +27292,7 @@
       <c r="N783" s="11"/>
     </row>
     <row r="784" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A784" s="132"/>
+      <c r="A784" s="130"/>
       <c r="B784" s="11"/>
       <c r="C784" s="11"/>
       <c r="D784" s="11"/>
@@ -27017,7 +27316,7 @@
       <c r="N784" s="11"/>
     </row>
     <row r="785" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A785" s="132"/>
+      <c r="A785" s="130"/>
       <c r="B785" s="11"/>
       <c r="C785" s="11"/>
       <c r="D785" s="11" t="s">
@@ -27043,7 +27342,7 @@
       <c r="N785" s="11"/>
     </row>
     <row r="786" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A786" s="132"/>
+      <c r="A786" s="130"/>
       <c r="B786" s="11"/>
       <c r="C786" s="11"/>
       <c r="D786" s="11"/>
@@ -27067,7 +27366,7 @@
       <c r="N786" s="11"/>
     </row>
     <row r="787" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A787" s="132"/>
+      <c r="A787" s="130"/>
       <c r="B787" s="11"/>
       <c r="C787" s="11"/>
       <c r="D787" s="11"/>
@@ -27091,7 +27390,7 @@
       <c r="N787" s="11"/>
     </row>
     <row r="788" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A788" s="132"/>
+      <c r="A788" s="130"/>
       <c r="B788" s="11"/>
       <c r="C788" s="11"/>
       <c r="D788" s="11"/>
@@ -27115,7 +27414,7 @@
       <c r="N788" s="11"/>
     </row>
     <row r="789" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A789" s="133"/>
+      <c r="A789" s="131"/>
       <c r="B789" s="11"/>
       <c r="C789" s="11"/>
       <c r="D789" s="11"/>
@@ -27155,7 +27454,7 @@
       <c r="N790" s="11"/>
     </row>
     <row r="791" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A791" s="131">
+      <c r="A791" s="129">
         <v>159</v>
       </c>
       <c r="B791" s="11" t="s">
@@ -27185,7 +27484,7 @@
       <c r="N791" s="11"/>
     </row>
     <row r="792" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A792" s="132"/>
+      <c r="A792" s="130"/>
       <c r="B792" s="11"/>
       <c r="C792" s="11"/>
       <c r="D792" s="11"/>
@@ -27209,7 +27508,7 @@
       <c r="N792" s="11"/>
     </row>
     <row r="793" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A793" s="132"/>
+      <c r="A793" s="130"/>
       <c r="B793" s="11"/>
       <c r="C793" s="11"/>
       <c r="D793" s="11"/>
@@ -27233,7 +27532,7 @@
       <c r="N793" s="11"/>
     </row>
     <row r="794" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A794" s="132"/>
+      <c r="A794" s="130"/>
       <c r="B794" s="11"/>
       <c r="C794" s="11"/>
       <c r="D794" s="11"/>
@@ -27257,7 +27556,7 @@
       <c r="N794" s="11"/>
     </row>
     <row r="795" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A795" s="132"/>
+      <c r="A795" s="130"/>
       <c r="B795" s="11"/>
       <c r="C795" s="11"/>
       <c r="D795" s="11"/>
@@ -27281,7 +27580,7 @@
       <c r="N795" s="11"/>
     </row>
     <row r="796" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A796" s="132"/>
+      <c r="A796" s="130"/>
       <c r="B796" s="11"/>
       <c r="C796" s="11"/>
       <c r="D796" s="11" t="s">
@@ -27307,7 +27606,7 @@
       <c r="N796" s="11"/>
     </row>
     <row r="797" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A797" s="132"/>
+      <c r="A797" s="130"/>
       <c r="B797" s="11"/>
       <c r="C797" s="11"/>
       <c r="D797" s="11"/>
@@ -27331,7 +27630,7 @@
       <c r="N797" s="11"/>
     </row>
     <row r="798" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A798" s="132"/>
+      <c r="A798" s="130"/>
       <c r="B798" s="11"/>
       <c r="C798" s="11"/>
       <c r="D798" s="11"/>
@@ -27355,7 +27654,7 @@
       <c r="N798" s="11"/>
     </row>
     <row r="799" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A799" s="132"/>
+      <c r="A799" s="130"/>
       <c r="B799" s="11"/>
       <c r="C799" s="11"/>
       <c r="D799" s="11"/>
@@ -27379,7 +27678,7 @@
       <c r="N799" s="11"/>
     </row>
     <row r="800" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A800" s="133"/>
+      <c r="A800" s="131"/>
       <c r="B800" s="11"/>
       <c r="C800" s="11"/>
       <c r="D800" s="11"/>
@@ -27419,7 +27718,7 @@
       <c r="N801" s="11"/>
     </row>
     <row r="802" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A802" s="131">
+      <c r="A802" s="129">
         <v>160</v>
       </c>
       <c r="B802" s="11" t="s">
@@ -27449,7 +27748,7 @@
       <c r="N802" s="11"/>
     </row>
     <row r="803" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A803" s="132"/>
+      <c r="A803" s="130"/>
       <c r="B803" s="11"/>
       <c r="C803" s="11"/>
       <c r="D803" s="11"/>
@@ -27473,7 +27772,7 @@
       <c r="N803" s="11"/>
     </row>
     <row r="804" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A804" s="132"/>
+      <c r="A804" s="130"/>
       <c r="B804" s="11"/>
       <c r="C804" s="11"/>
       <c r="D804" s="11"/>
@@ -27497,7 +27796,7 @@
       <c r="N804" s="11"/>
     </row>
     <row r="805" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A805" s="132"/>
+      <c r="A805" s="130"/>
       <c r="B805" s="11"/>
       <c r="C805" s="11"/>
       <c r="D805" s="11"/>
@@ -27521,7 +27820,7 @@
       <c r="N805" s="11"/>
     </row>
     <row r="806" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A806" s="132"/>
+      <c r="A806" s="130"/>
       <c r="B806" s="11"/>
       <c r="C806" s="11"/>
       <c r="D806" s="11"/>
@@ -27545,7 +27844,7 @@
       <c r="N806" s="11"/>
     </row>
     <row r="807" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A807" s="132"/>
+      <c r="A807" s="130"/>
       <c r="B807" s="11"/>
       <c r="C807" s="11"/>
       <c r="D807" s="11" t="s">
@@ -27571,7 +27870,7 @@
       <c r="N807" s="11"/>
     </row>
     <row r="808" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A808" s="132"/>
+      <c r="A808" s="130"/>
       <c r="B808" s="11"/>
       <c r="C808" s="11"/>
       <c r="D808" s="11"/>
@@ -27595,7 +27894,7 @@
       <c r="N808" s="11"/>
     </row>
     <row r="809" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A809" s="132"/>
+      <c r="A809" s="130"/>
       <c r="B809" s="11"/>
       <c r="C809" s="11"/>
       <c r="D809" s="11"/>
@@ -27619,7 +27918,7 @@
       <c r="N809" s="11"/>
     </row>
     <row r="810" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A810" s="132"/>
+      <c r="A810" s="130"/>
       <c r="B810" s="11"/>
       <c r="C810" s="11"/>
       <c r="D810" s="11"/>
@@ -27643,7 +27942,7 @@
       <c r="N810" s="11"/>
     </row>
     <row r="811" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A811" s="133"/>
+      <c r="A811" s="131"/>
       <c r="B811" s="11"/>
       <c r="C811" s="11"/>
       <c r="D811" s="11"/>
@@ -27683,7 +27982,7 @@
       <c r="N812" s="11"/>
     </row>
     <row r="813" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A813" s="131">
+      <c r="A813" s="129">
         <v>161</v>
       </c>
       <c r="B813" s="11" t="s">
@@ -27713,7 +28012,7 @@
       <c r="N813" s="11"/>
     </row>
     <row r="814" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A814" s="132"/>
+      <c r="A814" s="130"/>
       <c r="B814" s="11"/>
       <c r="C814" s="11"/>
       <c r="D814" s="11"/>
@@ -27737,7 +28036,7 @@
       <c r="N814" s="11"/>
     </row>
     <row r="815" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A815" s="132"/>
+      <c r="A815" s="130"/>
       <c r="B815" s="11"/>
       <c r="C815" s="11"/>
       <c r="D815" s="11"/>
@@ -27761,7 +28060,7 @@
       <c r="N815" s="11"/>
     </row>
     <row r="816" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A816" s="132"/>
+      <c r="A816" s="130"/>
       <c r="B816" s="11"/>
       <c r="C816" s="11"/>
       <c r="D816" s="11"/>
@@ -27785,7 +28084,7 @@
       <c r="N816" s="11"/>
     </row>
     <row r="817" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A817" s="132"/>
+      <c r="A817" s="130"/>
       <c r="B817" s="11"/>
       <c r="C817" s="11"/>
       <c r="D817" s="11"/>
@@ -27809,7 +28108,7 @@
       <c r="N817" s="11"/>
     </row>
     <row r="818" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A818" s="132"/>
+      <c r="A818" s="130"/>
       <c r="B818" s="11"/>
       <c r="C818" s="11"/>
       <c r="D818" s="11" t="s">
@@ -27835,7 +28134,7 @@
       <c r="N818" s="11"/>
     </row>
     <row r="819" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A819" s="132"/>
+      <c r="A819" s="130"/>
       <c r="B819" s="11"/>
       <c r="C819" s="11"/>
       <c r="D819" s="11"/>
@@ -27859,7 +28158,7 @@
       <c r="N819" s="11"/>
     </row>
     <row r="820" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A820" s="132"/>
+      <c r="A820" s="130"/>
       <c r="B820" s="11"/>
       <c r="C820" s="11"/>
       <c r="D820" s="11"/>
@@ -27883,7 +28182,7 @@
       <c r="N820" s="11"/>
     </row>
     <row r="821" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A821" s="132"/>
+      <c r="A821" s="130"/>
       <c r="B821" s="11"/>
       <c r="C821" s="11"/>
       <c r="D821" s="11"/>
@@ -27907,7 +28206,7 @@
       <c r="N821" s="11"/>
     </row>
     <row r="822" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A822" s="133"/>
+      <c r="A822" s="131"/>
       <c r="B822" s="11"/>
       <c r="C822" s="11"/>
       <c r="D822" s="11"/>
@@ -27947,7 +28246,7 @@
       <c r="N823" s="11"/>
     </row>
     <row r="824" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A824" s="131">
+      <c r="A824" s="129">
         <v>162</v>
       </c>
       <c r="B824" s="11" t="s">
@@ -27977,7 +28276,7 @@
       <c r="N824" s="11"/>
     </row>
     <row r="825" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A825" s="132"/>
+      <c r="A825" s="130"/>
       <c r="B825" s="11"/>
       <c r="C825" s="11"/>
       <c r="D825" s="11"/>
@@ -28001,7 +28300,7 @@
       <c r="N825" s="11"/>
     </row>
     <row r="826" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A826" s="132"/>
+      <c r="A826" s="130"/>
       <c r="B826" s="11"/>
       <c r="C826" s="11"/>
       <c r="D826" s="11"/>
@@ -28025,7 +28324,7 @@
       <c r="N826" s="11"/>
     </row>
     <row r="827" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A827" s="132"/>
+      <c r="A827" s="130"/>
       <c r="B827" s="11"/>
       <c r="C827" s="11"/>
       <c r="D827" s="11"/>
@@ -28049,7 +28348,7 @@
       <c r="N827" s="11"/>
     </row>
     <row r="828" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A828" s="132"/>
+      <c r="A828" s="130"/>
       <c r="B828" s="11"/>
       <c r="C828" s="11"/>
       <c r="D828" s="11"/>
@@ -28073,7 +28372,7 @@
       <c r="N828" s="11"/>
     </row>
     <row r="829" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A829" s="132"/>
+      <c r="A829" s="130"/>
       <c r="B829" s="11"/>
       <c r="C829" s="11"/>
       <c r="D829" s="11" t="s">
@@ -28099,7 +28398,7 @@
       <c r="N829" s="11"/>
     </row>
     <row r="830" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A830" s="132"/>
+      <c r="A830" s="130"/>
       <c r="B830" s="11"/>
       <c r="C830" s="11"/>
       <c r="D830" s="11"/>
@@ -28123,7 +28422,7 @@
       <c r="N830" s="11"/>
     </row>
     <row r="831" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A831" s="132"/>
+      <c r="A831" s="130"/>
       <c r="B831" s="11"/>
       <c r="C831" s="11"/>
       <c r="D831" s="11"/>
@@ -28147,7 +28446,7 @@
       <c r="N831" s="11"/>
     </row>
     <row r="832" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A832" s="132"/>
+      <c r="A832" s="130"/>
       <c r="B832" s="11"/>
       <c r="C832" s="11"/>
       <c r="D832" s="11"/>
@@ -28171,7 +28470,7 @@
       <c r="N832" s="11"/>
     </row>
     <row r="833" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A833" s="133"/>
+      <c r="A833" s="131"/>
       <c r="B833" s="11"/>
       <c r="C833" s="11"/>
       <c r="D833" s="11"/>
@@ -28211,7 +28510,7 @@
       <c r="N834" s="11"/>
     </row>
     <row r="835" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A835" s="131">
+      <c r="A835" s="129">
         <v>163</v>
       </c>
       <c r="B835" s="11" t="s">
@@ -28241,7 +28540,7 @@
       <c r="N835" s="11"/>
     </row>
     <row r="836" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A836" s="132"/>
+      <c r="A836" s="130"/>
       <c r="B836" s="11"/>
       <c r="C836" s="11"/>
       <c r="D836" s="11"/>
@@ -28265,7 +28564,7 @@
       <c r="N836" s="11"/>
     </row>
     <row r="837" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A837" s="132"/>
+      <c r="A837" s="130"/>
       <c r="B837" s="11"/>
       <c r="C837" s="11"/>
       <c r="D837" s="11"/>
@@ -28289,7 +28588,7 @@
       <c r="N837" s="11"/>
     </row>
     <row r="838" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A838" s="132"/>
+      <c r="A838" s="130"/>
       <c r="B838" s="11"/>
       <c r="C838" s="11"/>
       <c r="D838" s="11"/>
@@ -28313,7 +28612,7 @@
       <c r="N838" s="11"/>
     </row>
     <row r="839" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A839" s="132"/>
+      <c r="A839" s="130"/>
       <c r="B839" s="11"/>
       <c r="C839" s="11"/>
       <c r="D839" s="11"/>
@@ -28337,7 +28636,7 @@
       <c r="N839" s="11"/>
     </row>
     <row r="840" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A840" s="132"/>
+      <c r="A840" s="130"/>
       <c r="B840" s="11"/>
       <c r="C840" s="11"/>
       <c r="D840" s="11" t="s">
@@ -28363,7 +28662,7 @@
       <c r="N840" s="11"/>
     </row>
     <row r="841" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A841" s="132"/>
+      <c r="A841" s="130"/>
       <c r="B841" s="11"/>
       <c r="C841" s="11"/>
       <c r="D841" s="11"/>
@@ -28387,7 +28686,7 @@
       <c r="N841" s="11"/>
     </row>
     <row r="842" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A842" s="132"/>
+      <c r="A842" s="130"/>
       <c r="B842" s="11"/>
       <c r="C842" s="11"/>
       <c r="D842" s="11"/>
@@ -28411,7 +28710,7 @@
       <c r="N842" s="11"/>
     </row>
     <row r="843" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A843" s="132"/>
+      <c r="A843" s="130"/>
       <c r="B843" s="11"/>
       <c r="C843" s="11"/>
       <c r="D843" s="11"/>
@@ -28435,7 +28734,7 @@
       <c r="N843" s="11"/>
     </row>
     <row r="844" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A844" s="133"/>
+      <c r="A844" s="131"/>
       <c r="B844" s="11"/>
       <c r="C844" s="11"/>
       <c r="D844" s="11"/>
@@ -28475,7 +28774,7 @@
       <c r="N845" s="11"/>
     </row>
     <row r="846" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A846" s="131">
+      <c r="A846" s="129">
         <v>164</v>
       </c>
       <c r="B846" s="11" t="s">
@@ -28505,7 +28804,7 @@
       <c r="N846" s="11"/>
     </row>
     <row r="847" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A847" s="132"/>
+      <c r="A847" s="130"/>
       <c r="B847" s="11"/>
       <c r="C847" s="11"/>
       <c r="D847" s="11"/>
@@ -28529,7 +28828,7 @@
       <c r="N847" s="11"/>
     </row>
     <row r="848" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A848" s="132"/>
+      <c r="A848" s="130"/>
       <c r="B848" s="11"/>
       <c r="C848" s="11"/>
       <c r="D848" s="11"/>
@@ -28553,7 +28852,7 @@
       <c r="N848" s="11"/>
     </row>
     <row r="849" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A849" s="132"/>
+      <c r="A849" s="130"/>
       <c r="B849" s="11"/>
       <c r="C849" s="11"/>
       <c r="D849" s="11"/>
@@ -28577,7 +28876,7 @@
       <c r="N849" s="11"/>
     </row>
     <row r="850" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A850" s="132"/>
+      <c r="A850" s="130"/>
       <c r="B850" s="11"/>
       <c r="C850" s="11"/>
       <c r="D850" s="11"/>
@@ -28601,7 +28900,7 @@
       <c r="N850" s="11"/>
     </row>
     <row r="851" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A851" s="132"/>
+      <c r="A851" s="130"/>
       <c r="B851" s="11"/>
       <c r="C851" s="11"/>
       <c r="D851" s="11" t="s">
@@ -28627,7 +28926,7 @@
       <c r="N851" s="11"/>
     </row>
     <row r="852" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A852" s="132"/>
+      <c r="A852" s="130"/>
       <c r="B852" s="11"/>
       <c r="C852" s="11"/>
       <c r="D852" s="11"/>
@@ -28651,7 +28950,7 @@
       <c r="N852" s="11"/>
     </row>
     <row r="853" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A853" s="132"/>
+      <c r="A853" s="130"/>
       <c r="B853" s="11"/>
       <c r="C853" s="11"/>
       <c r="D853" s="11"/>
@@ -28675,7 +28974,7 @@
       <c r="N853" s="11"/>
     </row>
     <row r="854" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A854" s="132"/>
+      <c r="A854" s="130"/>
       <c r="B854" s="11"/>
       <c r="C854" s="11"/>
       <c r="D854" s="11"/>
@@ -28699,7 +28998,7 @@
       <c r="N854" s="11"/>
     </row>
     <row r="855" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A855" s="133"/>
+      <c r="A855" s="131"/>
       <c r="B855" s="11"/>
       <c r="C855" s="11"/>
       <c r="D855" s="11"/>
@@ -28739,7 +29038,7 @@
       <c r="N856" s="11"/>
     </row>
     <row r="857" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A857" s="131">
+      <c r="A857" s="129">
         <v>165</v>
       </c>
       <c r="B857" s="11" t="s">
@@ -28769,7 +29068,7 @@
       <c r="N857" s="11"/>
     </row>
     <row r="858" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A858" s="132"/>
+      <c r="A858" s="130"/>
       <c r="B858" s="11"/>
       <c r="C858" s="11"/>
       <c r="D858" s="11"/>
@@ -28793,7 +29092,7 @@
       <c r="N858" s="11"/>
     </row>
     <row r="859" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A859" s="132"/>
+      <c r="A859" s="130"/>
       <c r="B859" s="11"/>
       <c r="C859" s="11"/>
       <c r="D859" s="11" t="s">
@@ -28819,7 +29118,7 @@
       <c r="N859" s="11"/>
     </row>
     <row r="860" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A860" s="132"/>
+      <c r="A860" s="130"/>
       <c r="B860" s="11"/>
       <c r="C860" s="11"/>
       <c r="D860" s="11"/>
@@ -28843,7 +29142,7 @@
       <c r="N860" s="11"/>
     </row>
     <row r="861" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A861" s="132"/>
+      <c r="A861" s="130"/>
       <c r="B861" s="11"/>
       <c r="C861" s="11"/>
       <c r="D861" s="11" t="s">
@@ -28869,7 +29168,7 @@
       <c r="N861" s="11"/>
     </row>
     <row r="862" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A862" s="132"/>
+      <c r="A862" s="130"/>
       <c r="B862" s="11"/>
       <c r="C862" s="11"/>
       <c r="D862" s="11"/>
@@ -28893,7 +29192,7 @@
       <c r="N862" s="11"/>
     </row>
     <row r="863" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A863" s="132"/>
+      <c r="A863" s="130"/>
       <c r="B863" s="11"/>
       <c r="C863" s="11"/>
       <c r="D863" s="11" t="s">
@@ -28919,7 +29218,7 @@
       <c r="N863" s="11"/>
     </row>
     <row r="864" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A864" s="132"/>
+      <c r="A864" s="130"/>
       <c r="B864" s="11"/>
       <c r="C864" s="11"/>
       <c r="D864" s="11"/>
@@ -28943,7 +29242,7 @@
       <c r="N864" s="11"/>
     </row>
     <row r="865" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A865" s="132"/>
+      <c r="A865" s="130"/>
       <c r="B865" s="11"/>
       <c r="C865" s="11"/>
       <c r="D865" s="11" t="s">
@@ -28969,7 +29268,7 @@
       <c r="N865" s="11"/>
     </row>
     <row r="866" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A866" s="132"/>
+      <c r="A866" s="130"/>
       <c r="B866" s="11"/>
       <c r="C866" s="11"/>
       <c r="D866" s="11"/>
@@ -28993,7 +29292,7 @@
       <c r="N866" s="11"/>
     </row>
     <row r="867" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A867" s="132"/>
+      <c r="A867" s="130"/>
       <c r="B867" s="11"/>
       <c r="C867" s="11"/>
       <c r="D867" s="11" t="s">
@@ -29019,7 +29318,7 @@
       <c r="N867" s="11"/>
     </row>
     <row r="868" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A868" s="132"/>
+      <c r="A868" s="130"/>
       <c r="B868" s="11"/>
       <c r="C868" s="11"/>
       <c r="D868" s="11"/>
@@ -29043,7 +29342,7 @@
       <c r="N868" s="11"/>
     </row>
     <row r="869" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A869" s="132"/>
+      <c r="A869" s="130"/>
       <c r="B869" s="11"/>
       <c r="C869" s="11"/>
       <c r="D869" s="11" t="s">
@@ -29069,7 +29368,7 @@
       <c r="N869" s="11"/>
     </row>
     <row r="870" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A870" s="132"/>
+      <c r="A870" s="130"/>
       <c r="B870" s="11"/>
       <c r="C870" s="11"/>
       <c r="D870" s="11"/>
@@ -29093,7 +29392,7 @@
       <c r="N870" s="11"/>
     </row>
     <row r="871" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A871" s="132"/>
+      <c r="A871" s="130"/>
       <c r="B871" s="11"/>
       <c r="C871" s="11"/>
       <c r="D871" s="11" t="s">
@@ -29119,7 +29418,7 @@
       <c r="N871" s="11"/>
     </row>
     <row r="872" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A872" s="133"/>
+      <c r="A872" s="131"/>
       <c r="B872" s="11"/>
       <c r="C872" s="11"/>
       <c r="D872" s="11"/>
@@ -29159,7 +29458,7 @@
       <c r="N873" s="11"/>
     </row>
     <row r="874" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A874" s="131">
+      <c r="A874" s="129">
         <v>166</v>
       </c>
       <c r="B874" s="11" t="s">
@@ -29189,7 +29488,7 @@
       <c r="N874" s="11"/>
     </row>
     <row r="875" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A875" s="132"/>
+      <c r="A875" s="130"/>
       <c r="B875" s="11"/>
       <c r="C875" s="11"/>
       <c r="D875" s="11"/>
@@ -29213,7 +29512,7 @@
       <c r="N875" s="11"/>
     </row>
     <row r="876" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A876" s="132"/>
+      <c r="A876" s="130"/>
       <c r="B876" s="11"/>
       <c r="C876" s="11"/>
       <c r="D876" s="11"/>
@@ -29237,7 +29536,7 @@
       <c r="N876" s="11"/>
     </row>
     <row r="877" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A877" s="132"/>
+      <c r="A877" s="130"/>
       <c r="B877" s="11"/>
       <c r="C877" s="11"/>
       <c r="D877" s="11"/>
@@ -29261,7 +29560,7 @@
       <c r="N877" s="11"/>
     </row>
     <row r="878" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A878" s="132"/>
+      <c r="A878" s="130"/>
       <c r="B878" s="11"/>
       <c r="C878" s="11"/>
       <c r="D878" s="11"/>
@@ -29285,7 +29584,7 @@
       <c r="N878" s="11"/>
     </row>
     <row r="879" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A879" s="132"/>
+      <c r="A879" s="130"/>
       <c r="B879" s="11"/>
       <c r="C879" s="11"/>
       <c r="D879" s="11" t="s">
@@ -29311,7 +29610,7 @@
       <c r="N879" s="11"/>
     </row>
     <row r="880" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A880" s="132"/>
+      <c r="A880" s="130"/>
       <c r="B880" s="11"/>
       <c r="C880" s="11"/>
       <c r="D880" s="11"/>
@@ -29335,7 +29634,7 @@
       <c r="N880" s="11"/>
     </row>
     <row r="881" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A881" s="132"/>
+      <c r="A881" s="130"/>
       <c r="B881" s="11"/>
       <c r="C881" s="11"/>
       <c r="D881" s="11"/>
@@ -29359,7 +29658,7 @@
       <c r="N881" s="11"/>
     </row>
     <row r="882" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A882" s="132"/>
+      <c r="A882" s="130"/>
       <c r="B882" s="11"/>
       <c r="C882" s="11"/>
       <c r="D882" s="11"/>
@@ -29383,7 +29682,7 @@
       <c r="N882" s="11"/>
     </row>
     <row r="883" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A883" s="132"/>
+      <c r="A883" s="130"/>
       <c r="B883" s="11"/>
       <c r="C883" s="11"/>
       <c r="D883" s="11"/>
@@ -29407,7 +29706,7 @@
       <c r="N883" s="11"/>
     </row>
     <row r="884" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A884" s="132"/>
+      <c r="A884" s="130"/>
       <c r="B884" s="11"/>
       <c r="C884" s="11"/>
       <c r="D884" s="11" t="s">
@@ -29433,7 +29732,7 @@
       <c r="N884" s="11"/>
     </row>
     <row r="885" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A885" s="132"/>
+      <c r="A885" s="130"/>
       <c r="B885" s="11"/>
       <c r="C885" s="11"/>
       <c r="D885" s="11"/>
@@ -29457,7 +29756,7 @@
       <c r="N885" s="11"/>
     </row>
     <row r="886" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A886" s="132"/>
+      <c r="A886" s="130"/>
       <c r="B886" s="11"/>
       <c r="C886" s="11"/>
       <c r="D886" s="11"/>
@@ -29481,7 +29780,7 @@
       <c r="N886" s="11"/>
     </row>
     <row r="887" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A887" s="132"/>
+      <c r="A887" s="130"/>
       <c r="B887" s="11"/>
       <c r="C887" s="11"/>
       <c r="D887" s="11"/>
@@ -29505,7 +29804,7 @@
       <c r="N887" s="11"/>
     </row>
     <row r="888" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A888" s="132"/>
+      <c r="A888" s="130"/>
       <c r="B888" s="11"/>
       <c r="C888" s="11"/>
       <c r="D888" s="11"/>
@@ -29529,7 +29828,7 @@
       <c r="N888" s="11"/>
     </row>
     <row r="889" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A889" s="132"/>
+      <c r="A889" s="130"/>
       <c r="B889" s="11"/>
       <c r="C889" s="11"/>
       <c r="D889" s="11" t="s">
@@ -29555,7 +29854,7 @@
       <c r="N889" s="11"/>
     </row>
     <row r="890" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A890" s="132"/>
+      <c r="A890" s="130"/>
       <c r="B890" s="11"/>
       <c r="C890" s="11"/>
       <c r="D890" s="11"/>
@@ -29579,7 +29878,7 @@
       <c r="N890" s="11"/>
     </row>
     <row r="891" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A891" s="132"/>
+      <c r="A891" s="130"/>
       <c r="B891" s="11"/>
       <c r="C891" s="11"/>
       <c r="D891" s="11"/>
@@ -29603,7 +29902,7 @@
       <c r="N891" s="11"/>
     </row>
     <row r="892" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A892" s="132"/>
+      <c r="A892" s="130"/>
       <c r="B892" s="11"/>
       <c r="C892" s="11"/>
       <c r="D892" s="11"/>
@@ -29627,7 +29926,7 @@
       <c r="N892" s="11"/>
     </row>
     <row r="893" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A893" s="132"/>
+      <c r="A893" s="130"/>
       <c r="B893" s="11"/>
       <c r="C893" s="11"/>
       <c r="D893" s="11"/>
@@ -29651,7 +29950,7 @@
       <c r="N893" s="11"/>
     </row>
     <row r="894" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A894" s="132"/>
+      <c r="A894" s="130"/>
       <c r="B894" s="11"/>
       <c r="C894" s="11"/>
       <c r="D894" s="11" t="s">
@@ -29677,7 +29976,7 @@
       <c r="N894" s="11"/>
     </row>
     <row r="895" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A895" s="132"/>
+      <c r="A895" s="130"/>
       <c r="B895" s="11"/>
       <c r="C895" s="11"/>
       <c r="D895" s="11"/>
@@ -29701,7 +30000,7 @@
       <c r="N895" s="11"/>
     </row>
     <row r="896" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A896" s="132"/>
+      <c r="A896" s="130"/>
       <c r="B896" s="11"/>
       <c r="C896" s="11"/>
       <c r="D896" s="11"/>
@@ -29725,7 +30024,7 @@
       <c r="N896" s="11"/>
     </row>
     <row r="897" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A897" s="132"/>
+      <c r="A897" s="130"/>
       <c r="B897" s="11"/>
       <c r="C897" s="11"/>
       <c r="D897" s="11"/>
@@ -29749,7 +30048,7 @@
       <c r="N897" s="11"/>
     </row>
     <row r="898" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A898" s="133"/>
+      <c r="A898" s="131"/>
       <c r="B898" s="11"/>
       <c r="C898" s="11"/>
       <c r="D898" s="11"/>
@@ -29789,7 +30088,7 @@
       <c r="N899" s="11"/>
     </row>
     <row r="900" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A900" s="131">
+      <c r="A900" s="129">
         <v>167</v>
       </c>
       <c r="B900" s="11" t="s">
@@ -29819,7 +30118,7 @@
       <c r="N900" s="11"/>
     </row>
     <row r="901" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A901" s="132"/>
+      <c r="A901" s="130"/>
       <c r="B901" s="11"/>
       <c r="C901" s="11"/>
       <c r="D901" s="11"/>
@@ -29843,7 +30142,7 @@
       <c r="N901" s="11"/>
     </row>
     <row r="902" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A902" s="132"/>
+      <c r="A902" s="130"/>
       <c r="B902" s="11"/>
       <c r="C902" s="11"/>
       <c r="D902" s="11"/>
@@ -29867,7 +30166,7 @@
       <c r="N902" s="11"/>
     </row>
     <row r="903" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A903" s="132"/>
+      <c r="A903" s="130"/>
       <c r="B903" s="11"/>
       <c r="C903" s="11"/>
       <c r="D903" s="11"/>
@@ -29891,7 +30190,7 @@
       <c r="N903" s="11"/>
     </row>
     <row r="904" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A904" s="132"/>
+      <c r="A904" s="130"/>
       <c r="B904" s="11"/>
       <c r="C904" s="11"/>
       <c r="D904" s="11"/>
@@ -29915,7 +30214,7 @@
       <c r="N904" s="11"/>
     </row>
     <row r="905" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A905" s="132"/>
+      <c r="A905" s="130"/>
       <c r="B905" s="11"/>
       <c r="C905" s="11"/>
       <c r="D905" s="11" t="s">
@@ -29941,7 +30240,7 @@
       <c r="N905" s="11"/>
     </row>
     <row r="906" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A906" s="132"/>
+      <c r="A906" s="130"/>
       <c r="B906" s="11"/>
       <c r="C906" s="11"/>
       <c r="D906" s="11"/>
@@ -29965,7 +30264,7 @@
       <c r="N906" s="11"/>
     </row>
     <row r="907" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A907" s="132"/>
+      <c r="A907" s="130"/>
       <c r="B907" s="11"/>
       <c r="C907" s="11"/>
       <c r="D907" s="11"/>
@@ -29989,7 +30288,7 @@
       <c r="N907" s="11"/>
     </row>
     <row r="908" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A908" s="132"/>
+      <c r="A908" s="130"/>
       <c r="B908" s="11"/>
       <c r="C908" s="11"/>
       <c r="D908" s="11"/>
@@ -30013,7 +30312,7 @@
       <c r="N908" s="11"/>
     </row>
     <row r="909" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A909" s="132"/>
+      <c r="A909" s="130"/>
       <c r="B909" s="11"/>
       <c r="C909" s="11"/>
       <c r="D909" s="11"/>
@@ -30037,7 +30336,7 @@
       <c r="N909" s="11"/>
     </row>
     <row r="910" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A910" s="132"/>
+      <c r="A910" s="130"/>
       <c r="B910" s="11"/>
       <c r="C910" s="11"/>
       <c r="D910" s="11" t="s">
@@ -30063,7 +30362,7 @@
       <c r="N910" s="11"/>
     </row>
     <row r="911" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A911" s="132"/>
+      <c r="A911" s="130"/>
       <c r="B911" s="11"/>
       <c r="C911" s="11"/>
       <c r="D911" s="11"/>
@@ -30087,7 +30386,7 @@
       <c r="N911" s="11"/>
     </row>
     <row r="912" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A912" s="132"/>
+      <c r="A912" s="130"/>
       <c r="B912" s="11"/>
       <c r="C912" s="11"/>
       <c r="D912" s="11"/>
@@ -30111,7 +30410,7 @@
       <c r="N912" s="11"/>
     </row>
     <row r="913" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A913" s="132"/>
+      <c r="A913" s="130"/>
       <c r="B913" s="11"/>
       <c r="C913" s="11"/>
       <c r="D913" s="11"/>
@@ -30135,7 +30434,7 @@
       <c r="N913" s="11"/>
     </row>
     <row r="914" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A914" s="132"/>
+      <c r="A914" s="130"/>
       <c r="B914" s="11"/>
       <c r="C914" s="11"/>
       <c r="D914" s="11"/>
@@ -30159,7 +30458,7 @@
       <c r="N914" s="11"/>
     </row>
     <row r="915" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A915" s="132"/>
+      <c r="A915" s="130"/>
       <c r="B915" s="11"/>
       <c r="C915" s="11"/>
       <c r="D915" s="11" t="s">
@@ -30185,7 +30484,7 @@
       <c r="N915" s="11"/>
     </row>
     <row r="916" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A916" s="132"/>
+      <c r="A916" s="130"/>
       <c r="B916" s="11"/>
       <c r="C916" s="11"/>
       <c r="D916" s="11"/>
@@ -30209,7 +30508,7 @@
       <c r="N916" s="11"/>
     </row>
     <row r="917" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A917" s="132"/>
+      <c r="A917" s="130"/>
       <c r="B917" s="11"/>
       <c r="C917" s="11"/>
       <c r="D917" s="11"/>
@@ -30233,7 +30532,7 @@
       <c r="N917" s="11"/>
     </row>
     <row r="918" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A918" s="132"/>
+      <c r="A918" s="130"/>
       <c r="B918" s="11"/>
       <c r="C918" s="11"/>
       <c r="D918" s="11"/>
@@ -30257,7 +30556,7 @@
       <c r="N918" s="11"/>
     </row>
     <row r="919" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A919" s="132"/>
+      <c r="A919" s="130"/>
       <c r="B919" s="11"/>
       <c r="C919" s="11"/>
       <c r="D919" s="11"/>
@@ -30281,7 +30580,7 @@
       <c r="N919" s="11"/>
     </row>
     <row r="920" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A920" s="132"/>
+      <c r="A920" s="130"/>
       <c r="B920" s="11"/>
       <c r="C920" s="11"/>
       <c r="D920" s="11" t="s">
@@ -30307,7 +30606,7 @@
       <c r="N920" s="11"/>
     </row>
     <row r="921" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A921" s="132"/>
+      <c r="A921" s="130"/>
       <c r="B921" s="11"/>
       <c r="C921" s="11"/>
       <c r="D921" s="11"/>
@@ -30331,7 +30630,7 @@
       <c r="N921" s="11"/>
     </row>
     <row r="922" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A922" s="132"/>
+      <c r="A922" s="130"/>
       <c r="B922" s="11"/>
       <c r="C922" s="11"/>
       <c r="D922" s="11"/>
@@ -30355,7 +30654,7 @@
       <c r="N922" s="11"/>
     </row>
     <row r="923" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A923" s="132"/>
+      <c r="A923" s="130"/>
       <c r="B923" s="11"/>
       <c r="C923" s="11"/>
       <c r="D923" s="11"/>
@@ -30379,7 +30678,7 @@
       <c r="N923" s="11"/>
     </row>
     <row r="924" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A924" s="133"/>
+      <c r="A924" s="131"/>
       <c r="B924" s="11"/>
       <c r="C924" s="11"/>
       <c r="D924" s="11"/>
@@ -30419,7 +30718,7 @@
       <c r="N925" s="11"/>
     </row>
     <row r="926" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A926" s="131">
+      <c r="A926" s="129">
         <v>168</v>
       </c>
       <c r="B926" s="11" t="s">
@@ -30449,7 +30748,7 @@
       <c r="N926" s="11"/>
     </row>
     <row r="927" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A927" s="133"/>
+      <c r="A927" s="131"/>
       <c r="B927" s="11"/>
       <c r="C927" s="11"/>
       <c r="D927" s="11"/>
@@ -30581,7 +30880,7 @@
       <c r="N932" s="11"/>
     </row>
     <row r="933" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A933" s="131">
+      <c r="A933" s="129">
         <v>171</v>
       </c>
       <c r="B933" s="11" t="s">
@@ -30611,7 +30910,7 @@
       <c r="N933" s="11"/>
     </row>
     <row r="934" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A934" s="133"/>
+      <c r="A934" s="131"/>
       <c r="B934" s="11"/>
       <c r="C934" s="11"/>
       <c r="D934" s="11"/>
@@ -30651,7 +30950,7 @@
       <c r="N935" s="11"/>
     </row>
     <row r="936" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A936" s="131">
+      <c r="A936" s="129">
         <v>172</v>
       </c>
       <c r="B936" s="11" t="s">
@@ -30681,7 +30980,7 @@
       <c r="N936" s="11"/>
     </row>
     <row r="937" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A937" s="132"/>
+      <c r="A937" s="130"/>
       <c r="B937" s="11"/>
       <c r="C937" s="11"/>
       <c r="D937" s="11"/>
@@ -30705,7 +31004,7 @@
       <c r="N937" s="11"/>
     </row>
     <row r="938" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A938" s="132"/>
+      <c r="A938" s="130"/>
       <c r="B938" s="11"/>
       <c r="C938" s="11"/>
       <c r="D938" s="11"/>
@@ -30729,7 +31028,7 @@
       <c r="N938" s="11"/>
     </row>
     <row r="939" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A939" s="132"/>
+      <c r="A939" s="130"/>
       <c r="B939" s="11"/>
       <c r="C939" s="11"/>
       <c r="D939" s="11"/>
@@ -30753,7 +31052,7 @@
       <c r="N939" s="11"/>
     </row>
     <row r="940" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A940" s="132"/>
+      <c r="A940" s="130"/>
       <c r="B940" s="11"/>
       <c r="C940" s="11"/>
       <c r="D940" s="11"/>
@@ -30777,7 +31076,7 @@
       <c r="N940" s="11"/>
     </row>
     <row r="941" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A941" s="132"/>
+      <c r="A941" s="130"/>
       <c r="B941" s="11"/>
       <c r="C941" s="11"/>
       <c r="D941" s="11" t="s">
@@ -30803,7 +31102,7 @@
       <c r="N941" s="11"/>
     </row>
     <row r="942" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A942" s="132"/>
+      <c r="A942" s="130"/>
       <c r="B942" s="11"/>
       <c r="C942" s="11"/>
       <c r="D942" s="11"/>
@@ -30827,7 +31126,7 @@
       <c r="N942" s="11"/>
     </row>
     <row r="943" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A943" s="132"/>
+      <c r="A943" s="130"/>
       <c r="B943" s="11"/>
       <c r="C943" s="11"/>
       <c r="D943" s="11"/>
@@ -30851,7 +31150,7 @@
       <c r="N943" s="11"/>
     </row>
     <row r="944" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A944" s="132"/>
+      <c r="A944" s="130"/>
       <c r="B944" s="11"/>
       <c r="C944" s="11"/>
       <c r="D944" s="11"/>
@@ -30875,7 +31174,7 @@
       <c r="N944" s="11"/>
     </row>
     <row r="945" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A945" s="132"/>
+      <c r="A945" s="130"/>
       <c r="B945" s="11"/>
       <c r="C945" s="11"/>
       <c r="D945" s="11"/>
@@ -30899,7 +31198,7 @@
       <c r="N945" s="11"/>
     </row>
     <row r="946" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A946" s="132"/>
+      <c r="A946" s="130"/>
       <c r="B946" s="11"/>
       <c r="C946" s="11"/>
       <c r="D946" s="11" t="s">
@@ -30925,7 +31224,7 @@
       <c r="N946" s="11"/>
     </row>
     <row r="947" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A947" s="132"/>
+      <c r="A947" s="130"/>
       <c r="B947" s="11"/>
       <c r="C947" s="11"/>
       <c r="D947" s="11"/>
@@ -30949,7 +31248,7 @@
       <c r="N947" s="11"/>
     </row>
     <row r="948" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A948" s="132"/>
+      <c r="A948" s="130"/>
       <c r="B948" s="11"/>
       <c r="C948" s="11"/>
       <c r="D948" s="11"/>
@@ -30973,7 +31272,7 @@
       <c r="N948" s="11"/>
     </row>
     <row r="949" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A949" s="132"/>
+      <c r="A949" s="130"/>
       <c r="B949" s="11"/>
       <c r="C949" s="11"/>
       <c r="D949" s="11"/>
@@ -30997,7 +31296,7 @@
       <c r="N949" s="11"/>
     </row>
     <row r="950" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A950" s="132"/>
+      <c r="A950" s="130"/>
       <c r="B950" s="11"/>
       <c r="C950" s="11"/>
       <c r="D950" s="11"/>
@@ -31021,7 +31320,7 @@
       <c r="N950" s="11"/>
     </row>
     <row r="951" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A951" s="132"/>
+      <c r="A951" s="130"/>
       <c r="B951" s="11"/>
       <c r="C951" s="11"/>
       <c r="D951" s="11" t="s">
@@ -31047,7 +31346,7 @@
       <c r="N951" s="11"/>
     </row>
     <row r="952" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A952" s="132"/>
+      <c r="A952" s="130"/>
       <c r="B952" s="11"/>
       <c r="C952" s="11"/>
       <c r="D952" s="11"/>
@@ -31071,7 +31370,7 @@
       <c r="N952" s="11"/>
     </row>
     <row r="953" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A953" s="132"/>
+      <c r="A953" s="130"/>
       <c r="B953" s="11"/>
       <c r="C953" s="11"/>
       <c r="D953" s="11"/>
@@ -31095,7 +31394,7 @@
       <c r="N953" s="11"/>
     </row>
     <row r="954" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A954" s="132"/>
+      <c r="A954" s="130"/>
       <c r="B954" s="11"/>
       <c r="C954" s="11"/>
       <c r="D954" s="11"/>
@@ -31119,7 +31418,7 @@
       <c r="N954" s="11"/>
     </row>
     <row r="955" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A955" s="133"/>
+      <c r="A955" s="131"/>
       <c r="B955" s="11"/>
       <c r="C955" s="11"/>
       <c r="D955" s="11"/>
@@ -31159,7 +31458,7 @@
       <c r="N956" s="11"/>
     </row>
     <row r="957" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A957" s="142">
+      <c r="A957" s="140">
         <v>173</v>
       </c>
       <c r="B957" s="11" t="s">
@@ -31191,7 +31490,7 @@
       </c>
     </row>
     <row r="958" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A958" s="133"/>
+      <c r="A958" s="131"/>
       <c r="B958" s="11"/>
       <c r="C958" s="11"/>
       <c r="D958" s="11"/>
@@ -31231,7 +31530,7 @@
       <c r="N959" s="11"/>
     </row>
     <row r="960" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A960" s="131">
+      <c r="A960" s="129">
         <v>174</v>
       </c>
       <c r="B960" s="11" t="s">
@@ -31263,7 +31562,7 @@
       </c>
     </row>
     <row r="961" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A961" s="133"/>
+      <c r="A961" s="131"/>
       <c r="B961" s="11"/>
       <c r="C961" s="11"/>
       <c r="D961" s="11"/>
@@ -31303,7 +31602,7 @@
       <c r="N962" s="11"/>
     </row>
     <row r="963" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A963" s="131">
+      <c r="A963" s="129">
         <v>175</v>
       </c>
       <c r="B963" s="11" t="s">
@@ -31333,7 +31632,7 @@
       <c r="N963" s="11"/>
     </row>
     <row r="964" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A964" s="132"/>
+      <c r="A964" s="130"/>
       <c r="B964" s="11"/>
       <c r="C964" s="11"/>
       <c r="D964" s="11"/>
@@ -31357,7 +31656,7 @@
       <c r="N964" s="11"/>
     </row>
     <row r="965" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A965" s="132"/>
+      <c r="A965" s="130"/>
       <c r="B965" s="11"/>
       <c r="C965" s="11"/>
       <c r="D965" s="11"/>
@@ -31381,7 +31680,7 @@
       <c r="N965" s="11"/>
     </row>
     <row r="966" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A966" s="132"/>
+      <c r="A966" s="130"/>
       <c r="B966" s="11"/>
       <c r="C966" s="11"/>
       <c r="D966" s="11"/>
@@ -31405,7 +31704,7 @@
       <c r="N966" s="11"/>
     </row>
     <row r="967" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A967" s="133"/>
+      <c r="A967" s="131"/>
       <c r="B967" s="11"/>
       <c r="C967" s="11"/>
       <c r="D967" s="11"/>
@@ -31445,7 +31744,7 @@
       <c r="N968" s="11"/>
     </row>
     <row r="969" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A969" s="131">
+      <c r="A969" s="129">
         <v>176</v>
       </c>
       <c r="B969" s="11" t="s">
@@ -31475,7 +31774,7 @@
       <c r="N969" s="11"/>
     </row>
     <row r="970" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A970" s="132"/>
+      <c r="A970" s="130"/>
       <c r="B970" s="11"/>
       <c r="C970" s="11"/>
       <c r="D970" s="11"/>
@@ -31499,7 +31798,7 @@
       <c r="N970" s="11"/>
     </row>
     <row r="971" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A971" s="132"/>
+      <c r="A971" s="130"/>
       <c r="B971" s="11"/>
       <c r="C971" s="11"/>
       <c r="D971" s="11"/>
@@ -31523,7 +31822,7 @@
       <c r="N971" s="11"/>
     </row>
     <row r="972" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A972" s="132"/>
+      <c r="A972" s="130"/>
       <c r="B972" s="11"/>
       <c r="C972" s="11"/>
       <c r="D972" s="11"/>
@@ -31547,7 +31846,7 @@
       <c r="N972" s="11"/>
     </row>
     <row r="973" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A973" s="133"/>
+      <c r="A973" s="131"/>
       <c r="B973" s="11"/>
       <c r="C973" s="11"/>
       <c r="D973" s="11"/>
@@ -31587,7 +31886,7 @@
       <c r="N974" s="11"/>
     </row>
     <row r="975" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A975" s="131">
+      <c r="A975" s="129">
         <v>177</v>
       </c>
       <c r="B975" s="11" t="s">
@@ -31617,7 +31916,7 @@
       <c r="N975" s="11"/>
     </row>
     <row r="976" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A976" s="133"/>
+      <c r="A976" s="131"/>
       <c r="B976" s="11"/>
       <c r="C976" s="11"/>
       <c r="D976" s="11" t="s">
@@ -31659,7 +31958,7 @@
       <c r="N977" s="11"/>
     </row>
     <row r="978" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A978" s="131">
+      <c r="A978" s="129">
         <v>178</v>
       </c>
       <c r="B978" s="11" t="s">
@@ -31689,7 +31988,7 @@
       <c r="N978" s="11"/>
     </row>
     <row r="979" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A979" s="132"/>
+      <c r="A979" s="130"/>
       <c r="B979" s="11"/>
       <c r="C979" s="11"/>
       <c r="D979" s="11"/>
@@ -31713,7 +32012,7 @@
       <c r="N979" s="11"/>
     </row>
     <row r="980" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A980" s="132"/>
+      <c r="A980" s="130"/>
       <c r="B980" s="11"/>
       <c r="C980" s="11"/>
       <c r="D980" s="11" t="s">
@@ -31739,7 +32038,7 @@
       <c r="N980" s="11"/>
     </row>
     <row r="981" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A981" s="133"/>
+      <c r="A981" s="131"/>
       <c r="B981" s="11"/>
       <c r="C981" s="11"/>
       <c r="D981" s="11"/>
@@ -31779,7 +32078,7 @@
       <c r="N982" s="11"/>
     </row>
     <row r="983" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A983" s="131">
+      <c r="A983" s="129">
         <v>179</v>
       </c>
       <c r="B983" s="11" t="s">
@@ -31809,7 +32108,7 @@
       <c r="N983" s="11"/>
     </row>
     <row r="984" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A984" s="132"/>
+      <c r="A984" s="130"/>
       <c r="B984" s="11"/>
       <c r="C984" s="11"/>
       <c r="D984" s="11"/>
@@ -31833,7 +32132,7 @@
       <c r="N984" s="11"/>
     </row>
     <row r="985" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A985" s="132"/>
+      <c r="A985" s="130"/>
       <c r="B985" s="11"/>
       <c r="C985" s="11"/>
       <c r="D985" s="11"/>
@@ -31857,7 +32156,7 @@
       <c r="N985" s="11"/>
     </row>
     <row r="986" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A986" s="132"/>
+      <c r="A986" s="130"/>
       <c r="B986" s="11"/>
       <c r="C986" s="11"/>
       <c r="D986" s="11"/>
@@ -31881,7 +32180,7 @@
       <c r="N986" s="11"/>
     </row>
     <row r="987" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A987" s="132"/>
+      <c r="A987" s="130"/>
       <c r="B987" s="11"/>
       <c r="C987" s="11"/>
       <c r="D987" s="11"/>
@@ -31905,7 +32204,7 @@
       <c r="N987" s="11"/>
     </row>
     <row r="988" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A988" s="132"/>
+      <c r="A988" s="130"/>
       <c r="B988" s="11"/>
       <c r="C988" s="11"/>
       <c r="D988" s="11" t="s">
@@ -31931,7 +32230,7 @@
       <c r="N988" s="11"/>
     </row>
     <row r="989" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A989" s="132"/>
+      <c r="A989" s="130"/>
       <c r="B989" s="11"/>
       <c r="C989" s="11"/>
       <c r="D989" s="11"/>
@@ -31955,7 +32254,7 @@
       <c r="N989" s="11"/>
     </row>
     <row r="990" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A990" s="132"/>
+      <c r="A990" s="130"/>
       <c r="B990" s="11"/>
       <c r="C990" s="11"/>
       <c r="D990" s="11"/>
@@ -31979,7 +32278,7 @@
       <c r="N990" s="11"/>
     </row>
     <row r="991" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A991" s="132"/>
+      <c r="A991" s="130"/>
       <c r="B991" s="11"/>
       <c r="C991" s="11"/>
       <c r="D991" s="11"/>
@@ -32003,7 +32302,7 @@
       <c r="N991" s="11"/>
     </row>
     <row r="992" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A992" s="133"/>
+      <c r="A992" s="131"/>
       <c r="B992" s="11"/>
       <c r="C992" s="11"/>
       <c r="D992" s="11"/>
@@ -32135,7 +32434,7 @@
       <c r="N997" s="11"/>
     </row>
     <row r="998" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A998" s="131">
+      <c r="A998" s="129">
         <v>182</v>
       </c>
       <c r="B998" s="11" t="s">
@@ -32165,7 +32464,7 @@
       <c r="N998" s="11"/>
     </row>
     <row r="999" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A999" s="132"/>
+      <c r="A999" s="130"/>
       <c r="B999" s="11"/>
       <c r="C999" s="11"/>
       <c r="D999" s="11"/>
@@ -32189,7 +32488,7 @@
       <c r="N999" s="11"/>
     </row>
     <row r="1000" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1000" s="132"/>
+      <c r="A1000" s="130"/>
       <c r="B1000" s="11"/>
       <c r="C1000" s="11"/>
       <c r="D1000" s="11"/>
@@ -32213,7 +32512,7 @@
       <c r="N1000" s="11"/>
     </row>
     <row r="1001" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1001" s="132"/>
+      <c r="A1001" s="130"/>
       <c r="B1001" s="11"/>
       <c r="C1001" s="11"/>
       <c r="D1001" s="11"/>
@@ -32237,7 +32536,7 @@
       <c r="N1001" s="11"/>
     </row>
     <row r="1002" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1002" s="132"/>
+      <c r="A1002" s="130"/>
       <c r="B1002" s="11"/>
       <c r="C1002" s="11"/>
       <c r="D1002" s="11"/>
@@ -32261,7 +32560,7 @@
       <c r="N1002" s="11"/>
     </row>
     <row r="1003" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1003" s="132"/>
+      <c r="A1003" s="130"/>
       <c r="B1003" s="115"/>
       <c r="C1003" s="115"/>
       <c r="D1003" s="115" t="s">
@@ -32287,7 +32586,7 @@
       <c r="N1003" s="115"/>
     </row>
     <row r="1004" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1004" s="132"/>
+      <c r="A1004" s="130"/>
       <c r="B1004" s="115"/>
       <c r="C1004" s="115"/>
       <c r="D1004" s="115"/>
@@ -32311,7 +32610,7 @@
       <c r="N1004" s="115"/>
     </row>
     <row r="1005" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1005" s="132"/>
+      <c r="A1005" s="130"/>
       <c r="B1005" s="115"/>
       <c r="C1005" s="115"/>
       <c r="D1005" s="115"/>
@@ -32335,7 +32634,7 @@
       <c r="N1005" s="115"/>
     </row>
     <row r="1006" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1006" s="132"/>
+      <c r="A1006" s="130"/>
       <c r="B1006" s="115"/>
       <c r="C1006" s="115"/>
       <c r="D1006" s="115"/>
@@ -32359,7 +32658,7 @@
       <c r="N1006" s="115"/>
     </row>
     <row r="1007" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1007" s="133"/>
+      <c r="A1007" s="131"/>
       <c r="B1007" s="115"/>
       <c r="C1007" s="115"/>
       <c r="D1007" s="115"/>
@@ -32399,7 +32698,7 @@
       <c r="N1008" s="11"/>
     </row>
     <row r="1009" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1009" s="131">
+      <c r="A1009" s="129">
         <v>183</v>
       </c>
       <c r="B1009" s="11" t="s">
@@ -32429,7 +32728,7 @@
       <c r="N1009" s="11"/>
     </row>
     <row r="1010" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1010" s="132"/>
+      <c r="A1010" s="130"/>
       <c r="B1010" s="11"/>
       <c r="C1010" s="11"/>
       <c r="D1010" s="11"/>
@@ -32453,7 +32752,7 @@
       <c r="N1010" s="11"/>
     </row>
     <row r="1011" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1011" s="132"/>
+      <c r="A1011" s="130"/>
       <c r="B1011" s="11"/>
       <c r="C1011" s="11"/>
       <c r="D1011" s="11"/>
@@ -32477,7 +32776,7 @@
       <c r="N1011" s="11"/>
     </row>
     <row r="1012" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1012" s="132"/>
+      <c r="A1012" s="130"/>
       <c r="B1012" s="11"/>
       <c r="C1012" s="11"/>
       <c r="D1012" s="11"/>
@@ -32501,7 +32800,7 @@
       <c r="N1012" s="11"/>
     </row>
     <row r="1013" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1013" s="132"/>
+      <c r="A1013" s="130"/>
       <c r="B1013" s="11"/>
       <c r="C1013" s="11"/>
       <c r="D1013" s="11"/>
@@ -32525,7 +32824,7 @@
       <c r="N1013" s="11"/>
     </row>
     <row r="1014" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1014" s="132"/>
+      <c r="A1014" s="130"/>
       <c r="B1014" s="11"/>
       <c r="C1014" s="11"/>
       <c r="D1014" s="11" t="s">
@@ -32551,7 +32850,7 @@
       <c r="N1014" s="11"/>
     </row>
     <row r="1015" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1015" s="132"/>
+      <c r="A1015" s="130"/>
       <c r="B1015" s="11"/>
       <c r="C1015" s="11"/>
       <c r="D1015" s="11"/>
@@ -32575,7 +32874,7 @@
       <c r="N1015" s="11"/>
     </row>
     <row r="1016" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1016" s="132"/>
+      <c r="A1016" s="130"/>
       <c r="B1016" s="11"/>
       <c r="C1016" s="11"/>
       <c r="D1016" s="11"/>
@@ -32599,7 +32898,7 @@
       <c r="N1016" s="11"/>
     </row>
     <row r="1017" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1017" s="132"/>
+      <c r="A1017" s="130"/>
       <c r="B1017" s="11"/>
       <c r="C1017" s="11"/>
       <c r="D1017" s="11"/>
@@ -32623,7 +32922,7 @@
       <c r="N1017" s="11"/>
     </row>
     <row r="1018" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1018" s="132"/>
+      <c r="A1018" s="130"/>
       <c r="B1018" s="11"/>
       <c r="C1018" s="11"/>
       <c r="D1018" s="11"/>
@@ -32647,7 +32946,7 @@
       <c r="N1018" s="11"/>
     </row>
     <row r="1019" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1019" s="132"/>
+      <c r="A1019" s="130"/>
       <c r="B1019" s="11"/>
       <c r="C1019" s="11"/>
       <c r="D1019" s="11" t="s">
@@ -32673,7 +32972,7 @@
       <c r="N1019" s="11"/>
     </row>
     <row r="1020" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1020" s="132"/>
+      <c r="A1020" s="130"/>
       <c r="B1020" s="11"/>
       <c r="C1020" s="11"/>
       <c r="D1020" s="11"/>
@@ -32697,7 +32996,7 @@
       <c r="N1020" s="11"/>
     </row>
     <row r="1021" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1021" s="132"/>
+      <c r="A1021" s="130"/>
       <c r="B1021" s="11"/>
       <c r="C1021" s="11"/>
       <c r="D1021" s="11"/>
@@ -32721,7 +33020,7 @@
       <c r="N1021" s="11"/>
     </row>
     <row r="1022" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1022" s="132"/>
+      <c r="A1022" s="130"/>
       <c r="B1022" s="11"/>
       <c r="C1022" s="11"/>
       <c r="D1022" s="11"/>
@@ -32745,7 +33044,7 @@
       <c r="N1022" s="11"/>
     </row>
     <row r="1023" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1023" s="132"/>
+      <c r="A1023" s="130"/>
       <c r="B1023" s="11"/>
       <c r="C1023" s="11"/>
       <c r="D1023" s="11"/>
@@ -32769,7 +33068,7 @@
       <c r="N1023" s="11"/>
     </row>
     <row r="1024" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1024" s="132"/>
+      <c r="A1024" s="130"/>
       <c r="B1024" s="11"/>
       <c r="C1024" s="11"/>
       <c r="D1024" s="11" t="s">
@@ -32795,7 +33094,7 @@
       <c r="N1024" s="11"/>
     </row>
     <row r="1025" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1025" s="132"/>
+      <c r="A1025" s="130"/>
       <c r="B1025" s="11"/>
       <c r="C1025" s="11"/>
       <c r="D1025" s="11"/>
@@ -32819,7 +33118,7 @@
       <c r="N1025" s="11"/>
     </row>
     <row r="1026" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1026" s="132"/>
+      <c r="A1026" s="130"/>
       <c r="B1026" s="11"/>
       <c r="C1026" s="11"/>
       <c r="D1026" s="11"/>
@@ -32843,7 +33142,7 @@
       <c r="N1026" s="11"/>
     </row>
     <row r="1027" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1027" s="132"/>
+      <c r="A1027" s="130"/>
       <c r="B1027" s="11"/>
       <c r="C1027" s="11"/>
       <c r="D1027" s="11"/>
@@ -32867,7 +33166,7 @@
       <c r="N1027" s="11"/>
     </row>
     <row r="1028" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1028" s="133"/>
+      <c r="A1028" s="131"/>
       <c r="B1028" s="11"/>
       <c r="C1028" s="11"/>
       <c r="D1028" s="11"/>
@@ -32907,7 +33206,7 @@
       <c r="N1029" s="11"/>
     </row>
     <row r="1030" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1030" s="131">
+      <c r="A1030" s="129">
         <v>184</v>
       </c>
       <c r="B1030" s="11" t="s">
@@ -32937,7 +33236,7 @@
       <c r="N1030" s="11"/>
     </row>
     <row r="1031" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1031" s="132"/>
+      <c r="A1031" s="130"/>
       <c r="B1031" s="11"/>
       <c r="C1031" s="11"/>
       <c r="D1031" s="11"/>
@@ -32961,7 +33260,7 @@
       <c r="N1031" s="11"/>
     </row>
     <row r="1032" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1032" s="132"/>
+      <c r="A1032" s="130"/>
       <c r="B1032" s="11"/>
       <c r="C1032" s="11"/>
       <c r="D1032" s="11"/>
@@ -32985,7 +33284,7 @@
       <c r="N1032" s="11"/>
     </row>
     <row r="1033" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1033" s="132"/>
+      <c r="A1033" s="130"/>
       <c r="B1033" s="11"/>
       <c r="C1033" s="11"/>
       <c r="D1033" s="11"/>
@@ -33009,7 +33308,7 @@
       <c r="N1033" s="11"/>
     </row>
     <row r="1034" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1034" s="132"/>
+      <c r="A1034" s="130"/>
       <c r="B1034" s="11"/>
       <c r="C1034" s="11"/>
       <c r="D1034" s="11"/>
@@ -33033,7 +33332,7 @@
       <c r="N1034" s="11"/>
     </row>
     <row r="1035" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1035" s="132"/>
+      <c r="A1035" s="130"/>
       <c r="B1035" s="11"/>
       <c r="C1035" s="11"/>
       <c r="D1035" s="11" t="s">
@@ -33059,7 +33358,7 @@
       <c r="N1035" s="11"/>
     </row>
     <row r="1036" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1036" s="132"/>
+      <c r="A1036" s="130"/>
       <c r="B1036" s="11"/>
       <c r="C1036" s="11"/>
       <c r="D1036" s="11"/>
@@ -33083,7 +33382,7 @@
       <c r="N1036" s="11"/>
     </row>
     <row r="1037" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1037" s="132"/>
+      <c r="A1037" s="130"/>
       <c r="B1037" s="11"/>
       <c r="C1037" s="11"/>
       <c r="D1037" s="11"/>
@@ -33107,7 +33406,7 @@
       <c r="N1037" s="11"/>
     </row>
     <row r="1038" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1038" s="132"/>
+      <c r="A1038" s="130"/>
       <c r="B1038" s="11"/>
       <c r="C1038" s="11"/>
       <c r="D1038" s="11"/>
@@ -33131,7 +33430,7 @@
       <c r="N1038" s="11"/>
     </row>
     <row r="1039" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1039" s="132"/>
+      <c r="A1039" s="130"/>
       <c r="B1039" s="11"/>
       <c r="C1039" s="11"/>
       <c r="D1039" s="11"/>
@@ -33155,7 +33454,7 @@
       <c r="N1039" s="11"/>
     </row>
     <row r="1040" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1040" s="132"/>
+      <c r="A1040" s="130"/>
       <c r="B1040" s="11"/>
       <c r="C1040" s="11"/>
       <c r="D1040" s="11" t="s">
@@ -33181,7 +33480,7 @@
       <c r="N1040" s="11"/>
     </row>
     <row r="1041" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1041" s="132"/>
+      <c r="A1041" s="130"/>
       <c r="B1041" s="11"/>
       <c r="C1041" s="11"/>
       <c r="D1041" s="11"/>
@@ -33205,7 +33504,7 @@
       <c r="N1041" s="11"/>
     </row>
     <row r="1042" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1042" s="132"/>
+      <c r="A1042" s="130"/>
       <c r="B1042" s="11"/>
       <c r="C1042" s="11"/>
       <c r="D1042" s="11"/>
@@ -33229,7 +33528,7 @@
       <c r="N1042" s="11"/>
     </row>
     <row r="1043" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1043" s="132"/>
+      <c r="A1043" s="130"/>
       <c r="B1043" s="11"/>
       <c r="C1043" s="11"/>
       <c r="D1043" s="11"/>
@@ -33253,7 +33552,7 @@
       <c r="N1043" s="11"/>
     </row>
     <row r="1044" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1044" s="132"/>
+      <c r="A1044" s="130"/>
       <c r="B1044" s="11"/>
       <c r="C1044" s="11"/>
       <c r="D1044" s="11"/>
@@ -33277,7 +33576,7 @@
       <c r="N1044" s="11"/>
     </row>
     <row r="1045" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1045" s="132"/>
+      <c r="A1045" s="130"/>
       <c r="B1045" s="11"/>
       <c r="C1045" s="11"/>
       <c r="D1045" s="11" t="s">
@@ -33303,7 +33602,7 @@
       <c r="N1045" s="11"/>
     </row>
     <row r="1046" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1046" s="132"/>
+      <c r="A1046" s="130"/>
       <c r="B1046" s="11"/>
       <c r="C1046" s="11"/>
       <c r="D1046" s="11"/>
@@ -33327,7 +33626,7 @@
       <c r="N1046" s="11"/>
     </row>
     <row r="1047" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1047" s="132"/>
+      <c r="A1047" s="130"/>
       <c r="B1047" s="11"/>
       <c r="C1047" s="11"/>
       <c r="D1047" s="11"/>
@@ -33351,7 +33650,7 @@
       <c r="N1047" s="11"/>
     </row>
     <row r="1048" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1048" s="132"/>
+      <c r="A1048" s="130"/>
       <c r="B1048" s="11"/>
       <c r="C1048" s="11"/>
       <c r="D1048" s="11"/>
@@ -33375,7 +33674,7 @@
       <c r="N1048" s="11"/>
     </row>
     <row r="1049" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1049" s="133"/>
+      <c r="A1049" s="131"/>
       <c r="B1049" s="11"/>
       <c r="C1049" s="11"/>
       <c r="D1049" s="11"/>
@@ -33415,7 +33714,7 @@
       <c r="N1050" s="11"/>
     </row>
     <row r="1051" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1051" s="131">
+      <c r="A1051" s="129">
         <v>185</v>
       </c>
       <c r="B1051" s="11" t="s">
@@ -33445,7 +33744,7 @@
       <c r="N1051" s="11"/>
     </row>
     <row r="1052" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1052" s="133"/>
+      <c r="A1052" s="131"/>
       <c r="B1052" s="11"/>
       <c r="C1052" s="11"/>
       <c r="D1052" s="11"/>
@@ -33485,7 +33784,7 @@
       <c r="N1053" s="11"/>
     </row>
     <row r="1054" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1054" s="131">
+      <c r="A1054" s="129">
         <v>186</v>
       </c>
       <c r="B1054" s="11" t="s">
@@ -33515,7 +33814,7 @@
       <c r="N1054" s="11"/>
     </row>
     <row r="1055" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1055" s="133"/>
+      <c r="A1055" s="131"/>
       <c r="B1055" s="11"/>
       <c r="C1055" s="11"/>
       <c r="D1055" s="11"/>
@@ -33555,7 +33854,7 @@
       <c r="N1056" s="11"/>
     </row>
     <row r="1057" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1057" s="131">
+      <c r="A1057" s="129">
         <v>187</v>
       </c>
       <c r="B1057" s="11" t="s">
@@ -33585,7 +33884,7 @@
       <c r="N1057" s="11"/>
     </row>
     <row r="1058" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1058" s="132"/>
+      <c r="A1058" s="130"/>
       <c r="B1058" s="11"/>
       <c r="C1058" s="11"/>
       <c r="D1058" s="11"/>
@@ -33609,7 +33908,7 @@
       <c r="N1058" s="11"/>
     </row>
     <row r="1059" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1059" s="132"/>
+      <c r="A1059" s="130"/>
       <c r="B1059" s="11"/>
       <c r="C1059" s="11"/>
       <c r="D1059" s="11" t="s">
@@ -33635,7 +33934,7 @@
       <c r="N1059" s="11"/>
     </row>
     <row r="1060" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1060" s="132"/>
+      <c r="A1060" s="130"/>
       <c r="B1060" s="11"/>
       <c r="C1060" s="11"/>
       <c r="D1060" s="11"/>
@@ -33659,7 +33958,7 @@
       <c r="N1060" s="11"/>
     </row>
     <row r="1061" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1061" s="132"/>
+      <c r="A1061" s="130"/>
       <c r="B1061" s="11"/>
       <c r="C1061" s="11"/>
       <c r="D1061" s="11" t="s">
@@ -33685,7 +33984,7 @@
       <c r="N1061" s="11"/>
     </row>
     <row r="1062" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1062" s="132"/>
+      <c r="A1062" s="130"/>
       <c r="B1062" s="11"/>
       <c r="C1062" s="11"/>
       <c r="D1062" s="11"/>
@@ -33709,7 +34008,7 @@
       <c r="N1062" s="11"/>
     </row>
     <row r="1063" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1063" s="132"/>
+      <c r="A1063" s="130"/>
       <c r="B1063" s="11"/>
       <c r="C1063" s="11"/>
       <c r="D1063" s="11" t="s">
@@ -33735,7 +34034,7 @@
       <c r="N1063" s="11"/>
     </row>
     <row r="1064" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1064" s="133"/>
+      <c r="A1064" s="131"/>
       <c r="B1064" s="11"/>
       <c r="C1064" s="11"/>
       <c r="D1064" s="11"/>
@@ -33775,7 +34074,7 @@
       <c r="N1065" s="11"/>
     </row>
     <row r="1066" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1066" s="131">
+      <c r="A1066" s="129">
         <v>188</v>
       </c>
       <c r="B1066" s="11" t="s">
@@ -33805,7 +34104,7 @@
       <c r="N1066" s="11"/>
     </row>
     <row r="1067" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1067" s="132"/>
+      <c r="A1067" s="130"/>
       <c r="B1067" s="11"/>
       <c r="C1067" s="11"/>
       <c r="D1067" s="11"/>
@@ -33829,7 +34128,7 @@
       <c r="N1067" s="11"/>
     </row>
     <row r="1068" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1068" s="132"/>
+      <c r="A1068" s="130"/>
       <c r="B1068" s="11"/>
       <c r="C1068" s="11"/>
       <c r="D1068" s="126" t="s">
@@ -33855,7 +34154,7 @@
       <c r="N1068" s="11"/>
     </row>
     <row r="1069" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1069" s="132"/>
+      <c r="A1069" s="130"/>
       <c r="B1069" s="11"/>
       <c r="C1069" s="11"/>
       <c r="D1069" s="11"/>
@@ -33879,7 +34178,7 @@
       <c r="N1069" s="11"/>
     </row>
     <row r="1070" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1070" s="132"/>
+      <c r="A1070" s="130"/>
       <c r="B1070" s="11"/>
       <c r="C1070" s="11"/>
       <c r="D1070" s="126" t="s">
@@ -33905,7 +34204,7 @@
       <c r="N1070" s="11"/>
     </row>
     <row r="1071" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1071" s="132"/>
+      <c r="A1071" s="130"/>
       <c r="B1071" s="11"/>
       <c r="C1071" s="11"/>
       <c r="D1071" s="11"/>
@@ -33929,7 +34228,7 @@
       <c r="N1071" s="11"/>
     </row>
     <row r="1072" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1072" s="132"/>
+      <c r="A1072" s="130"/>
       <c r="B1072" s="11"/>
       <c r="C1072" s="11"/>
       <c r="D1072" s="126" t="s">
@@ -33955,7 +34254,7 @@
       <c r="N1072" s="11"/>
     </row>
     <row r="1073" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1073" s="133"/>
+      <c r="A1073" s="131"/>
       <c r="B1073" s="11"/>
       <c r="C1073" s="11"/>
       <c r="D1073" s="11"/>
@@ -33995,7 +34294,7 @@
       <c r="N1074" s="11"/>
     </row>
     <row r="1075" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1075" s="131">
+      <c r="A1075" s="129">
         <v>189</v>
       </c>
       <c r="B1075" s="11" t="s">
@@ -34027,7 +34326,7 @@
       </c>
     </row>
     <row r="1076" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1076" s="132"/>
+      <c r="A1076" s="130"/>
       <c r="B1076" s="11"/>
       <c r="C1076" s="11"/>
       <c r="D1076" s="11"/>
@@ -34051,7 +34350,7 @@
       <c r="N1076" s="11"/>
     </row>
     <row r="1077" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1077" s="132"/>
+      <c r="A1077" s="130"/>
       <c r="B1077" s="11"/>
       <c r="C1077" s="11"/>
       <c r="D1077" s="11"/>
@@ -34075,7 +34374,7 @@
       <c r="N1077" s="11"/>
     </row>
     <row r="1078" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1078" s="132"/>
+      <c r="A1078" s="130"/>
       <c r="B1078" s="11"/>
       <c r="C1078" s="11"/>
       <c r="D1078" s="11"/>
@@ -34099,7 +34398,7 @@
       <c r="N1078" s="11"/>
     </row>
     <row r="1079" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1079" s="132"/>
+      <c r="A1079" s="130"/>
       <c r="B1079" s="11"/>
       <c r="C1079" s="11"/>
       <c r="D1079" s="11"/>
@@ -34123,7 +34422,7 @@
       <c r="N1079" s="11"/>
     </row>
     <row r="1080" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1080" s="132"/>
+      <c r="A1080" s="130"/>
       <c r="B1080" s="11"/>
       <c r="C1080" s="11"/>
       <c r="D1080" s="125" t="s">
@@ -34149,7 +34448,7 @@
       <c r="N1080" s="11"/>
     </row>
     <row r="1081" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1081" s="132"/>
+      <c r="A1081" s="130"/>
       <c r="B1081" s="11"/>
       <c r="C1081" s="11"/>
       <c r="D1081" s="11"/>
@@ -34173,7 +34472,7 @@
       <c r="N1081" s="11"/>
     </row>
     <row r="1082" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1082" s="132"/>
+      <c r="A1082" s="130"/>
       <c r="B1082" s="11"/>
       <c r="C1082" s="11"/>
       <c r="D1082" s="11"/>
@@ -34197,7 +34496,7 @@
       <c r="N1082" s="11"/>
     </row>
     <row r="1083" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1083" s="132"/>
+      <c r="A1083" s="130"/>
       <c r="B1083" s="11"/>
       <c r="C1083" s="11"/>
       <c r="D1083" s="11"/>
@@ -34221,7 +34520,7 @@
       <c r="N1083" s="11"/>
     </row>
     <row r="1084" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1084" s="133"/>
+      <c r="A1084" s="131"/>
       <c r="B1084" s="11"/>
       <c r="C1084" s="11"/>
       <c r="D1084" s="11"/>
@@ -34261,7 +34560,7 @@
       <c r="N1085" s="11"/>
     </row>
     <row r="1086" spans="1:14" ht="15" hidden="1" customHeight="1">
-      <c r="A1086" s="131">
+      <c r="A1086" s="129">
         <v>190</v>
       </c>
       <c r="B1086" s="11" t="s">
@@ -34291,7 +34590,7 @@
       <c r="N1086" s="11"/>
     </row>
     <row r="1087" spans="1:14" ht="15" hidden="1" customHeight="1">
-      <c r="A1087" s="132"/>
+      <c r="A1087" s="130"/>
       <c r="B1087" s="11"/>
       <c r="C1087" s="11"/>
       <c r="D1087" s="11"/>
@@ -34315,7 +34614,7 @@
       <c r="N1087" s="11"/>
     </row>
     <row r="1088" spans="1:14" ht="15" hidden="1" customHeight="1">
-      <c r="A1088" s="132"/>
+      <c r="A1088" s="130"/>
       <c r="B1088" s="11"/>
       <c r="C1088" s="11"/>
       <c r="D1088" s="11" t="s">
@@ -34341,7 +34640,7 @@
       <c r="N1088" s="11"/>
     </row>
     <row r="1089" spans="1:14" ht="15" hidden="1" customHeight="1">
-      <c r="A1089" s="133"/>
+      <c r="A1089" s="131"/>
       <c r="B1089" s="11"/>
       <c r="C1089" s="11"/>
       <c r="D1089" s="11"/>
@@ -34381,7 +34680,7 @@
       <c r="N1090" s="11"/>
     </row>
     <row r="1091" spans="1:14" ht="15" hidden="1" customHeight="1">
-      <c r="A1091" s="131">
+      <c r="A1091" s="129">
         <v>191</v>
       </c>
       <c r="B1091" s="11" t="s">
@@ -34411,7 +34710,7 @@
       <c r="N1091" s="11"/>
     </row>
     <row r="1092" spans="1:14" ht="15" hidden="1" customHeight="1">
-      <c r="A1092" s="133"/>
+      <c r="A1092" s="131"/>
       <c r="B1092" s="11"/>
       <c r="C1092" s="11"/>
       <c r="D1092" s="11"/>
@@ -34541,7 +34840,7 @@
       <c r="N1097" s="11"/>
     </row>
     <row r="1098" spans="1:14" ht="15" hidden="1" customHeight="1">
-      <c r="A1098" s="131">
+      <c r="A1098" s="129">
         <v>194</v>
       </c>
       <c r="B1098" s="11"/>
@@ -34569,7 +34868,7 @@
       <c r="N1098" s="11"/>
     </row>
     <row r="1099" spans="1:14" ht="15" hidden="1" customHeight="1">
-      <c r="A1099" s="132"/>
+      <c r="A1099" s="130"/>
       <c r="B1099" s="11"/>
       <c r="C1099" s="11"/>
       <c r="D1099" s="11" t="s">
@@ -34595,7 +34894,7 @@
       <c r="N1099" s="11"/>
     </row>
     <row r="1100" spans="1:14" ht="15" hidden="1" customHeight="1">
-      <c r="A1100" s="132"/>
+      <c r="A1100" s="130"/>
       <c r="B1100" s="11"/>
       <c r="C1100" s="11"/>
       <c r="D1100" s="11" t="s">
@@ -34621,7 +34920,7 @@
       <c r="N1100" s="11"/>
     </row>
     <row r="1101" spans="1:14" ht="15" hidden="1" customHeight="1">
-      <c r="A1101" s="133"/>
+      <c r="A1101" s="131"/>
       <c r="B1101" s="11"/>
       <c r="C1101" s="11"/>
       <c r="D1101" s="11" t="s">
@@ -34663,7 +34962,7 @@
       <c r="N1102" s="11"/>
     </row>
     <row r="1103" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1103" s="131">
+      <c r="A1103" s="129">
         <v>195</v>
       </c>
       <c r="B1103" s="11"/>
@@ -34691,7 +34990,7 @@
       <c r="N1103" s="11"/>
     </row>
     <row r="1104" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1104" s="132"/>
+      <c r="A1104" s="130"/>
       <c r="B1104" s="11"/>
       <c r="C1104" s="11"/>
       <c r="D1104" s="11" t="s">
@@ -34717,7 +35016,7 @@
       <c r="N1104" s="11"/>
     </row>
     <row r="1105" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1105" s="132"/>
+      <c r="A1105" s="130"/>
       <c r="B1105" s="11"/>
       <c r="C1105" s="11"/>
       <c r="D1105" s="11" t="s">
@@ -34743,7 +35042,7 @@
       <c r="N1105" s="11"/>
     </row>
     <row r="1106" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1106" s="132"/>
+      <c r="A1106" s="130"/>
       <c r="B1106" s="11"/>
       <c r="C1106" s="11"/>
       <c r="D1106" s="11" t="s">
@@ -34769,7 +35068,7 @@
       <c r="N1106" s="11"/>
     </row>
     <row r="1107" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1107" s="132"/>
+      <c r="A1107" s="130"/>
       <c r="B1107" s="11"/>
       <c r="C1107" s="11"/>
       <c r="D1107" s="11" t="s">
@@ -34795,7 +35094,7 @@
       <c r="N1107" s="11"/>
     </row>
     <row r="1108" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1108" s="132"/>
+      <c r="A1108" s="130"/>
       <c r="B1108" s="11"/>
       <c r="C1108" s="11"/>
       <c r="D1108" s="11" t="s">
@@ -34821,7 +35120,7 @@
       <c r="N1108" s="11"/>
     </row>
     <row r="1109" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1109" s="132"/>
+      <c r="A1109" s="130"/>
       <c r="B1109" s="11"/>
       <c r="C1109" s="11"/>
       <c r="D1109" s="11" t="s">
@@ -34847,7 +35146,7 @@
       <c r="N1109" s="11"/>
     </row>
     <row r="1110" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1110" s="132"/>
+      <c r="A1110" s="130"/>
       <c r="B1110" s="11"/>
       <c r="C1110" s="11"/>
       <c r="D1110" s="11" t="s">
@@ -34873,7 +35172,7 @@
       <c r="N1110" s="11"/>
     </row>
     <row r="1111" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1111" s="132"/>
+      <c r="A1111" s="130"/>
       <c r="B1111" s="11"/>
       <c r="C1111" s="11"/>
       <c r="D1111" s="11" t="s">
@@ -34899,7 +35198,7 @@
       <c r="N1111" s="11"/>
     </row>
     <row r="1112" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1112" s="132"/>
+      <c r="A1112" s="130"/>
       <c r="B1112" s="11"/>
       <c r="C1112" s="11"/>
       <c r="D1112" s="11" t="s">
@@ -34925,7 +35224,7 @@
       <c r="N1112" s="11"/>
     </row>
     <row r="1113" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1113" s="132"/>
+      <c r="A1113" s="130"/>
       <c r="B1113" s="11"/>
       <c r="C1113" s="11"/>
       <c r="D1113" s="11" t="s">
@@ -34951,7 +35250,7 @@
       <c r="N1113" s="11"/>
     </row>
     <row r="1114" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1114" s="132"/>
+      <c r="A1114" s="130"/>
       <c r="B1114" s="11"/>
       <c r="C1114" s="11"/>
       <c r="D1114" s="11" t="s">
@@ -34977,7 +35276,7 @@
       <c r="N1114" s="11"/>
     </row>
     <row r="1115" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1115" s="132"/>
+      <c r="A1115" s="130"/>
       <c r="B1115" s="11"/>
       <c r="C1115" s="11"/>
       <c r="D1115" s="11" t="s">
@@ -35003,7 +35302,7 @@
       <c r="N1115" s="11"/>
     </row>
     <row r="1116" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1116" s="132"/>
+      <c r="A1116" s="130"/>
       <c r="B1116" s="11"/>
       <c r="C1116" s="11"/>
       <c r="D1116" s="11" t="s">
@@ -35029,7 +35328,7 @@
       <c r="N1116" s="11"/>
     </row>
     <row r="1117" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1117" s="132"/>
+      <c r="A1117" s="130"/>
       <c r="B1117" s="11"/>
       <c r="C1117" s="11"/>
       <c r="D1117" s="11" t="s">
@@ -35055,7 +35354,7 @@
       <c r="N1117" s="11"/>
     </row>
     <row r="1118" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1118" s="132"/>
+      <c r="A1118" s="130"/>
       <c r="B1118" s="11"/>
       <c r="C1118" s="11"/>
       <c r="D1118" s="11" t="s">
@@ -35081,7 +35380,7 @@
       <c r="N1118" s="11"/>
     </row>
     <row r="1119" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1119" s="132"/>
+      <c r="A1119" s="130"/>
       <c r="B1119" s="11"/>
       <c r="C1119" s="11"/>
       <c r="D1119" s="11" t="s">
@@ -35107,7 +35406,7 @@
       <c r="N1119" s="11"/>
     </row>
     <row r="1120" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1120" s="132"/>
+      <c r="A1120" s="130"/>
       <c r="B1120" s="11"/>
       <c r="C1120" s="11"/>
       <c r="D1120" s="11" t="s">
@@ -35133,7 +35432,7 @@
       <c r="N1120" s="11"/>
     </row>
     <row r="1121" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1121" s="132"/>
+      <c r="A1121" s="130"/>
       <c r="B1121" s="11"/>
       <c r="C1121" s="11"/>
       <c r="D1121" s="11" t="s">
@@ -35159,7 +35458,7 @@
       <c r="N1121" s="11"/>
     </row>
     <row r="1122" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1122" s="132"/>
+      <c r="A1122" s="130"/>
       <c r="B1122" s="11"/>
       <c r="C1122" s="11"/>
       <c r="D1122" s="11" t="s">
@@ -35185,7 +35484,7 @@
       <c r="N1122" s="11"/>
     </row>
     <row r="1123" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1123" s="132"/>
+      <c r="A1123" s="130"/>
       <c r="B1123" s="11"/>
       <c r="C1123" s="11"/>
       <c r="D1123" s="11" t="s">
@@ -35211,7 +35510,7 @@
       <c r="N1123" s="11"/>
     </row>
     <row r="1124" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1124" s="132"/>
+      <c r="A1124" s="130"/>
       <c r="B1124" s="11"/>
       <c r="C1124" s="11"/>
       <c r="D1124" s="11" t="s">
@@ -35237,7 +35536,7 @@
       <c r="N1124" s="11"/>
     </row>
     <row r="1125" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1125" s="132"/>
+      <c r="A1125" s="130"/>
       <c r="B1125" s="11"/>
       <c r="C1125" s="11"/>
       <c r="D1125" s="11" t="s">
@@ -35263,7 +35562,7 @@
       <c r="N1125" s="11"/>
     </row>
     <row r="1126" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1126" s="133"/>
+      <c r="A1126" s="131"/>
       <c r="B1126" s="11"/>
       <c r="C1126" s="11"/>
       <c r="D1126" s="11" t="s">
@@ -35349,7 +35648,7 @@
       <c r="N1129" s="11"/>
     </row>
     <row r="1130" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1130" s="131">
+      <c r="A1130" s="129">
         <v>197</v>
       </c>
       <c r="B1130" s="70" t="s">
@@ -35379,7 +35678,7 @@
       <c r="N1130" s="11"/>
     </row>
     <row r="1131" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1131" s="132"/>
+      <c r="A1131" s="130"/>
       <c r="B1131" s="70" t="s">
         <v>556</v>
       </c>
@@ -35407,7 +35706,7 @@
       <c r="N1131" s="11"/>
     </row>
     <row r="1132" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1132" s="132"/>
+      <c r="A1132" s="130"/>
       <c r="B1132" s="70" t="s">
         <v>556</v>
       </c>
@@ -35435,7 +35734,7 @@
       <c r="N1132" s="11"/>
     </row>
     <row r="1133" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1133" s="133"/>
+      <c r="A1133" s="131"/>
       <c r="B1133" s="70" t="s">
         <v>556</v>
       </c>
@@ -35479,7 +35778,7 @@
       <c r="N1134" s="11"/>
     </row>
     <row r="1135" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1135" s="131">
+      <c r="A1135" s="129">
         <v>202</v>
       </c>
       <c r="B1135" s="70">
@@ -35509,7 +35808,7 @@
       <c r="N1135" s="11"/>
     </row>
     <row r="1136" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1136" s="132"/>
+      <c r="A1136" s="130"/>
       <c r="B1136" s="70">
         <v>59</v>
       </c>
@@ -35537,7 +35836,7 @@
       <c r="N1136" s="11"/>
     </row>
     <row r="1137" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1137" s="132"/>
+      <c r="A1137" s="130"/>
       <c r="B1137" s="70">
         <v>59</v>
       </c>
@@ -35565,7 +35864,7 @@
       <c r="N1137" s="11"/>
     </row>
     <row r="1138" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1138" s="133"/>
+      <c r="A1138" s="131"/>
       <c r="B1138" s="70">
         <v>59</v>
       </c>
@@ -35609,7 +35908,7 @@
       <c r="N1139" s="11"/>
     </row>
     <row r="1140" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1140" s="131">
+      <c r="A1140" s="129">
         <v>203</v>
       </c>
       <c r="B1140" s="70" t="s">
@@ -35639,7 +35938,7 @@
       <c r="N1140" s="11"/>
     </row>
     <row r="1141" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1141" s="132"/>
+      <c r="A1141" s="130"/>
       <c r="B1141" s="70" t="s">
         <v>559</v>
       </c>
@@ -35667,7 +35966,7 @@
       <c r="N1141" s="11"/>
     </row>
     <row r="1142" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1142" s="132"/>
+      <c r="A1142" s="130"/>
       <c r="B1142" s="70" t="s">
         <v>559</v>
       </c>
@@ -35695,7 +35994,7 @@
       <c r="N1142" s="11"/>
     </row>
     <row r="1143" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1143" s="133"/>
+      <c r="A1143" s="131"/>
       <c r="B1143" s="70" t="s">
         <v>559</v>
       </c>
@@ -35739,7 +36038,7 @@
       <c r="N1144" s="11"/>
     </row>
     <row r="1145" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1145" s="131">
+      <c r="A1145" s="129">
         <v>204</v>
       </c>
       <c r="B1145" s="70">
@@ -35769,7 +36068,7 @@
       <c r="N1145" s="11"/>
     </row>
     <row r="1146" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1146" s="132"/>
+      <c r="A1146" s="130"/>
       <c r="B1146" s="70">
         <v>27</v>
       </c>
@@ -35797,7 +36096,7 @@
       <c r="N1146" s="11"/>
     </row>
     <row r="1147" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1147" s="132"/>
+      <c r="A1147" s="130"/>
       <c r="B1147" s="70">
         <v>27</v>
       </c>
@@ -35825,7 +36124,7 @@
       <c r="N1147" s="11"/>
     </row>
     <row r="1148" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1148" s="133"/>
+      <c r="A1148" s="131"/>
       <c r="B1148" s="70">
         <v>27</v>
       </c>
@@ -35869,7 +36168,7 @@
       <c r="N1149" s="11"/>
     </row>
     <row r="1150" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1150" s="131">
+      <c r="A1150" s="129">
         <v>205</v>
       </c>
       <c r="B1150" s="70" t="s">
@@ -35899,7 +36198,7 @@
       <c r="N1150" s="11"/>
     </row>
     <row r="1151" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1151" s="132"/>
+      <c r="A1151" s="130"/>
       <c r="B1151" s="70" t="s">
         <v>562</v>
       </c>
@@ -35927,7 +36226,7 @@
       <c r="N1151" s="11"/>
     </row>
     <row r="1152" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1152" s="132"/>
+      <c r="A1152" s="130"/>
       <c r="B1152" s="70" t="s">
         <v>562</v>
       </c>
@@ -35955,7 +36254,7 @@
       <c r="N1152" s="11"/>
     </row>
     <row r="1153" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1153" s="133"/>
+      <c r="A1153" s="131"/>
       <c r="B1153" s="70" t="s">
         <v>562</v>
       </c>
@@ -35999,7 +36298,7 @@
       <c r="N1154" s="11"/>
     </row>
     <row r="1155" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1155" s="131">
+      <c r="A1155" s="129">
         <v>206</v>
       </c>
       <c r="B1155" s="70">
@@ -36029,7 +36328,7 @@
       <c r="N1155" s="11"/>
     </row>
     <row r="1156" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1156" s="132"/>
+      <c r="A1156" s="130"/>
       <c r="B1156" s="70">
         <v>40</v>
       </c>
@@ -36057,7 +36356,7 @@
       <c r="N1156" s="11"/>
     </row>
     <row r="1157" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1157" s="132"/>
+      <c r="A1157" s="130"/>
       <c r="B1157" s="70">
         <v>40</v>
       </c>
@@ -36085,7 +36384,7 @@
       <c r="N1157" s="11"/>
     </row>
     <row r="1158" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1158" s="133"/>
+      <c r="A1158" s="131"/>
       <c r="B1158" s="70">
         <v>40</v>
       </c>
@@ -36129,7 +36428,7 @@
       <c r="N1159" s="11"/>
     </row>
     <row r="1160" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1160" s="131">
+      <c r="A1160" s="129">
         <v>207</v>
       </c>
       <c r="B1160" s="70" t="s">
@@ -36159,7 +36458,7 @@
       <c r="N1160" s="11"/>
     </row>
     <row r="1161" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1161" s="132"/>
+      <c r="A1161" s="130"/>
       <c r="B1161" s="70" t="s">
         <v>565</v>
       </c>
@@ -36187,7 +36486,7 @@
       <c r="N1161" s="11"/>
     </row>
     <row r="1162" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1162" s="132"/>
+      <c r="A1162" s="130"/>
       <c r="B1162" s="70" t="s">
         <v>565</v>
       </c>
@@ -36215,7 +36514,7 @@
       <c r="N1162" s="11"/>
     </row>
     <row r="1163" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1163" s="133"/>
+      <c r="A1163" s="131"/>
       <c r="B1163" s="70" t="s">
         <v>565</v>
       </c>
@@ -36259,7 +36558,7 @@
       <c r="N1164" s="11"/>
     </row>
     <row r="1165" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1165" s="131">
+      <c r="A1165" s="129">
         <v>208</v>
       </c>
       <c r="B1165" s="70">
@@ -36289,7 +36588,7 @@
       <c r="N1165" s="11"/>
     </row>
     <row r="1166" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1166" s="132"/>
+      <c r="A1166" s="130"/>
       <c r="B1166" s="70">
         <v>81</v>
       </c>
@@ -36317,7 +36616,7 @@
       <c r="N1166" s="11"/>
     </row>
     <row r="1167" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1167" s="132"/>
+      <c r="A1167" s="130"/>
       <c r="B1167" s="70">
         <v>81</v>
       </c>
@@ -36345,7 +36644,7 @@
       <c r="N1167" s="11"/>
     </row>
     <row r="1168" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1168" s="133"/>
+      <c r="A1168" s="131"/>
       <c r="B1168" s="70">
         <v>81</v>
       </c>
@@ -36389,7 +36688,7 @@
       <c r="N1169" s="11"/>
     </row>
     <row r="1170" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1170" s="131">
+      <c r="A1170" s="129">
         <v>209</v>
       </c>
       <c r="B1170" s="70">
@@ -36419,7 +36718,7 @@
       <c r="N1170" s="11"/>
     </row>
     <row r="1171" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1171" s="132"/>
+      <c r="A1171" s="130"/>
       <c r="B1171" s="70">
         <v>46</v>
       </c>
@@ -36447,7 +36746,7 @@
       <c r="N1171" s="11"/>
     </row>
     <row r="1172" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1172" s="132"/>
+      <c r="A1172" s="130"/>
       <c r="B1172" s="70">
         <v>46</v>
       </c>
@@ -36475,7 +36774,7 @@
       <c r="N1172" s="11"/>
     </row>
     <row r="1173" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1173" s="133"/>
+      <c r="A1173" s="131"/>
       <c r="B1173" s="70">
         <v>46</v>
       </c>
@@ -36519,7 +36818,7 @@
       <c r="N1174" s="11"/>
     </row>
     <row r="1175" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1175" s="131">
+      <c r="A1175" s="129">
         <v>210</v>
       </c>
       <c r="B1175" s="70">
@@ -36549,7 +36848,7 @@
       <c r="N1175" s="11"/>
     </row>
     <row r="1176" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1176" s="132"/>
+      <c r="A1176" s="130"/>
       <c r="B1176" s="70">
         <v>86</v>
       </c>
@@ -36577,7 +36876,7 @@
       <c r="N1176" s="11"/>
     </row>
     <row r="1177" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1177" s="132"/>
+      <c r="A1177" s="130"/>
       <c r="B1177" s="70">
         <v>86</v>
       </c>
@@ -36605,7 +36904,7 @@
       <c r="N1177" s="11"/>
     </row>
     <row r="1178" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1178" s="133"/>
+      <c r="A1178" s="131"/>
       <c r="B1178" s="70">
         <v>86</v>
       </c>
@@ -36813,7 +37112,7 @@
       <c r="N1186" s="14"/>
     </row>
     <row r="1187" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1187" s="138"/>
+      <c r="A1187" s="136"/>
       <c r="B1187" s="5" t="s">
         <v>48</v>
       </c>
@@ -36843,7 +37142,7 @@
       <c r="N1187" s="14"/>
     </row>
     <row r="1188" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1188" s="138"/>
+      <c r="A1188" s="136"/>
       <c r="B1188" s="5" t="s">
         <v>48</v>
       </c>
@@ -36873,17 +37172,17 @@
       <c r="N1188" s="14"/>
     </row>
     <row r="1189" spans="1:14" ht="18.75" hidden="1" customHeight="1">
-      <c r="A1189" s="138"/>
+      <c r="A1189" s="136"/>
       <c r="B1189" s="66" t="s">
         <v>48</v>
       </c>
       <c r="C1189" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="D1189" s="146" t="s">
+      <c r="D1189" s="144" t="s">
         <v>574</v>
       </c>
-      <c r="E1189" s="147"/>
+      <c r="E1189" s="145"/>
       <c r="F1189" s="66" t="s">
         <v>15</v>
       </c>
@@ -38992,6 +39291,543 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF4EC6AF-B661-4C65-A2DC-5863988C9585}">
+  <dimension ref="B1:D47"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="87.44140625" customWidth="1"/>
+    <col min="3" max="3" width="29.21875" customWidth="1"/>
+    <col min="4" max="4" width="68" customWidth="1"/>
+    <col min="5" max="6" width="8.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:4">
+      <c r="B1" t="s">
+        <v>634</v>
+      </c>
+      <c r="C1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D1" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="2" spans="2:4" ht="18">
+      <c r="B2" s="150" t="s">
+        <v>252</v>
+      </c>
+      <c r="C2" t="s">
+        <v>640</v>
+      </c>
+      <c r="D2" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" ht="18">
+      <c r="B3" s="152" t="s">
+        <v>281</v>
+      </c>
+      <c r="C3" t="s">
+        <v>640</v>
+      </c>
+      <c r="D3" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" ht="18">
+      <c r="B4" s="146" t="s">
+        <v>198</v>
+      </c>
+      <c r="C4" t="s">
+        <v>692</v>
+      </c>
+      <c r="D4" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" ht="18">
+      <c r="B5" s="146" t="s">
+        <v>198</v>
+      </c>
+      <c r="C5" t="s">
+        <v>692</v>
+      </c>
+      <c r="D5" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="18">
+      <c r="B6" s="146" t="s">
+        <v>198</v>
+      </c>
+      <c r="C6" t="s">
+        <v>692</v>
+      </c>
+      <c r="D6" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="18">
+      <c r="B7" s="146" t="s">
+        <v>207</v>
+      </c>
+      <c r="C7" t="s">
+        <v>692</v>
+      </c>
+      <c r="D7" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="18">
+      <c r="B8" s="146" t="s">
+        <v>636</v>
+      </c>
+      <c r="C8" t="s">
+        <v>692</v>
+      </c>
+      <c r="D8" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" ht="18">
+      <c r="B9" s="151" t="s">
+        <v>365</v>
+      </c>
+      <c r="C9" t="s">
+        <v>653</v>
+      </c>
+      <c r="D9" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" ht="18">
+      <c r="B10" s="152" t="s">
+        <v>369</v>
+      </c>
+      <c r="C10" t="s">
+        <v>653</v>
+      </c>
+      <c r="D10" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" ht="18">
+      <c r="B11" s="47" t="s">
+        <v>371</v>
+      </c>
+      <c r="C11" t="s">
+        <v>653</v>
+      </c>
+      <c r="D11" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" ht="18">
+      <c r="B12" s="152" t="s">
+        <v>109</v>
+      </c>
+      <c r="C12" t="s">
+        <v>693</v>
+      </c>
+      <c r="D12" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" ht="18">
+      <c r="B13" s="152" t="s">
+        <v>212</v>
+      </c>
+      <c r="C13" t="s">
+        <v>693</v>
+      </c>
+      <c r="D13" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" ht="18">
+      <c r="B14" s="47" t="s">
+        <v>214</v>
+      </c>
+      <c r="C14" t="s">
+        <v>693</v>
+      </c>
+      <c r="D14" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" ht="18">
+      <c r="B15" s="152" t="s">
+        <v>216</v>
+      </c>
+      <c r="C15" t="s">
+        <v>693</v>
+      </c>
+      <c r="D15" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" ht="18">
+      <c r="B16" s="47" t="s">
+        <v>218</v>
+      </c>
+      <c r="C16" t="s">
+        <v>693</v>
+      </c>
+      <c r="D16" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" ht="18">
+      <c r="B17" s="152" t="s">
+        <v>220</v>
+      </c>
+      <c r="C17" t="s">
+        <v>693</v>
+      </c>
+      <c r="D17" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" ht="18">
+      <c r="B18" s="47" t="s">
+        <v>222</v>
+      </c>
+      <c r="C18" t="s">
+        <v>693</v>
+      </c>
+      <c r="D18" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" ht="18">
+      <c r="B19" s="152" t="s">
+        <v>224</v>
+      </c>
+      <c r="C19" t="s">
+        <v>693</v>
+      </c>
+      <c r="D19" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" ht="18">
+      <c r="B20" s="47" t="s">
+        <v>240</v>
+      </c>
+      <c r="C20" t="s">
+        <v>670</v>
+      </c>
+      <c r="D20" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" ht="18">
+      <c r="B21" s="47" t="s">
+        <v>323</v>
+      </c>
+      <c r="C21" t="s">
+        <v>670</v>
+      </c>
+      <c r="D21" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" ht="18">
+      <c r="B22" s="152" t="s">
+        <v>325</v>
+      </c>
+      <c r="C22" t="s">
+        <v>669</v>
+      </c>
+      <c r="D22" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" ht="18">
+      <c r="B23" s="47" t="s">
+        <v>327</v>
+      </c>
+      <c r="C23" t="s">
+        <v>669</v>
+      </c>
+      <c r="D23" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" ht="18">
+      <c r="B24" s="152" t="s">
+        <v>329</v>
+      </c>
+      <c r="C24" t="s">
+        <v>669</v>
+      </c>
+      <c r="D24" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" ht="18">
+      <c r="B25" s="146" t="s">
+        <v>226</v>
+      </c>
+      <c r="C25" t="s">
+        <v>646</v>
+      </c>
+      <c r="D25" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" ht="18">
+      <c r="B26" s="146" t="s">
+        <v>229</v>
+      </c>
+      <c r="C26" t="s">
+        <v>646</v>
+      </c>
+      <c r="D26" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" ht="18">
+      <c r="B27" s="153" t="s">
+        <v>232</v>
+      </c>
+      <c r="C27" t="s">
+        <v>646</v>
+      </c>
+      <c r="D27" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" ht="18">
+      <c r="B28" s="146" t="s">
+        <v>234</v>
+      </c>
+      <c r="C28" t="s">
+        <v>646</v>
+      </c>
+      <c r="D28" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" ht="18">
+      <c r="B29" s="146" t="s">
+        <v>236</v>
+      </c>
+      <c r="C29" t="s">
+        <v>646</v>
+      </c>
+      <c r="D29" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" ht="18">
+      <c r="B30" s="146" t="s">
+        <v>238</v>
+      </c>
+      <c r="C30" t="s">
+        <v>646</v>
+      </c>
+      <c r="D30" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" ht="18">
+      <c r="B31" s="152" t="s">
+        <v>248</v>
+      </c>
+      <c r="C31" t="s">
+        <v>672</v>
+      </c>
+      <c r="D31" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" ht="18">
+      <c r="B32" s="47" t="s">
+        <v>250</v>
+      </c>
+      <c r="C32" t="s">
+        <v>672</v>
+      </c>
+      <c r="D32" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" ht="18">
+      <c r="B33" s="47" t="s">
+        <v>268</v>
+      </c>
+      <c r="C33" t="s">
+        <v>672</v>
+      </c>
+      <c r="D33" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" ht="18">
+      <c r="B34" s="152" t="s">
+        <v>270</v>
+      </c>
+      <c r="C34" t="s">
+        <v>672</v>
+      </c>
+      <c r="D34" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" ht="18">
+      <c r="B35" s="154" t="s">
+        <v>190</v>
+      </c>
+      <c r="C35" t="s">
+        <v>683</v>
+      </c>
+      <c r="D35" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" ht="18">
+      <c r="B36" s="17" t="s">
+        <v>346</v>
+      </c>
+      <c r="C36" t="s">
+        <v>683</v>
+      </c>
+      <c r="D36" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" ht="18">
+      <c r="B37" s="154" t="s">
+        <v>349</v>
+      </c>
+      <c r="C37" t="s">
+        <v>635</v>
+      </c>
+      <c r="D37" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" ht="18">
+      <c r="B38" s="154" t="s">
+        <v>351</v>
+      </c>
+      <c r="C38" t="s">
+        <v>635</v>
+      </c>
+      <c r="D38" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" ht="18">
+      <c r="B39" s="155" t="s">
+        <v>354</v>
+      </c>
+      <c r="C39" t="s">
+        <v>635</v>
+      </c>
+      <c r="D39" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" ht="18">
+      <c r="B40" s="154" t="s">
+        <v>363</v>
+      </c>
+      <c r="C40" t="s">
+        <v>635</v>
+      </c>
+      <c r="D40" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" ht="18">
+      <c r="B41" s="152" t="s">
+        <v>243</v>
+      </c>
+      <c r="C41" t="s">
+        <v>684</v>
+      </c>
+      <c r="D41" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" ht="18">
+      <c r="B42" s="47" t="s">
+        <v>246</v>
+      </c>
+      <c r="C42" t="s">
+        <v>684</v>
+      </c>
+      <c r="D42" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" ht="18">
+      <c r="B43" s="47" t="s">
+        <v>259</v>
+      </c>
+      <c r="C43" t="s">
+        <v>684</v>
+      </c>
+      <c r="D43" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" ht="18">
+      <c r="B44" s="152" t="s">
+        <v>262</v>
+      </c>
+      <c r="C44" t="s">
+        <v>684</v>
+      </c>
+      <c r="D44" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" ht="18">
+      <c r="B45" s="47" t="s">
+        <v>264</v>
+      </c>
+      <c r="C45" t="s">
+        <v>684</v>
+      </c>
+      <c r="D45" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" ht="18">
+      <c r="B46" s="152" t="s">
+        <v>266</v>
+      </c>
+      <c r="C46" t="s">
+        <v>684</v>
+      </c>
+      <c r="D46" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" ht="18">
+      <c r="B47" s="156" t="s">
+        <v>272</v>
+      </c>
+      <c r="C47" t="s">
+        <v>684</v>
+      </c>
+      <c r="D47" t="s">
+        <v>691</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F16041B-08CB-4EC6-9E47-CBC37F9DFA6A}">
   <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -39285,7 +40121,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEBAB262-57D3-42DC-96D3-D86004D06A38}">
   <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
